--- a/budget/output/Сводный бюджет Екатеринбурга.xlsx
+++ b/budget/output/Сводный бюджет Екатеринбурга.xlsx
@@ -6015,7 +6015,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>ЖК "Твоя Привелегия"</t>
+          <t>Твоя Привелегия</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -11457,7 +11457,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>ЖК "Исеть Парк"</t>
+          <t>Исеть Парк</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -16907,7 +16907,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>ЖК "Космонавтов 11"</t>
+          <t>Космонавтов 11</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -22339,7 +22339,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>ЖК "Утес"</t>
+          <t>Утес</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">

--- a/budget/output/Сводный бюджет Екатеринбурга.xlsx
+++ b/budget/output/Сводный бюджет Екатеринбурга.xlsx
@@ -2657,35 +2657,35 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF(B4=0,"-",B43/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IF(C4=0,"-",C43/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IF(D4=0,"-",D43/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D43/D4),"-")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IF(E4=0,"-",E43/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E43/E4),"-")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(F4=0,"-",F43/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F43/F4),"-")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IF(G4=0,"-",G43/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IF(H4=0,"-",H43/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IF(I4=0,"-",I43/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
@@ -4507,35 +4507,35 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IF(B4=0,"-",B80/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IF(C4=0,"-",C80/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IF(D4=0,"-",D80/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D80/D4),"-")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IF(E4=0,"-",E80/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E80/E4),"-")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(F4=0,"-",F80/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F80/F4),"-")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IF(G4=0,"-",G80/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IF(H4=0,"-",H80/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IF(I4=0,"-",I80/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
@@ -4907,35 +4907,35 @@
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B80+B82-B87</f>
+        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>C80+C82-C87</f>
+        <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
         <v/>
       </c>
       <c r="D89" s="9">
-        <f>D80+D82-D87</f>
+        <f>D80+IFERROR(D82*1,0)-IFERROR(D87*1,0)</f>
         <v/>
       </c>
       <c r="E89" s="9">
-        <f>E80+E82-E87</f>
+        <f>E80+IFERROR(E82*1,0)-IFERROR(E87*1,0)</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>F80+F82-F87</f>
+        <f>F80+IFERROR(F82*1,0)-IFERROR(F87*1,0)</f>
         <v/>
       </c>
       <c r="G89" s="9">
-        <f>G80+G82-G87</f>
+        <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>H80+H82-H87</f>
+        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
         <v/>
       </c>
       <c r="I89" s="9">
-        <f>I80+I82-I87</f>
+        <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
@@ -4957,35 +4957,35 @@
         </is>
       </c>
       <c r="B90" s="10">
-        <f>IF(B4=0,"-",B89/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
         <v/>
       </c>
       <c r="C90" s="10">
-        <f>IF(C4=0,"-",C89/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
         <v/>
       </c>
       <c r="D90" s="10">
-        <f>IF(D4=0,"-",D89/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D89/D4),"-")</f>
         <v/>
       </c>
       <c r="E90" s="10">
-        <f>IF(E4=0,"-",E89/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E89/E4),"-")</f>
         <v/>
       </c>
       <c r="F90" s="10">
-        <f>IF(F4=0,"-",F89/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F89/F4),"-")</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>IF(G4=0,"-",G89/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
       <c r="H90" s="10">
-        <f>IF(H4=0,"-",H89/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
         <v/>
       </c>
       <c r="I90" s="10">
-        <f>IF(I4=0,"-",I89/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
@@ -5357,35 +5357,35 @@
         </is>
       </c>
       <c r="B98" s="9">
-        <f>B89-B91-B94-B95</f>
+        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
         <v/>
       </c>
       <c r="C98" s="9">
-        <f>C89-C91-C94-C95</f>
+        <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
         <v/>
       </c>
       <c r="D98" s="9">
-        <f>D89-D91-D94-D95</f>
+        <f>IFERROR(D89*1,0)-IFERROR(D91*1,0)-IFERROR(D94*1,0)-IFERROR(D95*1,0)</f>
         <v/>
       </c>
       <c r="E98" s="9">
-        <f>E89-E91-E94-E95</f>
+        <f>IFERROR(E89*1,0)-IFERROR(E91*1,0)-IFERROR(E94*1,0)-IFERROR(E95*1,0)</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>F89-F91-F94-F95</f>
+        <f>IFERROR(F89*1,0)-IFERROR(F91*1,0)-IFERROR(F94*1,0)-IFERROR(F95*1,0)</f>
         <v/>
       </c>
       <c r="G98" s="9">
-        <f>G89-G91-G94-G95</f>
+        <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>H89-H91-H94-H95</f>
+        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
         <v/>
       </c>
       <c r="I98" s="9">
-        <f>I89-I91-I94-I95</f>
+        <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
@@ -5407,35 +5407,35 @@
         </is>
       </c>
       <c r="B99" s="10">
-        <f>IF(B4=0,"-",B98/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
         <v/>
       </c>
       <c r="C99" s="10">
-        <f>IF(C4=0,"-",C98/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
         <v/>
       </c>
       <c r="D99" s="10">
-        <f>IF(D4=0,"-",D98/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D98/D4),"-")</f>
         <v/>
       </c>
       <c r="E99" s="10">
-        <f>IF(E4=0,"-",E98/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E98/E4),"-")</f>
         <v/>
       </c>
       <c r="F99" s="10">
-        <f>IF(F4=0,"-",F98/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F98/F4),"-")</f>
         <v/>
       </c>
       <c r="G99" s="10">
-        <f>IF(G4=0,"-",G98/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
       <c r="H99" s="10">
-        <f>IF(H4=0,"-",H98/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
         <v/>
       </c>
       <c r="I99" s="10">
-        <f>IF(I4=0,"-",I98/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>
@@ -7766,35 +7766,35 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF(B4=0,"-",B43/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IF(C4=0,"-",C43/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IF(D4=0,"-",D43/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D43/D4),"-")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IF(E4=0,"-",E43/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E43/E4),"-")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(F4=0,"-",F43/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F43/F4),"-")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IF(G4=0,"-",G43/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IF(H4=0,"-",H43/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IF(I4=0,"-",I43/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
@@ -9225,18 +9225,42 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Создано с помощью сервиса ПланФакт</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Перейти в сервис</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" s="4" t="n"/>
@@ -9830,35 +9854,35 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IF(B4=0,"-",B80/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IF(C4=0,"-",C80/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IF(D4=0,"-",D80/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D80/D4),"-")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IF(E4=0,"-",E80/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E80/E4),"-")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(F4=0,"-",F80/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F80/F4),"-")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IF(G4=0,"-",G80/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IF(H4=0,"-",H80/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IF(I4=0,"-",I80/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
@@ -10270,35 +10294,35 @@
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B80+B82-B87</f>
+        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>C80+C82-C87</f>
+        <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
         <v/>
       </c>
       <c r="D89" s="9">
-        <f>D80+D82-D87</f>
+        <f>D80+IFERROR(D82*1,0)-IFERROR(D87*1,0)</f>
         <v/>
       </c>
       <c r="E89" s="9">
-        <f>E80+E82-E87</f>
+        <f>E80+IFERROR(E82*1,0)-IFERROR(E87*1,0)</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>F80+F82-F87</f>
+        <f>F80+IFERROR(F82*1,0)-IFERROR(F87*1,0)</f>
         <v/>
       </c>
       <c r="G89" s="9">
-        <f>G80+G82-G87</f>
+        <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>H80+H82-H87</f>
+        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
         <v/>
       </c>
       <c r="I89" s="9">
-        <f>I80+I82-I87</f>
+        <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
@@ -10320,35 +10344,35 @@
         </is>
       </c>
       <c r="B90" s="10">
-        <f>IF(B4=0,"-",B89/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
         <v/>
       </c>
       <c r="C90" s="10">
-        <f>IF(C4=0,"-",C89/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
         <v/>
       </c>
       <c r="D90" s="10">
-        <f>IF(D4=0,"-",D89/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D89/D4),"-")</f>
         <v/>
       </c>
       <c r="E90" s="10">
-        <f>IF(E4=0,"-",E89/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E89/E4),"-")</f>
         <v/>
       </c>
       <c r="F90" s="10">
-        <f>IF(F4=0,"-",F89/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F89/F4),"-")</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>IF(G4=0,"-",G89/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
       <c r="H90" s="10">
-        <f>IF(H4=0,"-",H89/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
         <v/>
       </c>
       <c r="I90" s="10">
-        <f>IF(I4=0,"-",I89/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
@@ -10740,35 +10764,35 @@
         </is>
       </c>
       <c r="B98" s="9">
-        <f>B89-B91-B94-B95</f>
+        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
         <v/>
       </c>
       <c r="C98" s="9">
-        <f>C89-C91-C94-C95</f>
+        <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
         <v/>
       </c>
       <c r="D98" s="9">
-        <f>D89-D91-D94-D95</f>
+        <f>IFERROR(D89*1,0)-IFERROR(D91*1,0)-IFERROR(D94*1,0)-IFERROR(D95*1,0)</f>
         <v/>
       </c>
       <c r="E98" s="9">
-        <f>E89-E91-E94-E95</f>
+        <f>IFERROR(E89*1,0)-IFERROR(E91*1,0)-IFERROR(E94*1,0)-IFERROR(E95*1,0)</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>F89-F91-F94-F95</f>
+        <f>IFERROR(F89*1,0)-IFERROR(F91*1,0)-IFERROR(F94*1,0)-IFERROR(F95*1,0)</f>
         <v/>
       </c>
       <c r="G98" s="9">
-        <f>G89-G91-G94-G95</f>
+        <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>H89-H91-H94-H95</f>
+        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
         <v/>
       </c>
       <c r="I98" s="9">
-        <f>I89-I91-I94-I95</f>
+        <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
@@ -10790,35 +10814,35 @@
         </is>
       </c>
       <c r="B99" s="10">
-        <f>IF(B4=0,"-",B98/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
         <v/>
       </c>
       <c r="C99" s="10">
-        <f>IF(C4=0,"-",C98/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
         <v/>
       </c>
       <c r="D99" s="10">
-        <f>IF(D4=0,"-",D98/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D98/D4),"-")</f>
         <v/>
       </c>
       <c r="E99" s="10">
-        <f>IF(E4=0,"-",E98/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E98/E4),"-")</f>
         <v/>
       </c>
       <c r="F99" s="10">
-        <f>IF(F4=0,"-",F98/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F98/F4),"-")</f>
         <v/>
       </c>
       <c r="G99" s="10">
-        <f>IF(G4=0,"-",G98/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
       <c r="H99" s="10">
-        <f>IF(H4=0,"-",H98/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
         <v/>
       </c>
       <c r="I99" s="10">
-        <f>IF(I4=0,"-",I98/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>
@@ -13157,35 +13181,35 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF(B4=0,"-",B43/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IF(C4=0,"-",C43/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IF(D4=0,"-",D43/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D43/D4),"-")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IF(E4=0,"-",E43/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E43/E4),"-")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(F4=0,"-",F43/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F43/F4),"-")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IF(G4=0,"-",G43/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IF(H4=0,"-",H43/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IF(I4=0,"-",I43/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
@@ -14616,18 +14640,42 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Создано с помощью сервиса ПланФакт</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Перейти в сервис</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" s="4" t="n"/>
@@ -15221,35 +15269,35 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IF(B4=0,"-",B80/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IF(C4=0,"-",C80/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IF(D4=0,"-",D80/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D80/D4),"-")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IF(E4=0,"-",E80/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E80/E4),"-")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(F4=0,"-",F80/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F80/F4),"-")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IF(G4=0,"-",G80/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IF(H4=0,"-",H80/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IF(I4=0,"-",I80/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
@@ -15661,35 +15709,35 @@
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B80+B82-B87</f>
+        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>C80+C82-C87</f>
+        <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
         <v/>
       </c>
       <c r="D89" s="9">
-        <f>D80+D82-D87</f>
+        <f>D80+IFERROR(D82*1,0)-IFERROR(D87*1,0)</f>
         <v/>
       </c>
       <c r="E89" s="9">
-        <f>E80+E82-E87</f>
+        <f>E80+IFERROR(E82*1,0)-IFERROR(E87*1,0)</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>F80+F82-F87</f>
+        <f>F80+IFERROR(F82*1,0)-IFERROR(F87*1,0)</f>
         <v/>
       </c>
       <c r="G89" s="9">
-        <f>G80+G82-G87</f>
+        <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>H80+H82-H87</f>
+        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
         <v/>
       </c>
       <c r="I89" s="9">
-        <f>I80+I82-I87</f>
+        <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
@@ -15711,35 +15759,35 @@
         </is>
       </c>
       <c r="B90" s="10">
-        <f>IF(B4=0,"-",B89/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
         <v/>
       </c>
       <c r="C90" s="10">
-        <f>IF(C4=0,"-",C89/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
         <v/>
       </c>
       <c r="D90" s="10">
-        <f>IF(D4=0,"-",D89/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D89/D4),"-")</f>
         <v/>
       </c>
       <c r="E90" s="10">
-        <f>IF(E4=0,"-",E89/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E89/E4),"-")</f>
         <v/>
       </c>
       <c r="F90" s="10">
-        <f>IF(F4=0,"-",F89/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F89/F4),"-")</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>IF(G4=0,"-",G89/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
       <c r="H90" s="10">
-        <f>IF(H4=0,"-",H89/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
         <v/>
       </c>
       <c r="I90" s="10">
-        <f>IF(I4=0,"-",I89/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
@@ -16131,35 +16179,35 @@
         </is>
       </c>
       <c r="B98" s="9">
-        <f>B89-B91-B94-B95</f>
+        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
         <v/>
       </c>
       <c r="C98" s="9">
-        <f>C89-C91-C94-C95</f>
+        <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
         <v/>
       </c>
       <c r="D98" s="9">
-        <f>D89-D91-D94-D95</f>
+        <f>IFERROR(D89*1,0)-IFERROR(D91*1,0)-IFERROR(D94*1,0)-IFERROR(D95*1,0)</f>
         <v/>
       </c>
       <c r="E98" s="9">
-        <f>E89-E91-E94-E95</f>
+        <f>IFERROR(E89*1,0)-IFERROR(E91*1,0)-IFERROR(E94*1,0)-IFERROR(E95*1,0)</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>F89-F91-F94-F95</f>
+        <f>IFERROR(F89*1,0)-IFERROR(F91*1,0)-IFERROR(F94*1,0)-IFERROR(F95*1,0)</f>
         <v/>
       </c>
       <c r="G98" s="9">
-        <f>G89-G91-G94-G95</f>
+        <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>H89-H91-H94-H95</f>
+        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
         <v/>
       </c>
       <c r="I98" s="9">
-        <f>I89-I91-I94-I95</f>
+        <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
@@ -16181,35 +16229,35 @@
         </is>
       </c>
       <c r="B99" s="10">
-        <f>IF(B4=0,"-",B98/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
         <v/>
       </c>
       <c r="C99" s="10">
-        <f>IF(C4=0,"-",C98/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
         <v/>
       </c>
       <c r="D99" s="10">
-        <f>IF(D4=0,"-",D98/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D98/D4),"-")</f>
         <v/>
       </c>
       <c r="E99" s="10">
-        <f>IF(E4=0,"-",E98/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E98/E4),"-")</f>
         <v/>
       </c>
       <c r="F99" s="10">
-        <f>IF(F4=0,"-",F98/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F98/F4),"-")</f>
         <v/>
       </c>
       <c r="G99" s="10">
-        <f>IF(G4=0,"-",G98/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
       <c r="H99" s="10">
-        <f>IF(H4=0,"-",H98/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
         <v/>
       </c>
       <c r="I99" s="10">
-        <f>IF(I4=0,"-",I98/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>
@@ -18560,35 +18608,35 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF(B4=0,"-",B43/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IF(C4=0,"-",C43/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IF(D4=0,"-",D43/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D43/D4),"-")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IF(E4=0,"-",E43/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E43/E4),"-")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(F4=0,"-",F43/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F43/F4),"-")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IF(G4=0,"-",G43/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IF(H4=0,"-",H43/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IF(I4=0,"-",I43/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
@@ -19999,18 +20047,42 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Создано с помощью сервиса ПланФакт</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Перейти в сервис</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" s="4" t="n"/>
@@ -20604,35 +20676,35 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IF(B4=0,"-",B80/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IF(C4=0,"-",C80/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IF(D4=0,"-",D80/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D80/D4),"-")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IF(E4=0,"-",E80/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E80/E4),"-")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(F4=0,"-",F80/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F80/F4),"-")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IF(G4=0,"-",G80/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IF(H4=0,"-",H80/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IF(I4=0,"-",I80/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
@@ -21044,35 +21116,35 @@
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B80+B82-B87</f>
+        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>C80+C82-C87</f>
+        <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
         <v/>
       </c>
       <c r="D89" s="9">
-        <f>D80+D82-D87</f>
+        <f>D80+IFERROR(D82*1,0)-IFERROR(D87*1,0)</f>
         <v/>
       </c>
       <c r="E89" s="9">
-        <f>E80+E82-E87</f>
+        <f>E80+IFERROR(E82*1,0)-IFERROR(E87*1,0)</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>F80+F82-F87</f>
+        <f>F80+IFERROR(F82*1,0)-IFERROR(F87*1,0)</f>
         <v/>
       </c>
       <c r="G89" s="9">
-        <f>G80+G82-G87</f>
+        <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>H80+H82-H87</f>
+        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
         <v/>
       </c>
       <c r="I89" s="9">
-        <f>I80+I82-I87</f>
+        <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
@@ -21094,35 +21166,35 @@
         </is>
       </c>
       <c r="B90" s="10">
-        <f>IF(B4=0,"-",B89/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
         <v/>
       </c>
       <c r="C90" s="10">
-        <f>IF(C4=0,"-",C89/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
         <v/>
       </c>
       <c r="D90" s="10">
-        <f>IF(D4=0,"-",D89/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D89/D4),"-")</f>
         <v/>
       </c>
       <c r="E90" s="10">
-        <f>IF(E4=0,"-",E89/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E89/E4),"-")</f>
         <v/>
       </c>
       <c r="F90" s="10">
-        <f>IF(F4=0,"-",F89/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F89/F4),"-")</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>IF(G4=0,"-",G89/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
       <c r="H90" s="10">
-        <f>IF(H4=0,"-",H89/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
         <v/>
       </c>
       <c r="I90" s="10">
-        <f>IF(I4=0,"-",I89/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
@@ -21514,35 +21586,35 @@
         </is>
       </c>
       <c r="B98" s="9">
-        <f>B89-B91-B94-B95</f>
+        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
         <v/>
       </c>
       <c r="C98" s="9">
-        <f>C89-C91-C94-C95</f>
+        <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
         <v/>
       </c>
       <c r="D98" s="9">
-        <f>D89-D91-D94-D95</f>
+        <f>IFERROR(D89*1,0)-IFERROR(D91*1,0)-IFERROR(D94*1,0)-IFERROR(D95*1,0)</f>
         <v/>
       </c>
       <c r="E98" s="9">
-        <f>E89-E91-E94-E95</f>
+        <f>IFERROR(E89*1,0)-IFERROR(E91*1,0)-IFERROR(E94*1,0)-IFERROR(E95*1,0)</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>F89-F91-F94-F95</f>
+        <f>IFERROR(F89*1,0)-IFERROR(F91*1,0)-IFERROR(F94*1,0)-IFERROR(F95*1,0)</f>
         <v/>
       </c>
       <c r="G98" s="9">
-        <f>G89-G91-G94-G95</f>
+        <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>H89-H91-H94-H95</f>
+        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
         <v/>
       </c>
       <c r="I98" s="9">
-        <f>I89-I91-I94-I95</f>
+        <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
@@ -21564,35 +21636,35 @@
         </is>
       </c>
       <c r="B99" s="10">
-        <f>IF(B4=0,"-",B98/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
         <v/>
       </c>
       <c r="C99" s="10">
-        <f>IF(C4=0,"-",C98/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
         <v/>
       </c>
       <c r="D99" s="10">
-        <f>IF(D4=0,"-",D98/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D98/D4),"-")</f>
         <v/>
       </c>
       <c r="E99" s="10">
-        <f>IF(E4=0,"-",E98/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E98/E4),"-")</f>
         <v/>
       </c>
       <c r="F99" s="10">
-        <f>IF(F4=0,"-",F98/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F98/F4),"-")</f>
         <v/>
       </c>
       <c r="G99" s="10">
-        <f>IF(G4=0,"-",G98/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
       <c r="H99" s="10">
-        <f>IF(H4=0,"-",H98/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
         <v/>
       </c>
       <c r="I99" s="10">
-        <f>IF(I4=0,"-",I98/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>
@@ -23945,35 +24017,35 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF(B4=0,"-",B43/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IF(C4=0,"-",C43/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IF(D4=0,"-",D43/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D43/D4),"-")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IF(E4=0,"-",E43/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E43/E4),"-")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(F4=0,"-",F43/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F43/F4),"-")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IF(G4=0,"-",G43/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IF(H4=0,"-",H43/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IF(I4=0,"-",I43/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
@@ -25404,18 +25476,42 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Создано с помощью сервиса ПланФакт</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="7" t="n"/>
-      <c r="G70" s="7" t="n"/>
-      <c r="H70" s="7" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Перейти в сервис</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" s="4" t="n"/>
@@ -26009,35 +26105,35 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IF(B4=0,"-",B80/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IF(C4=0,"-",C80/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IF(D4=0,"-",D80/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D80/D4),"-")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IF(E4=0,"-",E80/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E80/E4),"-")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(F4=0,"-",F80/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F80/F4),"-")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IF(G4=0,"-",G80/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IF(H4=0,"-",H80/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IF(I4=0,"-",I80/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
@@ -26449,35 +26545,35 @@
         </is>
       </c>
       <c r="B89" s="9">
-        <f>B80+B82-B87</f>
+        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
         <v/>
       </c>
       <c r="C89" s="9">
-        <f>C80+C82-C87</f>
+        <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
         <v/>
       </c>
       <c r="D89" s="9">
-        <f>D80+D82-D87</f>
+        <f>D80+IFERROR(D82*1,0)-IFERROR(D87*1,0)</f>
         <v/>
       </c>
       <c r="E89" s="9">
-        <f>E80+E82-E87</f>
+        <f>E80+IFERROR(E82*1,0)-IFERROR(E87*1,0)</f>
         <v/>
       </c>
       <c r="F89" s="9">
-        <f>F80+F82-F87</f>
+        <f>F80+IFERROR(F82*1,0)-IFERROR(F87*1,0)</f>
         <v/>
       </c>
       <c r="G89" s="9">
-        <f>G80+G82-G87</f>
+        <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
       <c r="H89" s="9">
-        <f>H80+H82-H87</f>
+        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
         <v/>
       </c>
       <c r="I89" s="9">
-        <f>I80+I82-I87</f>
+        <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
@@ -26499,35 +26595,35 @@
         </is>
       </c>
       <c r="B90" s="10">
-        <f>IF(B4=0,"-",B89/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
         <v/>
       </c>
       <c r="C90" s="10">
-        <f>IF(C4=0,"-",C89/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
         <v/>
       </c>
       <c r="D90" s="10">
-        <f>IF(D4=0,"-",D89/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D89/D4),"-")</f>
         <v/>
       </c>
       <c r="E90" s="10">
-        <f>IF(E4=0,"-",E89/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E89/E4),"-")</f>
         <v/>
       </c>
       <c r="F90" s="10">
-        <f>IF(F4=0,"-",F89/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F89/F4),"-")</f>
         <v/>
       </c>
       <c r="G90" s="10">
-        <f>IF(G4=0,"-",G89/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
       <c r="H90" s="10">
-        <f>IF(H4=0,"-",H89/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
         <v/>
       </c>
       <c r="I90" s="10">
-        <f>IF(I4=0,"-",I89/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
@@ -26919,35 +27015,35 @@
         </is>
       </c>
       <c r="B98" s="9">
-        <f>B89-B91-B94-B95</f>
+        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
         <v/>
       </c>
       <c r="C98" s="9">
-        <f>C89-C91-C94-C95</f>
+        <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
         <v/>
       </c>
       <c r="D98" s="9">
-        <f>D89-D91-D94-D95</f>
+        <f>IFERROR(D89*1,0)-IFERROR(D91*1,0)-IFERROR(D94*1,0)-IFERROR(D95*1,0)</f>
         <v/>
       </c>
       <c r="E98" s="9">
-        <f>E89-E91-E94-E95</f>
+        <f>IFERROR(E89*1,0)-IFERROR(E91*1,0)-IFERROR(E94*1,0)-IFERROR(E95*1,0)</f>
         <v/>
       </c>
       <c r="F98" s="9">
-        <f>F89-F91-F94-F95</f>
+        <f>IFERROR(F89*1,0)-IFERROR(F91*1,0)-IFERROR(F94*1,0)-IFERROR(F95*1,0)</f>
         <v/>
       </c>
       <c r="G98" s="9">
-        <f>G89-G91-G94-G95</f>
+        <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
       <c r="H98" s="9">
-        <f>H89-H91-H94-H95</f>
+        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
         <v/>
       </c>
       <c r="I98" s="9">
-        <f>I89-I91-I94-I95</f>
+        <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
@@ -26969,35 +27065,35 @@
         </is>
       </c>
       <c r="B99" s="10">
-        <f>IF(B4=0,"-",B98/B4)</f>
+        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
         <v/>
       </c>
       <c r="C99" s="10">
-        <f>IF(C4=0,"-",C98/C4)</f>
+        <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
         <v/>
       </c>
       <c r="D99" s="10">
-        <f>IF(D4=0,"-",D98/D4)</f>
+        <f>IFERROR(IF(D4=0,"-",D98/D4),"-")</f>
         <v/>
       </c>
       <c r="E99" s="10">
-        <f>IF(E4=0,"-",E98/E4)</f>
+        <f>IFERROR(IF(E4=0,"-",E98/E4),"-")</f>
         <v/>
       </c>
       <c r="F99" s="10">
-        <f>IF(F4=0,"-",F98/F4)</f>
+        <f>IFERROR(IF(F4=0,"-",F98/F4),"-")</f>
         <v/>
       </c>
       <c r="G99" s="10">
-        <f>IF(G4=0,"-",G98/G4)</f>
+        <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
       <c r="H99" s="10">
-        <f>IF(H4=0,"-",H98/H4)</f>
+        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
         <v/>
       </c>
       <c r="I99" s="10">
-        <f>IF(I4=0,"-",I98/I4)</f>
+        <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>

--- a/budget/output/Сводный бюджет Екатеринбурга.xlsx
+++ b/budget/output/Сводный бюджет Екатеринбурга.xlsx
@@ -680,9 +680,10 @@
         <f>SUM(G5,G6)</f>
         <v/>
       </c>
-      <c r="H4" s="7">
-        <f>SUM(H5,H6)</f>
-        <v/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="7">
         <f>SUM(I5,I6)</f>
@@ -707,7 +708,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>SUM('Твоя Привелегия'!B5,'Исеть Парк'!B5,'Космонавтов 11'!B5,'Утес'!B5)</f>
+        <f>SUM(C5,D5,E5,F5)</f>
         <v/>
       </c>
       <c r="C5" s="7">
@@ -730,9 +731,10 @@
         <f>SUM('Твоя Привелегия'!G5,'Исеть Парк'!G5,'Космонавтов 11'!G5,'Утес'!G5)</f>
         <v/>
       </c>
-      <c r="H5" s="7">
-        <f>SUM('Твоя Привелегия'!H5,'Исеть Парк'!H5,'Космонавтов 11'!H5,'Утес'!H5)</f>
-        <v/>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I5" s="7">
         <f>SUM('Твоя Привелегия'!I5,'Исеть Парк'!I5,'Космонавтов 11'!I5,'Утес'!I5)</f>
@@ -780,9 +782,10 @@
         <f>SUM(G7,G8,G9)</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>SUM(H7,H8,H9)</f>
-        <v/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I6" s="7">
         <f>SUM(I7,I8,I9)</f>
@@ -807,7 +810,7 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>SUM('Твоя Привелегия'!B7,'Исеть Парк'!B7,'Космонавтов 11'!B7,'Утес'!B7)</f>
+        <f>SUM(C7,D7,E7,F7)</f>
         <v/>
       </c>
       <c r="C7" s="7">
@@ -830,9 +833,10 @@
         <f>SUM('Твоя Привелегия'!G7,'Исеть Парк'!G7,'Космонавтов 11'!G7,'Утес'!G7)</f>
         <v/>
       </c>
-      <c r="H7" s="7">
-        <f>SUM('Твоя Привелегия'!H7,'Исеть Парк'!H7,'Космонавтов 11'!H7,'Утес'!H7)</f>
-        <v/>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I7" s="7">
         <f>SUM('Твоя Привелегия'!I7,'Исеть Парк'!I7,'Космонавтов 11'!I7,'Утес'!I7)</f>
@@ -857,7 +861,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>SUM('Твоя Привелегия'!B8,'Исеть Парк'!B8,'Космонавтов 11'!B8,'Утес'!B8)</f>
+        <f>SUM(C8,D8,E8,F8)</f>
         <v/>
       </c>
       <c r="C8" s="7">
@@ -880,9 +884,10 @@
         <f>SUM('Твоя Привелегия'!G8,'Исеть Парк'!G8,'Космонавтов 11'!G8,'Утес'!G8)</f>
         <v/>
       </c>
-      <c r="H8" s="7">
-        <f>SUM('Твоя Привелегия'!H8,'Исеть Парк'!H8,'Космонавтов 11'!H8,'Утес'!H8)</f>
-        <v/>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I8" s="7">
         <f>SUM('Твоя Привелегия'!I8,'Исеть Парк'!I8,'Космонавтов 11'!I8,'Утес'!I8)</f>
@@ -907,7 +912,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>SUM('Твоя Привелегия'!B9,'Исеть Парк'!B9,'Космонавтов 11'!B9,'Утес'!B9)</f>
+        <f>SUM(C9,D9,E9,F9)</f>
         <v/>
       </c>
       <c r="C9" s="7">
@@ -930,9 +935,10 @@
         <f>SUM('Твоя Привелегия'!G9,'Исеть Парк'!G9,'Космонавтов 11'!G9,'Утес'!G9)</f>
         <v/>
       </c>
-      <c r="H9" s="7">
-        <f>SUM('Твоя Привелегия'!H9,'Исеть Парк'!H9,'Космонавтов 11'!H9,'Утес'!H9)</f>
-        <v/>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I9" s="7">
         <f>SUM('Твоя Привелегия'!I9,'Исеть Парк'!I9,'Космонавтов 11'!I9,'Утес'!I9)</f>
@@ -980,9 +986,10 @@
         <f>SUM(G11,G12,G13,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30,G31,G32,G33,G34)</f>
         <v/>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(H11,H12,H13,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30,H31,H32,H33,H34)</f>
-        <v/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7">
         <f>SUM(I11,I12,I13,I21,I22,I23,I24,I25,I26,I27,I28,I29,I30,I31,I32,I33,I34)</f>
@@ -1007,7 +1014,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>SUM('Твоя Привелегия'!B11,'Исеть Парк'!B11,'Космонавтов 11'!B11,'Утес'!B11)</f>
+        <f>SUM(C11,D11,E11,F11)</f>
         <v/>
       </c>
       <c r="C11" s="7">
@@ -1030,9 +1037,10 @@
         <f>SUM('Твоя Привелегия'!G11,'Исеть Парк'!G11,'Космонавтов 11'!G11,'Утес'!G11)</f>
         <v/>
       </c>
-      <c r="H11" s="7">
-        <f>SUM('Твоя Привелегия'!H11,'Исеть Парк'!H11,'Космонавтов 11'!H11,'Утес'!H11)</f>
-        <v/>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I11" s="7">
         <f>SUM('Твоя Привелегия'!I11,'Исеть Парк'!I11,'Космонавтов 11'!I11,'Утес'!I11)</f>
@@ -1057,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>SUM('Твоя Привелегия'!B12,'Исеть Парк'!B12,'Космонавтов 11'!B12,'Утес'!B12)</f>
+        <f>SUM(C12,D12,E12,F12)</f>
         <v/>
       </c>
       <c r="C12" s="7">
@@ -1080,9 +1088,10 @@
         <f>SUM('Твоя Привелегия'!G12,'Исеть Парк'!G12,'Космонавтов 11'!G12,'Утес'!G12)</f>
         <v/>
       </c>
-      <c r="H12" s="7">
-        <f>SUM('Твоя Привелегия'!H12,'Исеть Парк'!H12,'Космонавтов 11'!H12,'Утес'!H12)</f>
-        <v/>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I12" s="7">
         <f>SUM('Твоя Привелегия'!I12,'Исеть Парк'!I12,'Космонавтов 11'!I12,'Утес'!I12)</f>
@@ -1130,9 +1139,10 @@
         <f>SUM(G14,G15,G16,G17,G18,G19,G20)</f>
         <v/>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(H14,H15,H16,H17,H18,H19,H20)</f>
-        <v/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7">
         <f>SUM(I14,I15,I16,I17,I18,I19,I20)</f>
@@ -1157,7 +1167,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>SUM('Твоя Привелегия'!B14,'Исеть Парк'!B14,'Космонавтов 11'!B14,'Утес'!B14)</f>
+        <f>SUM(C14,D14,E14,F14)</f>
         <v/>
       </c>
       <c r="C14" s="7">
@@ -1180,9 +1190,10 @@
         <f>SUM('Твоя Привелегия'!G14,'Исеть Парк'!G14,'Космонавтов 11'!G14,'Утес'!G14)</f>
         <v/>
       </c>
-      <c r="H14" s="7">
-        <f>SUM('Твоя Привелегия'!H14,'Исеть Парк'!H14,'Космонавтов 11'!H14,'Утес'!H14)</f>
-        <v/>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I14" s="7">
         <f>SUM('Твоя Привелегия'!I14,'Исеть Парк'!I14,'Космонавтов 11'!I14,'Утес'!I14)</f>
@@ -1207,7 +1218,7 @@
         </is>
       </c>
       <c r="B15" s="7">
-        <f>SUM('Твоя Привелегия'!B15,'Исеть Парк'!B15,'Космонавтов 11'!B15,'Утес'!B15)</f>
+        <f>SUM(C15,D15,E15,F15)</f>
         <v/>
       </c>
       <c r="C15" s="7">
@@ -1230,9 +1241,10 @@
         <f>SUM('Твоя Привелегия'!G15,'Исеть Парк'!G15,'Космонавтов 11'!G15,'Утес'!G15)</f>
         <v/>
       </c>
-      <c r="H15" s="7">
-        <f>SUM('Твоя Привелегия'!H15,'Исеть Парк'!H15,'Космонавтов 11'!H15,'Утес'!H15)</f>
-        <v/>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I15" s="7">
         <f>SUM('Твоя Привелегия'!I15,'Исеть Парк'!I15,'Космонавтов 11'!I15,'Утес'!I15)</f>
@@ -1257,7 +1269,7 @@
         </is>
       </c>
       <c r="B16" s="7">
-        <f>SUM('Твоя Привелегия'!B16,'Исеть Парк'!B16,'Космонавтов 11'!B16,'Утес'!B16)</f>
+        <f>SUM(C16,D16,E16,F16)</f>
         <v/>
       </c>
       <c r="C16" s="7">
@@ -1280,9 +1292,10 @@
         <f>SUM('Твоя Привелегия'!G16,'Исеть Парк'!G16,'Космонавтов 11'!G16,'Утес'!G16)</f>
         <v/>
       </c>
-      <c r="H16" s="7">
-        <f>SUM('Твоя Привелегия'!H16,'Исеть Парк'!H16,'Космонавтов 11'!H16,'Утес'!H16)</f>
-        <v/>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I16" s="7">
         <f>SUM('Твоя Привелегия'!I16,'Исеть Парк'!I16,'Космонавтов 11'!I16,'Утес'!I16)</f>
@@ -1307,7 +1320,7 @@
         </is>
       </c>
       <c r="B17" s="7">
-        <f>SUM('Твоя Привелегия'!B17,'Исеть Парк'!B17,'Космонавтов 11'!B17,'Утес'!B17)</f>
+        <f>SUM(C17,D17,E17,F17)</f>
         <v/>
       </c>
       <c r="C17" s="7">
@@ -1330,9 +1343,10 @@
         <f>SUM('Твоя Привелегия'!G17,'Исеть Парк'!G17,'Космонавтов 11'!G17,'Утес'!G17)</f>
         <v/>
       </c>
-      <c r="H17" s="7">
-        <f>SUM('Твоя Привелегия'!H17,'Исеть Парк'!H17,'Космонавтов 11'!H17,'Утес'!H17)</f>
-        <v/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I17" s="7">
         <f>SUM('Твоя Привелегия'!I17,'Исеть Парк'!I17,'Космонавтов 11'!I17,'Утес'!I17)</f>
@@ -1357,7 +1371,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM('Твоя Привелегия'!B18,'Исеть Парк'!B18,'Космонавтов 11'!B18,'Утес'!B18)</f>
+        <f>SUM(C18,D18,E18,F18)</f>
         <v/>
       </c>
       <c r="C18" s="7">
@@ -1380,9 +1394,10 @@
         <f>SUM('Твоя Привелегия'!G18,'Исеть Парк'!G18,'Космонавтов 11'!G18,'Утес'!G18)</f>
         <v/>
       </c>
-      <c r="H18" s="7">
-        <f>SUM('Твоя Привелегия'!H18,'Исеть Парк'!H18,'Космонавтов 11'!H18,'Утес'!H18)</f>
-        <v/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I18" s="7">
         <f>SUM('Твоя Привелегия'!I18,'Исеть Парк'!I18,'Космонавтов 11'!I18,'Утес'!I18)</f>
@@ -1407,7 +1422,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM('Твоя Привелегия'!B19,'Исеть Парк'!B19,'Космонавтов 11'!B19,'Утес'!B19)</f>
+        <f>SUM(C19,D19,E19,F19)</f>
         <v/>
       </c>
       <c r="C19" s="7">
@@ -1430,9 +1445,10 @@
         <f>SUM('Твоя Привелегия'!G19,'Исеть Парк'!G19,'Космонавтов 11'!G19,'Утес'!G19)</f>
         <v/>
       </c>
-      <c r="H19" s="7">
-        <f>SUM('Твоя Привелегия'!H19,'Исеть Парк'!H19,'Космонавтов 11'!H19,'Утес'!H19)</f>
-        <v/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I19" s="7">
         <f>SUM('Твоя Привелегия'!I19,'Исеть Парк'!I19,'Космонавтов 11'!I19,'Утес'!I19)</f>
@@ -1457,7 +1473,7 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>SUM('Твоя Привелегия'!B20,'Исеть Парк'!B20,'Космонавтов 11'!B20,'Утес'!B20)</f>
+        <f>SUM(C20,D20,E20,F20)</f>
         <v/>
       </c>
       <c r="C20" s="7">
@@ -1480,9 +1496,10 @@
         <f>SUM('Твоя Привелегия'!G20,'Исеть Парк'!G20,'Космонавтов 11'!G20,'Утес'!G20)</f>
         <v/>
       </c>
-      <c r="H20" s="7">
-        <f>SUM('Твоя Привелегия'!H20,'Исеть Парк'!H20,'Космонавтов 11'!H20,'Утес'!H20)</f>
-        <v/>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I20" s="7">
         <f>SUM('Твоя Привелегия'!I20,'Исеть Парк'!I20,'Космонавтов 11'!I20,'Утес'!I20)</f>
@@ -1507,7 +1524,7 @@
         </is>
       </c>
       <c r="B21" s="7">
-        <f>SUM('Твоя Привелегия'!B21,'Исеть Парк'!B21,'Космонавтов 11'!B21,'Утес'!B21)</f>
+        <f>SUM(C21,D21,E21,F21)</f>
         <v/>
       </c>
       <c r="C21" s="7">
@@ -1530,9 +1547,10 @@
         <f>SUM('Твоя Привелегия'!G21,'Исеть Парк'!G21,'Космонавтов 11'!G21,'Утес'!G21)</f>
         <v/>
       </c>
-      <c r="H21" s="7">
-        <f>SUM('Твоя Привелегия'!H21,'Исеть Парк'!H21,'Космонавтов 11'!H21,'Утес'!H21)</f>
-        <v/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I21" s="7">
         <f>SUM('Твоя Привелегия'!I21,'Исеть Парк'!I21,'Космонавтов 11'!I21,'Утес'!I21)</f>
@@ -1557,7 +1575,7 @@
         </is>
       </c>
       <c r="B22" s="7">
-        <f>SUM('Твоя Привелегия'!B22,'Исеть Парк'!B22,'Космонавтов 11'!B22,'Утес'!B22)</f>
+        <f>SUM(C22,D22,E22,F22)</f>
         <v/>
       </c>
       <c r="C22" s="7">
@@ -1580,9 +1598,10 @@
         <f>SUM('Твоя Привелегия'!G22,'Исеть Парк'!G22,'Космонавтов 11'!G22,'Утес'!G22)</f>
         <v/>
       </c>
-      <c r="H22" s="7">
-        <f>SUM('Твоя Привелегия'!H22,'Исеть Парк'!H22,'Космонавтов 11'!H22,'Утес'!H22)</f>
-        <v/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I22" s="7">
         <f>SUM('Твоя Привелегия'!I22,'Исеть Парк'!I22,'Космонавтов 11'!I22,'Утес'!I22)</f>
@@ -1607,7 +1626,7 @@
         </is>
       </c>
       <c r="B23" s="7">
-        <f>SUM('Твоя Привелегия'!B23,'Исеть Парк'!B23,'Космонавтов 11'!B23,'Утес'!B23)</f>
+        <f>SUM(C23,D23,E23,F23)</f>
         <v/>
       </c>
       <c r="C23" s="7">
@@ -1630,9 +1649,10 @@
         <f>SUM('Твоя Привелегия'!G23,'Исеть Парк'!G23,'Космонавтов 11'!G23,'Утес'!G23)</f>
         <v/>
       </c>
-      <c r="H23" s="7">
-        <f>SUM('Твоя Привелегия'!H23,'Исеть Парк'!H23,'Космонавтов 11'!H23,'Утес'!H23)</f>
-        <v/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I23" s="7">
         <f>SUM('Твоя Привелегия'!I23,'Исеть Парк'!I23,'Космонавтов 11'!I23,'Утес'!I23)</f>
@@ -1657,7 +1677,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>SUM('Твоя Привелегия'!B24,'Исеть Парк'!B24,'Космонавтов 11'!B24,'Утес'!B24)</f>
+        <f>SUM(C24,D24,E24,F24)</f>
         <v/>
       </c>
       <c r="C24" s="7">
@@ -1680,9 +1700,10 @@
         <f>SUM('Твоя Привелегия'!G24,'Исеть Парк'!G24,'Космонавтов 11'!G24,'Утес'!G24)</f>
         <v/>
       </c>
-      <c r="H24" s="7">
-        <f>SUM('Твоя Привелегия'!H24,'Исеть Парк'!H24,'Космонавтов 11'!H24,'Утес'!H24)</f>
-        <v/>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I24" s="7">
         <f>SUM('Твоя Привелегия'!I24,'Исеть Парк'!I24,'Космонавтов 11'!I24,'Утес'!I24)</f>
@@ -1707,7 +1728,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>SUM('Твоя Привелегия'!B25,'Исеть Парк'!B25,'Космонавтов 11'!B25,'Утес'!B25)</f>
+        <f>SUM(C25,D25,E25,F25)</f>
         <v/>
       </c>
       <c r="C25" s="7">
@@ -1730,9 +1751,10 @@
         <f>SUM('Твоя Привелегия'!G25,'Исеть Парк'!G25,'Космонавтов 11'!G25,'Утес'!G25)</f>
         <v/>
       </c>
-      <c r="H25" s="7">
-        <f>SUM('Твоя Привелегия'!H25,'Исеть Парк'!H25,'Космонавтов 11'!H25,'Утес'!H25)</f>
-        <v/>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I25" s="7">
         <f>SUM('Твоя Привелегия'!I25,'Исеть Парк'!I25,'Космонавтов 11'!I25,'Утес'!I25)</f>
@@ -1757,7 +1779,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>SUM('Твоя Привелегия'!B26,'Исеть Парк'!B26,'Космонавтов 11'!B26,'Утес'!B26)</f>
+        <f>SUM(C26,D26,E26,F26)</f>
         <v/>
       </c>
       <c r="C26" s="7">
@@ -1780,9 +1802,10 @@
         <f>SUM('Твоя Привелегия'!G26,'Исеть Парк'!G26,'Космонавтов 11'!G26,'Утес'!G26)</f>
         <v/>
       </c>
-      <c r="H26" s="7">
-        <f>SUM('Твоя Привелегия'!H26,'Исеть Парк'!H26,'Космонавтов 11'!H26,'Утес'!H26)</f>
-        <v/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I26" s="7">
         <f>SUM('Твоя Привелегия'!I26,'Исеть Парк'!I26,'Космонавтов 11'!I26,'Утес'!I26)</f>
@@ -1807,7 +1830,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>SUM('Твоя Привелегия'!B27,'Исеть Парк'!B27,'Космонавтов 11'!B27,'Утес'!B27)</f>
+        <f>SUM(C27,D27,E27,F27)</f>
         <v/>
       </c>
       <c r="C27" s="7">
@@ -1830,9 +1853,10 @@
         <f>SUM('Твоя Привелегия'!G27,'Исеть Парк'!G27,'Космонавтов 11'!G27,'Утес'!G27)</f>
         <v/>
       </c>
-      <c r="H27" s="7">
-        <f>SUM('Твоя Привелегия'!H27,'Исеть Парк'!H27,'Космонавтов 11'!H27,'Утес'!H27)</f>
-        <v/>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I27" s="7">
         <f>SUM('Твоя Привелегия'!I27,'Исеть Парк'!I27,'Космонавтов 11'!I27,'Утес'!I27)</f>
@@ -1857,7 +1881,7 @@
         </is>
       </c>
       <c r="B28" s="7">
-        <f>SUM('Твоя Привелегия'!B28,'Исеть Парк'!B28,'Космонавтов 11'!B28,'Утес'!B28)</f>
+        <f>SUM(C28,D28,E28,F28)</f>
         <v/>
       </c>
       <c r="C28" s="7">
@@ -1880,9 +1904,10 @@
         <f>SUM('Твоя Привелегия'!G28,'Исеть Парк'!G28,'Космонавтов 11'!G28,'Утес'!G28)</f>
         <v/>
       </c>
-      <c r="H28" s="7">
-        <f>SUM('Твоя Привелегия'!H28,'Исеть Парк'!H28,'Космонавтов 11'!H28,'Утес'!H28)</f>
-        <v/>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I28" s="7">
         <f>SUM('Твоя Привелегия'!I28,'Исеть Парк'!I28,'Космонавтов 11'!I28,'Утес'!I28)</f>
@@ -1907,7 +1932,7 @@
         </is>
       </c>
       <c r="B29" s="7">
-        <f>SUM('Твоя Привелегия'!B29,'Исеть Парк'!B29,'Космонавтов 11'!B29,'Утес'!B29)</f>
+        <f>SUM(C29,D29,E29,F29)</f>
         <v/>
       </c>
       <c r="C29" s="7">
@@ -1930,9 +1955,10 @@
         <f>SUM('Твоя Привелегия'!G29,'Исеть Парк'!G29,'Космонавтов 11'!G29,'Утес'!G29)</f>
         <v/>
       </c>
-      <c r="H29" s="7">
-        <f>SUM('Твоя Привелегия'!H29,'Исеть Парк'!H29,'Космонавтов 11'!H29,'Утес'!H29)</f>
-        <v/>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I29" s="7">
         <f>SUM('Твоя Привелегия'!I29,'Исеть Парк'!I29,'Космонавтов 11'!I29,'Утес'!I29)</f>
@@ -1957,7 +1983,7 @@
         </is>
       </c>
       <c r="B30" s="7">
-        <f>SUM('Твоя Привелегия'!B30,'Исеть Парк'!B30,'Космонавтов 11'!B30,'Утес'!B30)</f>
+        <f>SUM(C30,D30,E30,F30)</f>
         <v/>
       </c>
       <c r="C30" s="7">
@@ -1980,9 +2006,10 @@
         <f>SUM('Твоя Привелегия'!G30,'Исеть Парк'!G30,'Космонавтов 11'!G30,'Утес'!G30)</f>
         <v/>
       </c>
-      <c r="H30" s="7">
-        <f>SUM('Твоя Привелегия'!H30,'Исеть Парк'!H30,'Космонавтов 11'!H30,'Утес'!H30)</f>
-        <v/>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I30" s="7">
         <f>SUM('Твоя Привелегия'!I30,'Исеть Парк'!I30,'Космонавтов 11'!I30,'Утес'!I30)</f>
@@ -2007,7 +2034,7 @@
         </is>
       </c>
       <c r="B31" s="7">
-        <f>SUM('Твоя Привелегия'!B31,'Исеть Парк'!B31,'Космонавтов 11'!B31,'Утес'!B31)</f>
+        <f>SUM(C31,D31,E31,F31)</f>
         <v/>
       </c>
       <c r="C31" s="7">
@@ -2030,9 +2057,10 @@
         <f>SUM('Твоя Привелегия'!G31,'Исеть Парк'!G31,'Космонавтов 11'!G31,'Утес'!G31)</f>
         <v/>
       </c>
-      <c r="H31" s="7">
-        <f>SUM('Твоя Привелегия'!H31,'Исеть Парк'!H31,'Космонавтов 11'!H31,'Утес'!H31)</f>
-        <v/>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I31" s="7">
         <f>SUM('Твоя Привелегия'!I31,'Исеть Парк'!I31,'Космонавтов 11'!I31,'Утес'!I31)</f>
@@ -2057,7 +2085,7 @@
         </is>
       </c>
       <c r="B32" s="7">
-        <f>SUM('Твоя Привелегия'!B32,'Исеть Парк'!B32,'Космонавтов 11'!B32,'Утес'!B32)</f>
+        <f>SUM(C32,D32,E32,F32)</f>
         <v/>
       </c>
       <c r="C32" s="7">
@@ -2080,9 +2108,10 @@
         <f>SUM('Твоя Привелегия'!G32,'Исеть Парк'!G32,'Космонавтов 11'!G32,'Утес'!G32)</f>
         <v/>
       </c>
-      <c r="H32" s="7">
-        <f>SUM('Твоя Привелегия'!H32,'Исеть Парк'!H32,'Космонавтов 11'!H32,'Утес'!H32)</f>
-        <v/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I32" s="7">
         <f>SUM('Твоя Привелегия'!I32,'Исеть Парк'!I32,'Космонавтов 11'!I32,'Утес'!I32)</f>
@@ -2107,7 +2136,7 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>SUM('Твоя Привелегия'!B33,'Исеть Парк'!B33,'Космонавтов 11'!B33,'Утес'!B33)</f>
+        <f>SUM(C33,D33,E33,F33)</f>
         <v/>
       </c>
       <c r="C33" s="7">
@@ -2130,9 +2159,10 @@
         <f>SUM('Твоя Привелегия'!G33,'Исеть Парк'!G33,'Космонавтов 11'!G33,'Утес'!G33)</f>
         <v/>
       </c>
-      <c r="H33" s="7">
-        <f>SUM('Твоя Привелегия'!H33,'Исеть Парк'!H33,'Космонавтов 11'!H33,'Утес'!H33)</f>
-        <v/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I33" s="7">
         <f>SUM('Твоя Привелегия'!I33,'Исеть Парк'!I33,'Космонавтов 11'!I33,'Утес'!I33)</f>
@@ -2180,9 +2210,10 @@
         <f>SUM(G35,G36,G37,G38,G39,G40,G41,G42)</f>
         <v/>
       </c>
-      <c r="H34" s="7">
-        <f>SUM(H35,H36,H37,H38,H39,H40,H41,H42)</f>
-        <v/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" s="7">
         <f>SUM(I35,I36,I37,I38,I39,I40,I41,I42)</f>
@@ -2207,7 +2238,7 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>SUM('Твоя Привелегия'!B35,'Исеть Парк'!B35,'Космонавтов 11'!B35,'Утес'!B35)</f>
+        <f>SUM(C35,D35,E35,F35)</f>
         <v/>
       </c>
       <c r="C35" s="7">
@@ -2230,9 +2261,10 @@
         <f>SUM('Твоя Привелегия'!G35,'Исеть Парк'!G35,'Космонавтов 11'!G35,'Утес'!G35)</f>
         <v/>
       </c>
-      <c r="H35" s="7">
-        <f>SUM('Твоя Привелегия'!H35,'Исеть Парк'!H35,'Космонавтов 11'!H35,'Утес'!H35)</f>
-        <v/>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I35" s="7">
         <f>SUM('Твоя Привелегия'!I35,'Исеть Парк'!I35,'Космонавтов 11'!I35,'Утес'!I35)</f>
@@ -2257,7 +2289,7 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>SUM('Твоя Привелегия'!B36,'Исеть Парк'!B36,'Космонавтов 11'!B36,'Утес'!B36)</f>
+        <f>SUM(C36,D36,E36,F36)</f>
         <v/>
       </c>
       <c r="C36" s="7">
@@ -2280,9 +2312,10 @@
         <f>SUM('Твоя Привелегия'!G36,'Исеть Парк'!G36,'Космонавтов 11'!G36,'Утес'!G36)</f>
         <v/>
       </c>
-      <c r="H36" s="7">
-        <f>SUM('Твоя Привелегия'!H36,'Исеть Парк'!H36,'Космонавтов 11'!H36,'Утес'!H36)</f>
-        <v/>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I36" s="7">
         <f>SUM('Твоя Привелегия'!I36,'Исеть Парк'!I36,'Космонавтов 11'!I36,'Утес'!I36)</f>
@@ -2307,7 +2340,7 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>SUM('Твоя Привелегия'!B37,'Исеть Парк'!B37,'Космонавтов 11'!B37,'Утес'!B37)</f>
+        <f>SUM(C37,D37,E37,F37)</f>
         <v/>
       </c>
       <c r="C37" s="7">
@@ -2330,9 +2363,10 @@
         <f>SUM('Твоя Привелегия'!G37,'Исеть Парк'!G37,'Космонавтов 11'!G37,'Утес'!G37)</f>
         <v/>
       </c>
-      <c r="H37" s="7">
-        <f>SUM('Твоя Привелегия'!H37,'Исеть Парк'!H37,'Космонавтов 11'!H37,'Утес'!H37)</f>
-        <v/>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I37" s="7">
         <f>SUM('Твоя Привелегия'!I37,'Исеть Парк'!I37,'Космонавтов 11'!I37,'Утес'!I37)</f>
@@ -2357,7 +2391,7 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>SUM('Твоя Привелегия'!B38,'Исеть Парк'!B38,'Космонавтов 11'!B38,'Утес'!B38)</f>
+        <f>SUM(C38,D38,E38,F38)</f>
         <v/>
       </c>
       <c r="C38" s="7">
@@ -2380,9 +2414,10 @@
         <f>SUM('Твоя Привелегия'!G38,'Исеть Парк'!G38,'Космонавтов 11'!G38,'Утес'!G38)</f>
         <v/>
       </c>
-      <c r="H38" s="7">
-        <f>SUM('Твоя Привелегия'!H38,'Исеть Парк'!H38,'Космонавтов 11'!H38,'Утес'!H38)</f>
-        <v/>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I38" s="7">
         <f>SUM('Твоя Привелегия'!I38,'Исеть Парк'!I38,'Космонавтов 11'!I38,'Утес'!I38)</f>
@@ -2407,7 +2442,7 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>SUM('Твоя Привелегия'!B39,'Исеть Парк'!B39,'Космонавтов 11'!B39,'Утес'!B39)</f>
+        <f>SUM(C39,D39,E39,F39)</f>
         <v/>
       </c>
       <c r="C39" s="7">
@@ -2430,9 +2465,10 @@
         <f>SUM('Твоя Привелегия'!G39,'Исеть Парк'!G39,'Космонавтов 11'!G39,'Утес'!G39)</f>
         <v/>
       </c>
-      <c r="H39" s="7">
-        <f>SUM('Твоя Привелегия'!H39,'Исеть Парк'!H39,'Космонавтов 11'!H39,'Утес'!H39)</f>
-        <v/>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I39" s="7">
         <f>SUM('Твоя Привелегия'!I39,'Исеть Парк'!I39,'Космонавтов 11'!I39,'Утес'!I39)</f>
@@ -2457,7 +2493,7 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>SUM('Твоя Привелегия'!B40,'Исеть Парк'!B40,'Космонавтов 11'!B40,'Утес'!B40)</f>
+        <f>SUM(C40,D40,E40,F40)</f>
         <v/>
       </c>
       <c r="C40" s="7">
@@ -2480,9 +2516,10 @@
         <f>SUM('Твоя Привелегия'!G40,'Исеть Парк'!G40,'Космонавтов 11'!G40,'Утес'!G40)</f>
         <v/>
       </c>
-      <c r="H40" s="7">
-        <f>SUM('Твоя Привелегия'!H40,'Исеть Парк'!H40,'Космонавтов 11'!H40,'Утес'!H40)</f>
-        <v/>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I40" s="7">
         <f>SUM('Твоя Привелегия'!I40,'Исеть Парк'!I40,'Космонавтов 11'!I40,'Утес'!I40)</f>
@@ -2507,7 +2544,7 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>SUM('Твоя Привелегия'!B41,'Исеть Парк'!B41,'Космонавтов 11'!B41,'Утес'!B41)</f>
+        <f>SUM(C41,D41,E41,F41)</f>
         <v/>
       </c>
       <c r="C41" s="7">
@@ -2530,9 +2567,10 @@
         <f>SUM('Твоя Привелегия'!G41,'Исеть Парк'!G41,'Космонавтов 11'!G41,'Утес'!G41)</f>
         <v/>
       </c>
-      <c r="H41" s="7">
-        <f>SUM('Твоя Привелегия'!H41,'Исеть Парк'!H41,'Космонавтов 11'!H41,'Утес'!H41)</f>
-        <v/>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I41" s="7">
         <f>SUM('Твоя Привелегия'!I41,'Исеть Парк'!I41,'Космонавтов 11'!I41,'Утес'!I41)</f>
@@ -2557,7 +2595,7 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>SUM('Твоя Привелегия'!B42,'Исеть Парк'!B42,'Космонавтов 11'!B42,'Утес'!B42)</f>
+        <f>SUM(C42,D42,E42,F42)</f>
         <v/>
       </c>
       <c r="C42" s="7">
@@ -2580,9 +2618,10 @@
         <f>SUM('Твоя Привелегия'!G42,'Исеть Парк'!G42,'Космонавтов 11'!G42,'Утес'!G42)</f>
         <v/>
       </c>
-      <c r="H42" s="7">
-        <f>SUM('Твоя Привелегия'!H42,'Исеть Парк'!H42,'Космонавтов 11'!H42,'Утес'!H42)</f>
-        <v/>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I42" s="7">
         <f>SUM('Твоя Привелегия'!I42,'Исеть Парк'!I42,'Космонавтов 11'!I42,'Утес'!I42)</f>
@@ -2630,9 +2669,10 @@
         <f>G4-G10</f>
         <v/>
       </c>
-      <c r="H43" s="9">
-        <f>H4-H10</f>
-        <v/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="9">
         <f>I4-I10</f>
@@ -2680,9 +2720,10 @@
         <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
-        <v/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="10">
         <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
@@ -2730,9 +2771,10 @@
         <f>SUM(G46,G47,G48,G52,G56,G57,G58,G59,G60,G63,G64,G65,G66,G67,G68,G69,G70,G71,G72,G73,G74,G75,G76,G77,G78,G79)</f>
         <v/>
       </c>
-      <c r="H45" s="7">
-        <f>SUM(H46,H47,H48,H52,H56,H57,H58,H59,H60,H63,H64,H65,H66,H67,H68,H69,H70,H71,H72,H73,H74,H75,H76,H77,H78,H79)</f>
-        <v/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="7">
         <f>SUM(I46,I47,I48,I52,I56,I57,I58,I59,I60,I63,I64,I65,I66,I67,I68,I69,I70,I71,I72,I73,I74,I75,I76,I77,I78,I79)</f>
@@ -2757,7 +2799,7 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>SUM('Твоя Привелегия'!B46,'Исеть Парк'!B46,'Космонавтов 11'!B46,'Утес'!B46)</f>
+        <f>SUM(C46,D46,E46,F46)</f>
         <v/>
       </c>
       <c r="C46" s="7">
@@ -2780,9 +2822,10 @@
         <f>SUM('Твоя Привелегия'!G46,'Исеть Парк'!G46,'Космонавтов 11'!G46,'Утес'!G46)</f>
         <v/>
       </c>
-      <c r="H46" s="7">
-        <f>SUM('Твоя Привелегия'!H46,'Исеть Парк'!H46,'Космонавтов 11'!H46,'Утес'!H46)</f>
-        <v/>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I46" s="7">
         <f>SUM('Твоя Привелегия'!I46,'Исеть Парк'!I46,'Космонавтов 11'!I46,'Утес'!I46)</f>
@@ -2807,7 +2850,7 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>SUM('Твоя Привелегия'!B47,'Исеть Парк'!B47,'Космонавтов 11'!B47,'Утес'!B47)</f>
+        <f>SUM(C47,D47,E47,F47)</f>
         <v/>
       </c>
       <c r="C47" s="7">
@@ -2830,9 +2873,10 @@
         <f>SUM('Твоя Привелегия'!G47,'Исеть Парк'!G47,'Космонавтов 11'!G47,'Утес'!G47)</f>
         <v/>
       </c>
-      <c r="H47" s="7">
-        <f>SUM('Твоя Привелегия'!H47,'Исеть Парк'!H47,'Космонавтов 11'!H47,'Утес'!H47)</f>
-        <v/>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I47" s="7">
         <f>SUM('Твоя Привелегия'!I47,'Исеть Парк'!I47,'Космонавтов 11'!I47,'Утес'!I47)</f>
@@ -2880,9 +2924,10 @@
         <f>SUM(G49,G50,G51)</f>
         <v/>
       </c>
-      <c r="H48" s="7">
-        <f>SUM(H49,H50,H51)</f>
-        <v/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="7">
         <f>SUM(I49,I50,I51)</f>
@@ -2907,7 +2952,7 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>SUM('Твоя Привелегия'!B49,'Исеть Парк'!B49,'Космонавтов 11'!B49,'Утес'!B49)</f>
+        <f>SUM(C49,D49,E49,F49)</f>
         <v/>
       </c>
       <c r="C49" s="7">
@@ -2930,9 +2975,10 @@
         <f>SUM('Твоя Привелегия'!G49,'Исеть Парк'!G49,'Космонавтов 11'!G49,'Утес'!G49)</f>
         <v/>
       </c>
-      <c r="H49" s="7">
-        <f>SUM('Твоя Привелегия'!H49,'Исеть Парк'!H49,'Космонавтов 11'!H49,'Утес'!H49)</f>
-        <v/>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I49" s="7">
         <f>SUM('Твоя Привелегия'!I49,'Исеть Парк'!I49,'Космонавтов 11'!I49,'Утес'!I49)</f>
@@ -2957,7 +3003,7 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>SUM('Твоя Привелегия'!B50,'Исеть Парк'!B50,'Космонавтов 11'!B50,'Утес'!B50)</f>
+        <f>SUM(C50,D50,E50,F50)</f>
         <v/>
       </c>
       <c r="C50" s="7">
@@ -2980,9 +3026,10 @@
         <f>SUM('Твоя Привелегия'!G50,'Исеть Парк'!G50,'Космонавтов 11'!G50,'Утес'!G50)</f>
         <v/>
       </c>
-      <c r="H50" s="7">
-        <f>SUM('Твоя Привелегия'!H50,'Исеть Парк'!H50,'Космонавтов 11'!H50,'Утес'!H50)</f>
-        <v/>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I50" s="7">
         <f>SUM('Твоя Привелегия'!I50,'Исеть Парк'!I50,'Космонавтов 11'!I50,'Утес'!I50)</f>
@@ -3007,7 +3054,7 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>SUM('Твоя Привелегия'!B51,'Исеть Парк'!B51,'Космонавтов 11'!B51,'Утес'!B51)</f>
+        <f>SUM(C51,D51,E51,F51)</f>
         <v/>
       </c>
       <c r="C51" s="7">
@@ -3030,9 +3077,10 @@
         <f>SUM('Твоя Привелегия'!G51,'Исеть Парк'!G51,'Космонавтов 11'!G51,'Утес'!G51)</f>
         <v/>
       </c>
-      <c r="H51" s="7">
-        <f>SUM('Твоя Привелегия'!H51,'Исеть Парк'!H51,'Космонавтов 11'!H51,'Утес'!H51)</f>
-        <v/>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I51" s="7">
         <f>SUM('Твоя Привелегия'!I51,'Исеть Парк'!I51,'Космонавтов 11'!I51,'Утес'!I51)</f>
@@ -3080,9 +3128,10 @@
         <f>SUM(G53,G54,G55)</f>
         <v/>
       </c>
-      <c r="H52" s="7">
-        <f>SUM(H53,H54,H55)</f>
-        <v/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="7">
         <f>SUM(I53,I54,I55)</f>
@@ -3107,7 +3156,7 @@
         </is>
       </c>
       <c r="B53" s="7">
-        <f>SUM('Твоя Привелегия'!B53,'Исеть Парк'!B53,'Космонавтов 11'!B53,'Утес'!B53)</f>
+        <f>SUM(C53,D53,E53,F53)</f>
         <v/>
       </c>
       <c r="C53" s="7">
@@ -3130,9 +3179,10 @@
         <f>SUM('Твоя Привелегия'!G53,'Исеть Парк'!G53,'Космонавтов 11'!G53,'Утес'!G53)</f>
         <v/>
       </c>
-      <c r="H53" s="7">
-        <f>SUM('Твоя Привелегия'!H53,'Исеть Парк'!H53,'Космонавтов 11'!H53,'Утес'!H53)</f>
-        <v/>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I53" s="7">
         <f>SUM('Твоя Привелегия'!I53,'Исеть Парк'!I53,'Космонавтов 11'!I53,'Утес'!I53)</f>
@@ -3157,7 +3207,7 @@
         </is>
       </c>
       <c r="B54" s="7">
-        <f>SUM('Твоя Привелегия'!B54,'Исеть Парк'!B54,'Космонавтов 11'!B54,'Утес'!B54)</f>
+        <f>SUM(C54,D54,E54,F54)</f>
         <v/>
       </c>
       <c r="C54" s="7">
@@ -3180,9 +3230,10 @@
         <f>SUM('Твоя Привелегия'!G54,'Исеть Парк'!G54,'Космонавтов 11'!G54,'Утес'!G54)</f>
         <v/>
       </c>
-      <c r="H54" s="7">
-        <f>SUM('Твоя Привелегия'!H54,'Исеть Парк'!H54,'Космонавтов 11'!H54,'Утес'!H54)</f>
-        <v/>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I54" s="7">
         <f>SUM('Твоя Привелегия'!I54,'Исеть Парк'!I54,'Космонавтов 11'!I54,'Утес'!I54)</f>
@@ -3207,7 +3258,7 @@
         </is>
       </c>
       <c r="B55" s="7">
-        <f>SUM('Твоя Привелегия'!B55,'Исеть Парк'!B55,'Космонавтов 11'!B55,'Утес'!B55)</f>
+        <f>SUM(C55,D55,E55,F55)</f>
         <v/>
       </c>
       <c r="C55" s="7">
@@ -3230,9 +3281,10 @@
         <f>SUM('Твоя Привелегия'!G55,'Исеть Парк'!G55,'Космонавтов 11'!G55,'Утес'!G55)</f>
         <v/>
       </c>
-      <c r="H55" s="7">
-        <f>SUM('Твоя Привелегия'!H55,'Исеть Парк'!H55,'Космонавтов 11'!H55,'Утес'!H55)</f>
-        <v/>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I55" s="7">
         <f>SUM('Твоя Привелегия'!I55,'Исеть Парк'!I55,'Космонавтов 11'!I55,'Утес'!I55)</f>
@@ -3257,7 +3309,7 @@
         </is>
       </c>
       <c r="B56" s="7">
-        <f>SUM('Твоя Привелегия'!B56,'Исеть Парк'!B56,'Космонавтов 11'!B56,'Утес'!B56)</f>
+        <f>SUM(C56,D56,E56,F56)</f>
         <v/>
       </c>
       <c r="C56" s="7">
@@ -3280,9 +3332,10 @@
         <f>SUM('Твоя Привелегия'!G56,'Исеть Парк'!G56,'Космонавтов 11'!G56,'Утес'!G56)</f>
         <v/>
       </c>
-      <c r="H56" s="7">
-        <f>SUM('Твоя Привелегия'!H56,'Исеть Парк'!H56,'Космонавтов 11'!H56,'Утес'!H56)</f>
-        <v/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I56" s="7">
         <f>SUM('Твоя Привелегия'!I56,'Исеть Парк'!I56,'Космонавтов 11'!I56,'Утес'!I56)</f>
@@ -3307,7 +3360,7 @@
         </is>
       </c>
       <c r="B57" s="7">
-        <f>SUM('Твоя Привелегия'!B57,'Исеть Парк'!B57,'Космонавтов 11'!B57,'Утес'!B57)</f>
+        <f>SUM(C57,D57,E57,F57)</f>
         <v/>
       </c>
       <c r="C57" s="7">
@@ -3330,9 +3383,10 @@
         <f>SUM('Твоя Привелегия'!G57,'Исеть Парк'!G57,'Космонавтов 11'!G57,'Утес'!G57)</f>
         <v/>
       </c>
-      <c r="H57" s="7">
-        <f>SUM('Твоя Привелегия'!H57,'Исеть Парк'!H57,'Космонавтов 11'!H57,'Утес'!H57)</f>
-        <v/>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I57" s="7">
         <f>SUM('Твоя Привелегия'!I57,'Исеть Парк'!I57,'Космонавтов 11'!I57,'Утес'!I57)</f>
@@ -3357,7 +3411,7 @@
         </is>
       </c>
       <c r="B58" s="7">
-        <f>SUM('Твоя Привелегия'!B58,'Исеть Парк'!B58,'Космонавтов 11'!B58,'Утес'!B58)</f>
+        <f>SUM(C58,D58,E58,F58)</f>
         <v/>
       </c>
       <c r="C58" s="7">
@@ -3380,9 +3434,10 @@
         <f>SUM('Твоя Привелегия'!G58,'Исеть Парк'!G58,'Космонавтов 11'!G58,'Утес'!G58)</f>
         <v/>
       </c>
-      <c r="H58" s="7">
-        <f>SUM('Твоя Привелегия'!H58,'Исеть Парк'!H58,'Космонавтов 11'!H58,'Утес'!H58)</f>
-        <v/>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I58" s="7">
         <f>SUM('Твоя Привелегия'!I58,'Исеть Парк'!I58,'Космонавтов 11'!I58,'Утес'!I58)</f>
@@ -3407,7 +3462,7 @@
         </is>
       </c>
       <c r="B59" s="7">
-        <f>SUM('Твоя Привелегия'!B59,'Исеть Парк'!B59,'Космонавтов 11'!B59,'Утес'!B59)</f>
+        <f>SUM(C59,D59,E59,F59)</f>
         <v/>
       </c>
       <c r="C59" s="7">
@@ -3430,9 +3485,10 @@
         <f>SUM('Твоя Привелегия'!G59,'Исеть Парк'!G59,'Космонавтов 11'!G59,'Утес'!G59)</f>
         <v/>
       </c>
-      <c r="H59" s="7">
-        <f>SUM('Твоя Привелегия'!H59,'Исеть Парк'!H59,'Космонавтов 11'!H59,'Утес'!H59)</f>
-        <v/>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I59" s="7">
         <f>SUM('Твоя Привелегия'!I59,'Исеть Парк'!I59,'Космонавтов 11'!I59,'Утес'!I59)</f>
@@ -3480,9 +3536,10 @@
         <f>SUM(G61,G62)</f>
         <v/>
       </c>
-      <c r="H60" s="7">
-        <f>SUM(H61,H62)</f>
-        <v/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="7">
         <f>SUM(I61,I62)</f>
@@ -3507,7 +3564,7 @@
         </is>
       </c>
       <c r="B61" s="7">
-        <f>SUM('Твоя Привелегия'!B61,'Исеть Парк'!B61,'Космонавтов 11'!B61,'Утес'!B61)</f>
+        <f>SUM(C61,D61,E61,F61)</f>
         <v/>
       </c>
       <c r="C61" s="7">
@@ -3530,9 +3587,10 @@
         <f>SUM('Твоя Привелегия'!G61,'Исеть Парк'!G61,'Космонавтов 11'!G61,'Утес'!G61)</f>
         <v/>
       </c>
-      <c r="H61" s="7">
-        <f>SUM('Твоя Привелегия'!H61,'Исеть Парк'!H61,'Космонавтов 11'!H61,'Утес'!H61)</f>
-        <v/>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I61" s="7">
         <f>SUM('Твоя Привелегия'!I61,'Исеть Парк'!I61,'Космонавтов 11'!I61,'Утес'!I61)</f>
@@ -3557,7 +3615,7 @@
         </is>
       </c>
       <c r="B62" s="7">
-        <f>SUM('Твоя Привелегия'!B62,'Исеть Парк'!B62,'Космонавтов 11'!B62,'Утес'!B62)</f>
+        <f>SUM(C62,D62,E62,F62)</f>
         <v/>
       </c>
       <c r="C62" s="7">
@@ -3580,9 +3638,10 @@
         <f>SUM('Твоя Привелегия'!G62,'Исеть Парк'!G62,'Космонавтов 11'!G62,'Утес'!G62)</f>
         <v/>
       </c>
-      <c r="H62" s="7">
-        <f>SUM('Твоя Привелегия'!H62,'Исеть Парк'!H62,'Космонавтов 11'!H62,'Утес'!H62)</f>
-        <v/>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I62" s="7">
         <f>SUM('Твоя Привелегия'!I62,'Исеть Парк'!I62,'Космонавтов 11'!I62,'Утес'!I62)</f>
@@ -3607,7 +3666,7 @@
         </is>
       </c>
       <c r="B63" s="7">
-        <f>SUM('Твоя Привелегия'!B63,'Исеть Парк'!B63,'Космонавтов 11'!B63,'Утес'!B63)</f>
+        <f>SUM(C63,D63,E63,F63)</f>
         <v/>
       </c>
       <c r="C63" s="7">
@@ -3630,9 +3689,10 @@
         <f>SUM('Твоя Привелегия'!G63,'Исеть Парк'!G63,'Космонавтов 11'!G63,'Утес'!G63)</f>
         <v/>
       </c>
-      <c r="H63" s="7">
-        <f>SUM('Твоя Привелегия'!H63,'Исеть Парк'!H63,'Космонавтов 11'!H63,'Утес'!H63)</f>
-        <v/>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I63" s="7">
         <f>SUM('Твоя Привелегия'!I63,'Исеть Парк'!I63,'Космонавтов 11'!I63,'Утес'!I63)</f>
@@ -3657,7 +3717,7 @@
         </is>
       </c>
       <c r="B64" s="7">
-        <f>SUM('Твоя Привелегия'!B64,'Исеть Парк'!B64,'Космонавтов 11'!B64,'Утес'!B64)</f>
+        <f>SUM(C64,D64,E64,F64)</f>
         <v/>
       </c>
       <c r="C64" s="7">
@@ -3680,9 +3740,10 @@
         <f>SUM('Твоя Привелегия'!G64,'Исеть Парк'!G64,'Космонавтов 11'!G64,'Утес'!G64)</f>
         <v/>
       </c>
-      <c r="H64" s="7">
-        <f>SUM('Твоя Привелегия'!H64,'Исеть Парк'!H64,'Космонавтов 11'!H64,'Утес'!H64)</f>
-        <v/>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I64" s="7">
         <f>SUM('Твоя Привелегия'!I64,'Исеть Парк'!I64,'Космонавтов 11'!I64,'Утес'!I64)</f>
@@ -3707,7 +3768,7 @@
         </is>
       </c>
       <c r="B65" s="7">
-        <f>SUM('Твоя Привелегия'!B65,'Исеть Парк'!B65,'Космонавтов 11'!B65,'Утес'!B65)</f>
+        <f>SUM(C65,D65,E65,F65)</f>
         <v/>
       </c>
       <c r="C65" s="7">
@@ -3730,9 +3791,10 @@
         <f>SUM('Твоя Привелегия'!G65,'Исеть Парк'!G65,'Космонавтов 11'!G65,'Утес'!G65)</f>
         <v/>
       </c>
-      <c r="H65" s="7">
-        <f>SUM('Твоя Привелегия'!H65,'Исеть Парк'!H65,'Космонавтов 11'!H65,'Утес'!H65)</f>
-        <v/>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I65" s="7">
         <f>SUM('Твоя Привелегия'!I65,'Исеть Парк'!I65,'Космонавтов 11'!I65,'Утес'!I65)</f>
@@ -3757,7 +3819,7 @@
         </is>
       </c>
       <c r="B66" s="7">
-        <f>SUM('Твоя Привелегия'!B66,'Исеть Парк'!B66,'Космонавтов 11'!B66,'Утес'!B66)</f>
+        <f>SUM(C66,D66,E66,F66)</f>
         <v/>
       </c>
       <c r="C66" s="7">
@@ -3780,9 +3842,10 @@
         <f>SUM('Твоя Привелегия'!G66,'Исеть Парк'!G66,'Космонавтов 11'!G66,'Утес'!G66)</f>
         <v/>
       </c>
-      <c r="H66" s="7">
-        <f>SUM('Твоя Привелегия'!H66,'Исеть Парк'!H66,'Космонавтов 11'!H66,'Утес'!H66)</f>
-        <v/>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I66" s="7">
         <f>SUM('Твоя Привелегия'!I66,'Исеть Парк'!I66,'Космонавтов 11'!I66,'Утес'!I66)</f>
@@ -3807,7 +3870,7 @@
         </is>
       </c>
       <c r="B67" s="7">
-        <f>SUM('Твоя Привелегия'!B67,'Исеть Парк'!B67,'Космонавтов 11'!B67,'Утес'!B67)</f>
+        <f>SUM(C67,D67,E67,F67)</f>
         <v/>
       </c>
       <c r="C67" s="7">
@@ -3830,9 +3893,10 @@
         <f>SUM('Твоя Привелегия'!G67,'Исеть Парк'!G67,'Космонавтов 11'!G67,'Утес'!G67)</f>
         <v/>
       </c>
-      <c r="H67" s="7">
-        <f>SUM('Твоя Привелегия'!H67,'Исеть Парк'!H67,'Космонавтов 11'!H67,'Утес'!H67)</f>
-        <v/>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I67" s="7">
         <f>SUM('Твоя Привелегия'!I67,'Исеть Парк'!I67,'Космонавтов 11'!I67,'Утес'!I67)</f>
@@ -3857,7 +3921,7 @@
         </is>
       </c>
       <c r="B68" s="7">
-        <f>SUM('Твоя Привелегия'!B68,'Исеть Парк'!B68,'Космонавтов 11'!B68,'Утес'!B68)</f>
+        <f>SUM(C68,D68,E68,F68)</f>
         <v/>
       </c>
       <c r="C68" s="7">
@@ -3880,9 +3944,10 @@
         <f>SUM('Твоя Привелегия'!G68,'Исеть Парк'!G68,'Космонавтов 11'!G68,'Утес'!G68)</f>
         <v/>
       </c>
-      <c r="H68" s="7">
-        <f>SUM('Твоя Привелегия'!H68,'Исеть Парк'!H68,'Космонавтов 11'!H68,'Утес'!H68)</f>
-        <v/>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I68" s="7">
         <f>SUM('Твоя Привелегия'!I68,'Исеть Парк'!I68,'Космонавтов 11'!I68,'Утес'!I68)</f>
@@ -3907,7 +3972,7 @@
         </is>
       </c>
       <c r="B69" s="7">
-        <f>SUM('Твоя Привелегия'!B69,'Исеть Парк'!B69,'Космонавтов 11'!B69,'Утес'!B69)</f>
+        <f>SUM(C69,D69,E69,F69)</f>
         <v/>
       </c>
       <c r="C69" s="7">
@@ -3930,9 +3995,10 @@
         <f>SUM('Твоя Привелегия'!G69,'Исеть Парк'!G69,'Космонавтов 11'!G69,'Утес'!G69)</f>
         <v/>
       </c>
-      <c r="H69" s="7">
-        <f>SUM('Твоя Привелегия'!H69,'Исеть Парк'!H69,'Космонавтов 11'!H69,'Утес'!H69)</f>
-        <v/>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I69" s="7">
         <f>SUM('Твоя Привелегия'!I69,'Исеть Парк'!I69,'Космонавтов 11'!I69,'Утес'!I69)</f>
@@ -3957,7 +4023,7 @@
         </is>
       </c>
       <c r="B70" s="7">
-        <f>SUM('Твоя Привелегия'!B70,'Исеть Парк'!B70,'Космонавтов 11'!B70,'Утес'!B70)</f>
+        <f>SUM(C70,D70,E70,F70)</f>
         <v/>
       </c>
       <c r="C70" s="7">
@@ -3980,9 +4046,10 @@
         <f>SUM('Твоя Привелегия'!G70,'Исеть Парк'!G70,'Космонавтов 11'!G70,'Утес'!G70)</f>
         <v/>
       </c>
-      <c r="H70" s="7">
-        <f>SUM('Твоя Привелегия'!H70,'Исеть Парк'!H70,'Космонавтов 11'!H70,'Утес'!H70)</f>
-        <v/>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I70" s="7">
         <f>SUM('Твоя Привелегия'!I70,'Исеть Парк'!I70,'Космонавтов 11'!I70,'Утес'!I70)</f>
@@ -4007,7 +4074,7 @@
         </is>
       </c>
       <c r="B71" s="7">
-        <f>SUM('Твоя Привелегия'!B71,'Исеть Парк'!B71,'Космонавтов 11'!B71,'Утес'!B71)</f>
+        <f>SUM(C71,D71,E71,F71)</f>
         <v/>
       </c>
       <c r="C71" s="7">
@@ -4030,9 +4097,10 @@
         <f>SUM('Твоя Привелегия'!G71,'Исеть Парк'!G71,'Космонавтов 11'!G71,'Утес'!G71)</f>
         <v/>
       </c>
-      <c r="H71" s="7">
-        <f>SUM('Твоя Привелегия'!H71,'Исеть Парк'!H71,'Космонавтов 11'!H71,'Утес'!H71)</f>
-        <v/>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I71" s="7">
         <f>SUM('Твоя Привелегия'!I71,'Исеть Парк'!I71,'Космонавтов 11'!I71,'Утес'!I71)</f>
@@ -4057,7 +4125,7 @@
         </is>
       </c>
       <c r="B72" s="7">
-        <f>SUM('Твоя Привелегия'!B72,'Исеть Парк'!B72,'Космонавтов 11'!B72,'Утес'!B72)</f>
+        <f>SUM(C72,D72,E72,F72)</f>
         <v/>
       </c>
       <c r="C72" s="7">
@@ -4080,9 +4148,10 @@
         <f>SUM('Твоя Привелегия'!G72,'Исеть Парк'!G72,'Космонавтов 11'!G72,'Утес'!G72)</f>
         <v/>
       </c>
-      <c r="H72" s="7">
-        <f>SUM('Твоя Привелегия'!H72,'Исеть Парк'!H72,'Космонавтов 11'!H72,'Утес'!H72)</f>
-        <v/>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I72" s="7">
         <f>SUM('Твоя Привелегия'!I72,'Исеть Парк'!I72,'Космонавтов 11'!I72,'Утес'!I72)</f>
@@ -4107,7 +4176,7 @@
         </is>
       </c>
       <c r="B73" s="7">
-        <f>SUM('Твоя Привелегия'!B73,'Исеть Парк'!B73,'Космонавтов 11'!B73,'Утес'!B73)</f>
+        <f>SUM(C73,D73,E73,F73)</f>
         <v/>
       </c>
       <c r="C73" s="7">
@@ -4130,9 +4199,10 @@
         <f>SUM('Твоя Привелегия'!G73,'Исеть Парк'!G73,'Космонавтов 11'!G73,'Утес'!G73)</f>
         <v/>
       </c>
-      <c r="H73" s="7">
-        <f>SUM('Твоя Привелегия'!H73,'Исеть Парк'!H73,'Космонавтов 11'!H73,'Утес'!H73)</f>
-        <v/>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I73" s="7">
         <f>SUM('Твоя Привелегия'!I73,'Исеть Парк'!I73,'Космонавтов 11'!I73,'Утес'!I73)</f>
@@ -4157,7 +4227,7 @@
         </is>
       </c>
       <c r="B74" s="7">
-        <f>SUM('Твоя Привелегия'!B74,'Исеть Парк'!B74,'Космонавтов 11'!B74,'Утес'!B74)</f>
+        <f>SUM(C74,D74,E74,F74)</f>
         <v/>
       </c>
       <c r="C74" s="7">
@@ -4180,9 +4250,10 @@
         <f>SUM('Твоя Привелегия'!G74,'Исеть Парк'!G74,'Космонавтов 11'!G74,'Утес'!G74)</f>
         <v/>
       </c>
-      <c r="H74" s="7">
-        <f>SUM('Твоя Привелегия'!H74,'Исеть Парк'!H74,'Космонавтов 11'!H74,'Утес'!H74)</f>
-        <v/>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I74" s="7">
         <f>SUM('Твоя Привелегия'!I74,'Исеть Парк'!I74,'Космонавтов 11'!I74,'Утес'!I74)</f>
@@ -4207,7 +4278,7 @@
         </is>
       </c>
       <c r="B75" s="7">
-        <f>SUM('Твоя Привелегия'!B75,'Исеть Парк'!B75,'Космонавтов 11'!B75,'Утес'!B75)</f>
+        <f>SUM(C75,D75,E75,F75)</f>
         <v/>
       </c>
       <c r="C75" s="7">
@@ -4230,9 +4301,10 @@
         <f>SUM('Твоя Привелегия'!G75,'Исеть Парк'!G75,'Космонавтов 11'!G75,'Утес'!G75)</f>
         <v/>
       </c>
-      <c r="H75" s="7">
-        <f>SUM('Твоя Привелегия'!H75,'Исеть Парк'!H75,'Космонавтов 11'!H75,'Утес'!H75)</f>
-        <v/>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I75" s="7">
         <f>SUM('Твоя Привелегия'!I75,'Исеть Парк'!I75,'Космонавтов 11'!I75,'Утес'!I75)</f>
@@ -4257,7 +4329,7 @@
         </is>
       </c>
       <c r="B76" s="7">
-        <f>SUM('Твоя Привелегия'!B76,'Исеть Парк'!B76,'Космонавтов 11'!B76,'Утес'!B76)</f>
+        <f>SUM(C76,D76,E76,F76)</f>
         <v/>
       </c>
       <c r="C76" s="7">
@@ -4280,9 +4352,10 @@
         <f>SUM('Твоя Привелегия'!G76,'Исеть Парк'!G76,'Космонавтов 11'!G76,'Утес'!G76)</f>
         <v/>
       </c>
-      <c r="H76" s="7">
-        <f>SUM('Твоя Привелегия'!H76,'Исеть Парк'!H76,'Космонавтов 11'!H76,'Утес'!H76)</f>
-        <v/>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I76" s="7">
         <f>SUM('Твоя Привелегия'!I76,'Исеть Парк'!I76,'Космонавтов 11'!I76,'Утес'!I76)</f>
@@ -4307,7 +4380,7 @@
         </is>
       </c>
       <c r="B77" s="7">
-        <f>SUM('Твоя Привелегия'!B77,'Исеть Парк'!B77,'Космонавтов 11'!B77,'Утес'!B77)</f>
+        <f>SUM(C77,D77,E77,F77)</f>
         <v/>
       </c>
       <c r="C77" s="7">
@@ -4330,9 +4403,10 @@
         <f>SUM('Твоя Привелегия'!G77,'Исеть Парк'!G77,'Космонавтов 11'!G77,'Утес'!G77)</f>
         <v/>
       </c>
-      <c r="H77" s="7">
-        <f>SUM('Твоя Привелегия'!H77,'Исеть Парк'!H77,'Космонавтов 11'!H77,'Утес'!H77)</f>
-        <v/>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I77" s="7">
         <f>SUM('Твоя Привелегия'!I77,'Исеть Парк'!I77,'Космонавтов 11'!I77,'Утес'!I77)</f>
@@ -4357,7 +4431,7 @@
         </is>
       </c>
       <c r="B78" s="7">
-        <f>SUM('Твоя Привелегия'!B78,'Исеть Парк'!B78,'Космонавтов 11'!B78,'Утес'!B78)</f>
+        <f>SUM(C78,D78,E78,F78)</f>
         <v/>
       </c>
       <c r="C78" s="7">
@@ -4380,9 +4454,10 @@
         <f>SUM('Твоя Привелегия'!G78,'Исеть Парк'!G78,'Космонавтов 11'!G78,'Утес'!G78)</f>
         <v/>
       </c>
-      <c r="H78" s="7">
-        <f>SUM('Твоя Привелегия'!H78,'Исеть Парк'!H78,'Космонавтов 11'!H78,'Утес'!H78)</f>
-        <v/>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I78" s="7">
         <f>SUM('Твоя Привелегия'!I78,'Исеть Парк'!I78,'Космонавтов 11'!I78,'Утес'!I78)</f>
@@ -4407,7 +4482,7 @@
         </is>
       </c>
       <c r="B79" s="7">
-        <f>SUM('Твоя Привелегия'!B79,'Исеть Парк'!B79,'Космонавтов 11'!B79,'Утес'!B79)</f>
+        <f>SUM(C79,D79,E79,F79)</f>
         <v/>
       </c>
       <c r="C79" s="7">
@@ -4430,9 +4505,10 @@
         <f>SUM('Твоя Привелегия'!G79,'Исеть Парк'!G79,'Космонавтов 11'!G79,'Утес'!G79)</f>
         <v/>
       </c>
-      <c r="H79" s="7">
-        <f>SUM('Твоя Привелегия'!H79,'Исеть Парк'!H79,'Космонавтов 11'!H79,'Утес'!H79)</f>
-        <v/>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I79" s="7">
         <f>SUM('Твоя Привелегия'!I79,'Исеть Парк'!I79,'Космонавтов 11'!I79,'Утес'!I79)</f>
@@ -4480,9 +4556,10 @@
         <f>G43-G45</f>
         <v/>
       </c>
-      <c r="H80" s="9">
-        <f>H43-H45</f>
-        <v/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" s="9">
         <f>I43-I45</f>
@@ -4530,9 +4607,10 @@
         <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
-      <c r="H81" s="10">
-        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
-        <v/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" s="10">
         <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
@@ -4580,9 +4658,10 @@
         <f>SUM(G83,G84,G85,G86)</f>
         <v/>
       </c>
-      <c r="H82" s="7">
-        <f>SUM(H83,H84,H85,H86)</f>
-        <v/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" s="7">
         <f>SUM(I83,I84,I85,I86)</f>
@@ -4607,7 +4686,7 @@
         </is>
       </c>
       <c r="B83" s="7">
-        <f>SUM('Твоя Привелегия'!B83,'Исеть Парк'!B83,'Космонавтов 11'!B83,'Утес'!B83)</f>
+        <f>SUM(C83,D83,E83,F83)</f>
         <v/>
       </c>
       <c r="C83" s="7">
@@ -4630,9 +4709,10 @@
         <f>SUM('Твоя Привелегия'!G83,'Исеть Парк'!G83,'Космонавтов 11'!G83,'Утес'!G83)</f>
         <v/>
       </c>
-      <c r="H83" s="7">
-        <f>SUM('Твоя Привелегия'!H83,'Исеть Парк'!H83,'Космонавтов 11'!H83,'Утес'!H83)</f>
-        <v/>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I83" s="7">
         <f>SUM('Твоя Привелегия'!I83,'Исеть Парк'!I83,'Космонавтов 11'!I83,'Утес'!I83)</f>
@@ -4657,7 +4737,7 @@
         </is>
       </c>
       <c r="B84" s="7">
-        <f>SUM('Твоя Привелегия'!B84,'Исеть Парк'!B84,'Космонавтов 11'!B84,'Утес'!B84)</f>
+        <f>SUM(C84,D84,E84,F84)</f>
         <v/>
       </c>
       <c r="C84" s="7">
@@ -4680,9 +4760,10 @@
         <f>SUM('Твоя Привелегия'!G84,'Исеть Парк'!G84,'Космонавтов 11'!G84,'Утес'!G84)</f>
         <v/>
       </c>
-      <c r="H84" s="7">
-        <f>SUM('Твоя Привелегия'!H84,'Исеть Парк'!H84,'Космонавтов 11'!H84,'Утес'!H84)</f>
-        <v/>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I84" s="7">
         <f>SUM('Твоя Привелегия'!I84,'Исеть Парк'!I84,'Космонавтов 11'!I84,'Утес'!I84)</f>
@@ -4707,7 +4788,7 @@
         </is>
       </c>
       <c r="B85" s="7">
-        <f>SUM('Твоя Привелегия'!B85,'Исеть Парк'!B85,'Космонавтов 11'!B85,'Утес'!B85)</f>
+        <f>SUM(C85,D85,E85,F85)</f>
         <v/>
       </c>
       <c r="C85" s="7">
@@ -4730,9 +4811,10 @@
         <f>SUM('Твоя Привелегия'!G85,'Исеть Парк'!G85,'Космонавтов 11'!G85,'Утес'!G85)</f>
         <v/>
       </c>
-      <c r="H85" s="7">
-        <f>SUM('Твоя Привелегия'!H85,'Исеть Парк'!H85,'Космонавтов 11'!H85,'Утес'!H85)</f>
-        <v/>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I85" s="7">
         <f>SUM('Твоя Привелегия'!I85,'Исеть Парк'!I85,'Космонавтов 11'!I85,'Утес'!I85)</f>
@@ -4757,7 +4839,7 @@
         </is>
       </c>
       <c r="B86" s="7">
-        <f>SUM('Твоя Привелегия'!B86,'Исеть Парк'!B86,'Космонавтов 11'!B86,'Утес'!B86)</f>
+        <f>SUM(C86,D86,E86,F86)</f>
         <v/>
       </c>
       <c r="C86" s="7">
@@ -4780,9 +4862,10 @@
         <f>SUM('Твоя Привелегия'!G86,'Исеть Парк'!G86,'Космонавтов 11'!G86,'Утес'!G86)</f>
         <v/>
       </c>
-      <c r="H86" s="7">
-        <f>SUM('Твоя Привелегия'!H86,'Исеть Парк'!H86,'Космонавтов 11'!H86,'Утес'!H86)</f>
-        <v/>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I86" s="7">
         <f>SUM('Твоя Привелегия'!I86,'Исеть Парк'!I86,'Космонавтов 11'!I86,'Утес'!I86)</f>
@@ -4830,9 +4913,10 @@
         <f>SUM(G88)</f>
         <v/>
       </c>
-      <c r="H87" s="7">
-        <f>SUM(H88)</f>
-        <v/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="7">
         <f>SUM(I88)</f>
@@ -4857,7 +4941,7 @@
         </is>
       </c>
       <c r="B88" s="7">
-        <f>SUM('Твоя Привелегия'!B88,'Исеть Парк'!B88,'Космонавтов 11'!B88,'Утес'!B88)</f>
+        <f>SUM(C88,D88,E88,F88)</f>
         <v/>
       </c>
       <c r="C88" s="7">
@@ -4880,9 +4964,10 @@
         <f>SUM('Твоя Привелегия'!G88,'Исеть Парк'!G88,'Космонавтов 11'!G88,'Утес'!G88)</f>
         <v/>
       </c>
-      <c r="H88" s="7">
-        <f>SUM('Твоя Привелегия'!H88,'Исеть Парк'!H88,'Космонавтов 11'!H88,'Утес'!H88)</f>
-        <v/>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I88" s="7">
         <f>SUM('Твоя Привелегия'!I88,'Исеть Парк'!I88,'Космонавтов 11'!I88,'Утес'!I88)</f>
@@ -4930,9 +5015,10 @@
         <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
-        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
-        <v/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="9">
         <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
@@ -4980,9 +5066,10 @@
         <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
-      <c r="H90" s="10">
-        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
-        <v/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I90" s="10">
         <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
@@ -5030,9 +5117,10 @@
         <f>SUM(G92,G93)</f>
         <v/>
       </c>
-      <c r="H91" s="7">
-        <f>SUM(H92,H93)</f>
-        <v/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I91" s="7">
         <f>SUM(I92,I93)</f>
@@ -5057,7 +5145,7 @@
         </is>
       </c>
       <c r="B92" s="7">
-        <f>SUM('Твоя Привелегия'!B92,'Исеть Парк'!B92,'Космонавтов 11'!B92,'Утес'!B92)</f>
+        <f>SUM(C92,D92,E92,F92)</f>
         <v/>
       </c>
       <c r="C92" s="7">
@@ -5080,9 +5168,10 @@
         <f>SUM('Твоя Привелегия'!G92,'Исеть Парк'!G92,'Космонавтов 11'!G92,'Утес'!G92)</f>
         <v/>
       </c>
-      <c r="H92" s="7">
-        <f>SUM('Твоя Привелегия'!H92,'Исеть Парк'!H92,'Космонавтов 11'!H92,'Утес'!H92)</f>
-        <v/>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I92" s="7">
         <f>SUM('Твоя Привелегия'!I92,'Исеть Парк'!I92,'Космонавтов 11'!I92,'Утес'!I92)</f>
@@ -5107,7 +5196,7 @@
         </is>
       </c>
       <c r="B93" s="7">
-        <f>SUM('Твоя Привелегия'!B93,'Исеть Парк'!B93,'Космонавтов 11'!B93,'Утес'!B93)</f>
+        <f>SUM(C93,D93,E93,F93)</f>
         <v/>
       </c>
       <c r="C93" s="7">
@@ -5130,9 +5219,10 @@
         <f>SUM('Твоя Привелегия'!G93,'Исеть Парк'!G93,'Космонавтов 11'!G93,'Утес'!G93)</f>
         <v/>
       </c>
-      <c r="H93" s="7">
-        <f>SUM('Твоя Привелегия'!H93,'Исеть Парк'!H93,'Космонавтов 11'!H93,'Утес'!H93)</f>
-        <v/>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I93" s="7">
         <f>SUM('Твоя Привелегия'!I93,'Исеть Парк'!I93,'Космонавтов 11'!I93,'Утес'!I93)</f>
@@ -5157,7 +5247,7 @@
         </is>
       </c>
       <c r="B94" s="7">
-        <f>SUM('Твоя Привелегия'!B94,'Исеть Парк'!B94,'Космонавтов 11'!B94,'Утес'!B94)</f>
+        <f>SUM(C94,D94,E94,F94)</f>
         <v/>
       </c>
       <c r="C94" s="7">
@@ -5180,9 +5270,10 @@
         <f>SUM('Твоя Привелегия'!G94,'Исеть Парк'!G94,'Космонавтов 11'!G94,'Утес'!G94)</f>
         <v/>
       </c>
-      <c r="H94" s="7">
-        <f>SUM('Твоя Привелегия'!H94,'Исеть Парк'!H94,'Космонавтов 11'!H94,'Утес'!H94)</f>
-        <v/>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I94" s="7">
         <f>SUM('Твоя Привелегия'!I94,'Исеть Парк'!I94,'Космонавтов 11'!I94,'Утес'!I94)</f>
@@ -5230,9 +5321,10 @@
         <f>SUM(G96,G97)</f>
         <v/>
       </c>
-      <c r="H95" s="7">
-        <f>SUM(H96,H97)</f>
-        <v/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="7">
         <f>SUM(I96,I97)</f>
@@ -5257,7 +5349,7 @@
         </is>
       </c>
       <c r="B96" s="7">
-        <f>SUM('Твоя Привелегия'!B96,'Исеть Парк'!B96,'Космонавтов 11'!B96,'Утес'!B96)</f>
+        <f>SUM(C96,D96,E96,F96)</f>
         <v/>
       </c>
       <c r="C96" s="7">
@@ -5280,9 +5372,10 @@
         <f>SUM('Твоя Привелегия'!G96,'Исеть Парк'!G96,'Космонавтов 11'!G96,'Утес'!G96)</f>
         <v/>
       </c>
-      <c r="H96" s="7">
-        <f>SUM('Твоя Привелегия'!H96,'Исеть Парк'!H96,'Космонавтов 11'!H96,'Утес'!H96)</f>
-        <v/>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I96" s="7">
         <f>SUM('Твоя Привелегия'!I96,'Исеть Парк'!I96,'Космонавтов 11'!I96,'Утес'!I96)</f>
@@ -5307,7 +5400,7 @@
         </is>
       </c>
       <c r="B97" s="7">
-        <f>SUM('Твоя Привелегия'!B97,'Исеть Парк'!B97,'Космонавтов 11'!B97,'Утес'!B97)</f>
+        <f>SUM(C97,D97,E97,F97)</f>
         <v/>
       </c>
       <c r="C97" s="7">
@@ -5330,9 +5423,10 @@
         <f>SUM('Твоя Привелегия'!G97,'Исеть Парк'!G97,'Космонавтов 11'!G97,'Утес'!G97)</f>
         <v/>
       </c>
-      <c r="H97" s="7">
-        <f>SUM('Твоя Привелегия'!H97,'Исеть Парк'!H97,'Космонавтов 11'!H97,'Утес'!H97)</f>
-        <v/>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I97" s="7">
         <f>SUM('Твоя Привелегия'!I97,'Исеть Парк'!I97,'Космонавтов 11'!I97,'Утес'!I97)</f>
@@ -5380,9 +5474,10 @@
         <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
-      <c r="H98" s="9">
-        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
-        <v/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="9">
         <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
@@ -5430,9 +5525,10 @@
         <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
-      <c r="H99" s="10">
-        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
-        <v/>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="10">
         <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
@@ -5639,9 +5735,10 @@
         <f>SUM(G5,G6)</f>
         <v/>
       </c>
-      <c r="H4" s="7">
-        <f>SUM(H5,H6)</f>
-        <v/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="7">
         <f>SUM(I5,I6)</f>
@@ -5665,10 +5762,9 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="7">
+        <f>SUM(C5,D5,E5,F5)</f>
+        <v/>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -5747,9 +5843,10 @@
         <f>SUM(G7,G8,G9)</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>SUM(H7,H8,H9)</f>
-        <v/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I6" s="7">
         <f>SUM(I7,I8,I9)</f>
@@ -5773,8 +5870,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>3590716.24</v>
+      <c r="B7" s="7">
+        <f>SUM(C7,D7,E7,F7)</f>
+        <v/>
       </c>
       <c r="C7" s="7" t="n">
         <v>897679.0600000001</v>
@@ -5821,10 +5919,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="7">
+        <f>SUM(C8,D8,E8,F8)</f>
+        <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -5879,10 +5976,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="7">
+        <f>SUM(C9,D9,E9,F9)</f>
+        <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -5961,9 +6057,10 @@
         <f>SUM(G11,G12,G13,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30,G31,G32,G33,G34)</f>
         <v/>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(H11,H12,H13,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30,H31,H32,H33,H34)</f>
-        <v/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7">
         <f>SUM(I11,I12,I13,I21,I22,I23,I24,I25,I26,I27,I28,I29,I30,I31,I32,I33,I34)</f>
@@ -5987,10 +6084,9 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="7">
+        <f>SUM(C11,D11,E11,F11)</f>
+        <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -6045,8 +6141,9 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
-        <v>1080</v>
+      <c r="B12" s="7">
+        <f>SUM(C12,D12,E12,F12)</f>
+        <v/>
       </c>
       <c r="C12" s="7" t="n">
         <v>1080</v>
@@ -6123,9 +6220,10 @@
         <f>SUM(G14,G15,G16,G17,G18,G19,G20)</f>
         <v/>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(H14,H15,H16,H17,H18,H19,H20)</f>
-        <v/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7">
         <f>SUM(I14,I15,I16,I17,I18,I19,I20)</f>
@@ -6149,10 +6247,9 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="7">
+        <f>SUM(C14,D14,E14,F14)</f>
+        <v/>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -6207,8 +6304,9 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
-        <v>184000</v>
+      <c r="B15" s="7">
+        <f>SUM(C15,D15,E15,F15)</f>
+        <v/>
       </c>
       <c r="C15" s="7" t="n">
         <v>46000</v>
@@ -6255,8 +6353,9 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
-        <v>18000</v>
+      <c r="B16" s="7">
+        <f>SUM(C16,D16,E16,F16)</f>
+        <v/>
       </c>
       <c r="C16" s="7" t="n">
         <v>18000</v>
@@ -6309,8 +6408,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>32095</v>
+      <c r="B17" s="7">
+        <f>SUM(C17,D17,E17,F17)</f>
+        <v/>
       </c>
       <c r="C17" s="7" t="n">
         <v>2095</v>
@@ -6357,8 +6457,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>35435.5</v>
+      <c r="B18" s="7">
+        <f>SUM(C18,D18,E18,F18)</f>
+        <v/>
       </c>
       <c r="C18" s="7" t="n">
         <v>5435.5</v>
@@ -6405,10 +6506,9 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B19" s="7">
+        <f>SUM(C19,D19,E19,F19)</f>
+        <v/>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -6463,10 +6563,9 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="7">
+        <f>SUM(C20,D20,E20,F20)</f>
+        <v/>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -6521,8 +6620,9 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>1040000</v>
+      <c r="B21" s="7">
+        <f>SUM(C21,D21,E21,F21)</f>
+        <v/>
       </c>
       <c r="C21" s="7" t="n">
         <v>260000</v>
@@ -6569,8 +6669,9 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>777600</v>
+      <c r="B22" s="7">
+        <f>SUM(C22,D22,E22,F22)</f>
+        <v/>
       </c>
       <c r="C22" s="7" t="n">
         <v>194400</v>
@@ -6617,10 +6718,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="7">
+        <f>SUM(C23,D23,E23,F23)</f>
+        <v/>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -6675,10 +6775,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="7">
+        <f>SUM(C24,D24,E24,F24)</f>
+        <v/>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -6733,8 +6832,9 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
-        <v>10000</v>
+      <c r="B25" s="7">
+        <f>SUM(C25,D25,E25,F25)</f>
+        <v/>
       </c>
       <c r="C25" s="7" t="n">
         <v>10000</v>
@@ -6787,10 +6887,9 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="7">
+        <f>SUM(C26,D26,E26,F26)</f>
+        <v/>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -6845,10 +6944,9 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="7">
+        <f>SUM(C27,D27,E27,F27)</f>
+        <v/>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -6903,10 +7001,9 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="7">
+        <f>SUM(C28,D28,E28,F28)</f>
+        <v/>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -6961,10 +7058,9 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="7">
+        <f>SUM(C29,D29,E29,F29)</f>
+        <v/>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -7019,10 +7115,9 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="7">
+        <f>SUM(C30,D30,E30,F30)</f>
+        <v/>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -7077,10 +7172,9 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="7">
+        <f>SUM(C31,D31,E31,F31)</f>
+        <v/>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -7135,10 +7229,9 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="7">
+        <f>SUM(C32,D32,E32,F32)</f>
+        <v/>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -7193,10 +7286,9 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B33" s="7">
+        <f>SUM(C33,D33,E33,F33)</f>
+        <v/>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -7275,9 +7367,10 @@
         <f>SUM(G35,G36,G37,G38,G39,G40,G41,G42)</f>
         <v/>
       </c>
-      <c r="H34" s="7">
-        <f>SUM(H35,H36,H37,H38,H39,H40,H41,H42)</f>
-        <v/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" s="7">
         <f>SUM(I35,I36,I37,I38,I39,I40,I41,I42)</f>
@@ -7301,8 +7394,9 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n">
-        <v>10000</v>
+      <c r="B35" s="7">
+        <f>SUM(C35,D35,E35,F35)</f>
+        <v/>
       </c>
       <c r="C35" s="7" t="n">
         <v>2500</v>
@@ -7349,8 +7443,9 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>260000</v>
+      <c r="B36" s="7">
+        <f>SUM(C36,D36,E36,F36)</f>
+        <v/>
       </c>
       <c r="C36" s="7" t="n">
         <v>65000</v>
@@ -7397,8 +7492,9 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
-        <v>26123.5</v>
+      <c r="B37" s="7">
+        <f>SUM(C37,D37,E37,F37)</f>
+        <v/>
       </c>
       <c r="C37" s="7" t="n">
         <v>5123.5</v>
@@ -7445,10 +7541,9 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="7">
+        <f>SUM(C38,D38,E38,F38)</f>
+        <v/>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -7503,8 +7598,9 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
-        <v>224000</v>
+      <c r="B39" s="7">
+        <f>SUM(C39,D39,E39,F39)</f>
+        <v/>
       </c>
       <c r="C39" s="7" t="n">
         <v>56000</v>
@@ -7551,10 +7647,9 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="7">
+        <f>SUM(C40,D40,E40,F40)</f>
+        <v/>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -7609,8 +7704,9 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n">
-        <v>4000</v>
+      <c r="B41" s="7">
+        <f>SUM(C41,D41,E41,F41)</f>
+        <v/>
       </c>
       <c r="C41" s="7" t="n">
         <v>1000</v>
@@ -7657,10 +7753,9 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="7">
+        <f>SUM(C42,D42,E42,F42)</f>
+        <v/>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -7739,9 +7834,10 @@
         <f>G4-G10</f>
         <v/>
       </c>
-      <c r="H43" s="9">
-        <f>H4-H10</f>
-        <v/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="9">
         <f>I4-I10</f>
@@ -7789,9 +7885,10 @@
         <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
-        <v/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="10">
         <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
@@ -7839,9 +7936,10 @@
         <f>SUM(G46,G47,G48,G52,G56,G57,G58,G59,G60,G63,G64,G65,G66,G67,G68,G69,G70,G71,G72,G73,G74,G75,G76,G77,G78,G79)</f>
         <v/>
       </c>
-      <c r="H45" s="7">
-        <f>SUM(H46,H47,H48,H52,H56,H57,H58,H59,H60,H63,H64,H65,H66,H67,H68,H69,H70,H71,H72,H73,H74,H75,H76,H77,H78,H79)</f>
-        <v/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="7">
         <f>SUM(I46,I47,I48,I52,I56,I57,I58,I59,I60,I63,I64,I65,I66,I67,I68,I69,I70,I71,I72,I73,I74,I75,I76,I77,I78,I79)</f>
@@ -7865,8 +7963,9 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7" t="n">
-        <v>269881.08</v>
+      <c r="B46" s="7">
+        <f>SUM(C46,D46,E46,F46)</f>
+        <v/>
       </c>
       <c r="C46" s="7" t="n">
         <v>67470.27</v>
@@ -7913,10 +8012,9 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="7">
+        <f>SUM(C47,D47,E47,F47)</f>
+        <v/>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -7995,9 +8093,10 @@
         <f>SUM(G49,G50,G51)</f>
         <v/>
       </c>
-      <c r="H48" s="7">
-        <f>SUM(H49,H50,H51)</f>
-        <v/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="7">
         <f>SUM(I49,I50,I51)</f>
@@ -8021,10 +8120,9 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="7">
+        <f>SUM(C49,D49,E49,F49)</f>
+        <v/>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -8079,10 +8177,9 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="7">
+        <f>SUM(C50,D50,E50,F50)</f>
+        <v/>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -8137,10 +8234,9 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="7">
+        <f>SUM(C51,D51,E51,F51)</f>
+        <v/>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -8219,9 +8315,10 @@
         <f>SUM(G53,G54,G55)</f>
         <v/>
       </c>
-      <c r="H52" s="7">
-        <f>SUM(H53,H54,H55)</f>
-        <v/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="7">
         <f>SUM(I53,I54,I55)</f>
@@ -8245,10 +8342,9 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="7">
+        <f>SUM(C53,D53,E53,F53)</f>
+        <v/>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -8303,10 +8399,9 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="7">
+        <f>SUM(C54,D54,E54,F54)</f>
+        <v/>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -8361,10 +8456,9 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B55" s="7">
+        <f>SUM(C55,D55,E55,F55)</f>
+        <v/>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -8419,10 +8513,9 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="7">
+        <f>SUM(C56,D56,E56,F56)</f>
+        <v/>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -8477,10 +8570,9 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="7">
+        <f>SUM(C57,D57,E57,F57)</f>
+        <v/>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -8535,10 +8627,9 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="7">
+        <f>SUM(C58,D58,E58,F58)</f>
+        <v/>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -8593,10 +8684,9 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="7">
+        <f>SUM(C59,D59,E59,F59)</f>
+        <v/>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -8675,9 +8765,10 @@
         <f>SUM(G61,G62)</f>
         <v/>
       </c>
-      <c r="H60" s="7">
-        <f>SUM(H61,H62)</f>
-        <v/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="7">
         <f>SUM(I61,I62)</f>
@@ -8701,10 +8792,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="7">
+        <f>SUM(C61,D61,E61,F61)</f>
+        <v/>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -8759,10 +8849,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="7">
+        <f>SUM(C62,D62,E62,F62)</f>
+        <v/>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -8817,10 +8906,9 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="7">
+        <f>SUM(C63,D63,E63,F63)</f>
+        <v/>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -8875,10 +8963,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="7">
+        <f>SUM(C64,D64,E64,F64)</f>
+        <v/>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -8933,10 +9020,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="7">
+        <f>SUM(C65,D65,E65,F65)</f>
+        <v/>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -8991,10 +9077,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="7">
+        <f>SUM(C66,D66,E66,F66)</f>
+        <v/>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -9049,10 +9134,9 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="7">
+        <f>SUM(C67,D67,E67,F67)</f>
+        <v/>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -9107,10 +9191,9 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="7">
+        <f>SUM(C68,D68,E68,F68)</f>
+        <v/>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -9165,10 +9248,9 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="7">
+        <f>SUM(C69,D69,E69,F69)</f>
+        <v/>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -9223,10 +9305,9 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="7">
+        <f>SUM(C70,D70,E70,F70)</f>
+        <v/>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -9281,10 +9362,9 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="7">
+        <f>SUM(C71,D71,E71,F71)</f>
+        <v/>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -9339,10 +9419,9 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="7">
+        <f>SUM(C72,D72,E72,F72)</f>
+        <v/>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -9397,10 +9476,9 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="7">
+        <f>SUM(C73,D73,E73,F73)</f>
+        <v/>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -9455,10 +9533,9 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="7">
+        <f>SUM(C74,D74,E74,F74)</f>
+        <v/>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -9513,10 +9590,9 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="7">
+        <f>SUM(C75,D75,E75,F75)</f>
+        <v/>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -9571,10 +9647,9 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="7">
+        <f>SUM(C76,D76,E76,F76)</f>
+        <v/>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -9629,10 +9704,9 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="7">
+        <f>SUM(C77,D77,E77,F77)</f>
+        <v/>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -9687,10 +9761,9 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="7">
+        <f>SUM(C78,D78,E78,F78)</f>
+        <v/>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -9745,10 +9818,9 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="7">
+        <f>SUM(C79,D79,E79,F79)</f>
+        <v/>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -9827,9 +9899,10 @@
         <f>G43-G45</f>
         <v/>
       </c>
-      <c r="H80" s="9">
-        <f>H43-H45</f>
-        <v/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" s="9">
         <f>I43-I45</f>
@@ -9877,9 +9950,10 @@
         <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
-      <c r="H81" s="10">
-        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
-        <v/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" s="10">
         <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
@@ -9927,9 +10001,10 @@
         <f>SUM(G83,G84,G85,G86)</f>
         <v/>
       </c>
-      <c r="H82" s="7">
-        <f>SUM(H83,H84,H85,H86)</f>
-        <v/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" s="7">
         <f>SUM(I83,I84,I85,I86)</f>
@@ -9953,10 +10028,9 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="7">
+        <f>SUM(C83,D83,E83,F83)</f>
+        <v/>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -10011,10 +10085,9 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="7">
+        <f>SUM(C84,D84,E84,F84)</f>
+        <v/>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -10069,10 +10142,9 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="7">
+        <f>SUM(C85,D85,E85,F85)</f>
+        <v/>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -10127,10 +10199,9 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="7">
+        <f>SUM(C86,D86,E86,F86)</f>
+        <v/>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -10209,9 +10280,10 @@
         <f>SUM(G88)</f>
         <v/>
       </c>
-      <c r="H87" s="7">
-        <f>SUM(H88)</f>
-        <v/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="7">
         <f>SUM(I88)</f>
@@ -10235,10 +10307,9 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="7">
+        <f>SUM(C88,D88,E88,F88)</f>
+        <v/>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -10317,9 +10388,10 @@
         <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
-        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
-        <v/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="9">
         <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
@@ -10367,9 +10439,10 @@
         <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
-      <c r="H90" s="10">
-        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
-        <v/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I90" s="10">
         <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
@@ -10417,9 +10490,10 @@
         <f>SUM(G92,G93)</f>
         <v/>
       </c>
-      <c r="H91" s="7">
-        <f>SUM(H92,H93)</f>
-        <v/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I91" s="7">
         <f>SUM(I92,I93)</f>
@@ -10443,10 +10517,9 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="7">
+        <f>SUM(C92,D92,E92,F92)</f>
+        <v/>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -10501,10 +10574,9 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="7">
+        <f>SUM(C93,D93,E93,F93)</f>
+        <v/>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -10559,10 +10631,9 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="7">
+        <f>SUM(C94,D94,E94,F94)</f>
+        <v/>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -10641,9 +10712,10 @@
         <f>SUM(G96,G97)</f>
         <v/>
       </c>
-      <c r="H95" s="7">
-        <f>SUM(H96,H97)</f>
-        <v/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="7">
         <f>SUM(I96,I97)</f>
@@ -10667,8 +10739,9 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
-        <v>54000</v>
+      <c r="B96" s="7">
+        <f>SUM(C96,D96,E96,F96)</f>
+        <v/>
       </c>
       <c r="C96" s="7" t="n">
         <v>13500</v>
@@ -10715,8 +10788,9 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7" t="n">
-        <v>217789.84</v>
+      <c r="B97" s="7">
+        <f>SUM(C97,D97,E97,F97)</f>
+        <v/>
       </c>
       <c r="C97" s="7" t="n">
         <v>54447.46</v>
@@ -10787,9 +10861,10 @@
         <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
-      <c r="H98" s="9">
-        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
-        <v/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="9">
         <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
@@ -10837,9 +10912,10 @@
         <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
-      <c r="H99" s="10">
-        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
-        <v/>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="10">
         <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
@@ -11046,9 +11122,10 @@
         <f>SUM(G5,G6)</f>
         <v/>
       </c>
-      <c r="H4" s="7">
-        <f>SUM(H5,H6)</f>
-        <v/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="7">
         <f>SUM(I5,I6)</f>
@@ -11072,10 +11149,9 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="7">
+        <f>SUM(C5,D5,E5,F5)</f>
+        <v/>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -11154,9 +11230,10 @@
         <f>SUM(G7,G8,G9)</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>SUM(H7,H8,H9)</f>
-        <v/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I6" s="7">
         <f>SUM(I7,I8,I9)</f>
@@ -11180,8 +11257,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>2998544</v>
+      <c r="B7" s="7">
+        <f>SUM(C7,D7,E7,F7)</f>
+        <v/>
       </c>
       <c r="C7" s="7" t="n">
         <v>749636</v>
@@ -11228,10 +11306,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="7">
+        <f>SUM(C8,D8,E8,F8)</f>
+        <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -11286,10 +11363,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="7">
+        <f>SUM(C9,D9,E9,F9)</f>
+        <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -11368,9 +11444,10 @@
         <f>SUM(G11,G12,G13,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30,G31,G32,G33,G34)</f>
         <v/>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(H11,H12,H13,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30,H31,H32,H33,H34)</f>
-        <v/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7">
         <f>SUM(I11,I12,I13,I21,I22,I23,I24,I25,I26,I27,I28,I29,I30,I31,I32,I33,I34)</f>
@@ -11394,10 +11471,9 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="7">
+        <f>SUM(C11,D11,E11,F11)</f>
+        <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -11452,10 +11528,9 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="7">
+        <f>SUM(C12,D12,E12,F12)</f>
+        <v/>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -11534,9 +11609,10 @@
         <f>SUM(G14,G15,G16,G17,G18,G19,G20)</f>
         <v/>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(H14,H15,H16,H17,H18,H19,H20)</f>
-        <v/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7">
         <f>SUM(I14,I15,I16,I17,I18,I19,I20)</f>
@@ -11560,10 +11636,9 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="7">
+        <f>SUM(C14,D14,E14,F14)</f>
+        <v/>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -11618,10 +11693,9 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="7">
+        <f>SUM(C15,D15,E15,F15)</f>
+        <v/>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -11676,10 +11750,9 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="7">
+        <f>SUM(C16,D16,E16,F16)</f>
+        <v/>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -11734,8 +11807,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>19356.4</v>
+      <c r="B17" s="7">
+        <f>SUM(C17,D17,E17,F17)</f>
+        <v/>
       </c>
       <c r="C17" s="7" t="n">
         <v>4356.4</v>
@@ -11782,8 +11856,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>19512.5</v>
+      <c r="B18" s="7">
+        <f>SUM(C18,D18,E18,F18)</f>
+        <v/>
       </c>
       <c r="C18" s="7" t="n">
         <v>4512.5</v>
@@ -11830,10 +11905,9 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B19" s="7">
+        <f>SUM(C19,D19,E19,F19)</f>
+        <v/>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -11888,10 +11962,9 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="7">
+        <f>SUM(C20,D20,E20,F20)</f>
+        <v/>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -11946,8 +12019,9 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>512000</v>
+      <c r="B21" s="7">
+        <f>SUM(C21,D21,E21,F21)</f>
+        <v/>
       </c>
       <c r="C21" s="7" t="n">
         <v>128000</v>
@@ -11994,8 +12068,9 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>840000</v>
+      <c r="B22" s="7">
+        <f>SUM(C22,D22,E22,F22)</f>
+        <v/>
       </c>
       <c r="C22" s="7" t="n">
         <v>210000</v>
@@ -12042,8 +12117,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
-        <v>56000</v>
+      <c r="B23" s="7">
+        <f>SUM(C23,D23,E23,F23)</f>
+        <v/>
       </c>
       <c r="C23" s="7" t="n">
         <v>14000</v>
@@ -12090,10 +12166,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="7">
+        <f>SUM(C24,D24,E24,F24)</f>
+        <v/>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -12148,10 +12223,9 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="7">
+        <f>SUM(C25,D25,E25,F25)</f>
+        <v/>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -12206,10 +12280,9 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="7">
+        <f>SUM(C26,D26,E26,F26)</f>
+        <v/>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -12264,8 +12337,9 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n">
-        <v>10000</v>
+      <c r="B27" s="7">
+        <f>SUM(C27,D27,E27,F27)</f>
+        <v/>
       </c>
       <c r="C27" s="7" t="n">
         <v>10000</v>
@@ -12318,10 +12392,9 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="7">
+        <f>SUM(C28,D28,E28,F28)</f>
+        <v/>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -12376,10 +12449,9 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="7">
+        <f>SUM(C29,D29,E29,F29)</f>
+        <v/>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -12434,8 +12506,9 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
-        <v>8000</v>
+      <c r="B30" s="7">
+        <f>SUM(C30,D30,E30,F30)</f>
+        <v/>
       </c>
       <c r="C30" s="7" t="n">
         <v>2000</v>
@@ -12482,10 +12555,9 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="7">
+        <f>SUM(C31,D31,E31,F31)</f>
+        <v/>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -12540,10 +12612,9 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="7">
+        <f>SUM(C32,D32,E32,F32)</f>
+        <v/>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -12598,10 +12669,9 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B33" s="7">
+        <f>SUM(C33,D33,E33,F33)</f>
+        <v/>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -12680,9 +12750,10 @@
         <f>SUM(G35,G36,G37,G38,G39,G40,G41,G42)</f>
         <v/>
       </c>
-      <c r="H34" s="7">
-        <f>SUM(H35,H36,H37,H38,H39,H40,H41,H42)</f>
-        <v/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" s="7">
         <f>SUM(I35,I36,I37,I38,I39,I40,I41,I42)</f>
@@ -12706,10 +12777,9 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="7">
+        <f>SUM(C35,D35,E35,F35)</f>
+        <v/>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -12764,8 +12834,9 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>240000</v>
+      <c r="B36" s="7">
+        <f>SUM(C36,D36,E36,F36)</f>
+        <v/>
       </c>
       <c r="C36" s="7" t="n">
         <v>60000</v>
@@ -12812,8 +12883,9 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
-        <v>4000</v>
+      <c r="B37" s="7">
+        <f>SUM(C37,D37,E37,F37)</f>
+        <v/>
       </c>
       <c r="C37" s="7" t="n">
         <v>1000</v>
@@ -12860,10 +12932,9 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="7">
+        <f>SUM(C38,D38,E38,F38)</f>
+        <v/>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -12918,8 +12989,9 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
-        <v>104000</v>
+      <c r="B39" s="7">
+        <f>SUM(C39,D39,E39,F39)</f>
+        <v/>
       </c>
       <c r="C39" s="7" t="n">
         <v>26000</v>
@@ -12966,10 +13038,9 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="7">
+        <f>SUM(C40,D40,E40,F40)</f>
+        <v/>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -13024,8 +13095,9 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n">
-        <v>4000</v>
+      <c r="B41" s="7">
+        <f>SUM(C41,D41,E41,F41)</f>
+        <v/>
       </c>
       <c r="C41" s="7" t="n">
         <v>1000</v>
@@ -13072,10 +13144,9 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="7">
+        <f>SUM(C42,D42,E42,F42)</f>
+        <v/>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -13154,9 +13225,10 @@
         <f>G4-G10</f>
         <v/>
       </c>
-      <c r="H43" s="9">
-        <f>H4-H10</f>
-        <v/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="9">
         <f>I4-I10</f>
@@ -13204,9 +13276,10 @@
         <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
-        <v/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="10">
         <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
@@ -13254,9 +13327,10 @@
         <f>SUM(G46,G47,G48,G52,G56,G57,G58,G59,G60,G63,G64,G65,G66,G67,G68,G69,G70,G71,G72,G73,G74,G75,G76,G77,G78,G79)</f>
         <v/>
       </c>
-      <c r="H45" s="7">
-        <f>SUM(H46,H47,H48,H52,H56,H57,H58,H59,H60,H63,H64,H65,H66,H67,H68,H69,H70,H71,H72,H73,H74,H75,H76,H77,H78,H79)</f>
-        <v/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="7">
         <f>SUM(I46,I47,I48,I52,I56,I57,I58,I59,I60,I63,I64,I65,I66,I67,I68,I69,I70,I71,I72,I73,I74,I75,I76,I77,I78,I79)</f>
@@ -13280,8 +13354,9 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7" t="n">
-        <v>334040.8</v>
+      <c r="B46" s="7">
+        <f>SUM(C46,D46,E46,F46)</f>
+        <v/>
       </c>
       <c r="C46" s="7" t="n">
         <v>83510.2</v>
@@ -13328,10 +13403,9 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="7">
+        <f>SUM(C47,D47,E47,F47)</f>
+        <v/>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -13410,9 +13484,10 @@
         <f>SUM(G49,G50,G51)</f>
         <v/>
       </c>
-      <c r="H48" s="7">
-        <f>SUM(H49,H50,H51)</f>
-        <v/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="7">
         <f>SUM(I49,I50,I51)</f>
@@ -13436,10 +13511,9 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="7">
+        <f>SUM(C49,D49,E49,F49)</f>
+        <v/>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -13494,10 +13568,9 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="7">
+        <f>SUM(C50,D50,E50,F50)</f>
+        <v/>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -13552,10 +13625,9 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="7">
+        <f>SUM(C51,D51,E51,F51)</f>
+        <v/>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -13634,9 +13706,10 @@
         <f>SUM(G53,G54,G55)</f>
         <v/>
       </c>
-      <c r="H52" s="7">
-        <f>SUM(H53,H54,H55)</f>
-        <v/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="7">
         <f>SUM(I53,I54,I55)</f>
@@ -13660,10 +13733,9 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="7">
+        <f>SUM(C53,D53,E53,F53)</f>
+        <v/>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -13718,10 +13790,9 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="7">
+        <f>SUM(C54,D54,E54,F54)</f>
+        <v/>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -13776,10 +13847,9 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B55" s="7">
+        <f>SUM(C55,D55,E55,F55)</f>
+        <v/>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -13834,10 +13904,9 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="7">
+        <f>SUM(C56,D56,E56,F56)</f>
+        <v/>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -13892,10 +13961,9 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="7">
+        <f>SUM(C57,D57,E57,F57)</f>
+        <v/>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -13950,10 +14018,9 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="7">
+        <f>SUM(C58,D58,E58,F58)</f>
+        <v/>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -14008,10 +14075,9 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="7">
+        <f>SUM(C59,D59,E59,F59)</f>
+        <v/>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -14090,9 +14156,10 @@
         <f>SUM(G61,G62)</f>
         <v/>
       </c>
-      <c r="H60" s="7">
-        <f>SUM(H61,H62)</f>
-        <v/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="7">
         <f>SUM(I61,I62)</f>
@@ -14116,10 +14183,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="7">
+        <f>SUM(C61,D61,E61,F61)</f>
+        <v/>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -14174,10 +14240,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="7">
+        <f>SUM(C62,D62,E62,F62)</f>
+        <v/>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -14232,10 +14297,9 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="7">
+        <f>SUM(C63,D63,E63,F63)</f>
+        <v/>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -14290,10 +14354,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="7">
+        <f>SUM(C64,D64,E64,F64)</f>
+        <v/>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -14348,10 +14411,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="7">
+        <f>SUM(C65,D65,E65,F65)</f>
+        <v/>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -14406,10 +14468,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="7">
+        <f>SUM(C66,D66,E66,F66)</f>
+        <v/>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -14464,10 +14525,9 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="7">
+        <f>SUM(C67,D67,E67,F67)</f>
+        <v/>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -14522,10 +14582,9 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="7">
+        <f>SUM(C68,D68,E68,F68)</f>
+        <v/>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -14580,10 +14639,9 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="7">
+        <f>SUM(C69,D69,E69,F69)</f>
+        <v/>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -14638,10 +14696,9 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="7">
+        <f>SUM(C70,D70,E70,F70)</f>
+        <v/>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -14696,10 +14753,9 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="7">
+        <f>SUM(C71,D71,E71,F71)</f>
+        <v/>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -14754,10 +14810,9 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="7">
+        <f>SUM(C72,D72,E72,F72)</f>
+        <v/>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -14812,10 +14867,9 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="7">
+        <f>SUM(C73,D73,E73,F73)</f>
+        <v/>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -14870,10 +14924,9 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="7">
+        <f>SUM(C74,D74,E74,F74)</f>
+        <v/>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -14928,10 +14981,9 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="7">
+        <f>SUM(C75,D75,E75,F75)</f>
+        <v/>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -14986,10 +15038,9 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="7">
+        <f>SUM(C76,D76,E76,F76)</f>
+        <v/>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -15044,10 +15095,9 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="7">
+        <f>SUM(C77,D77,E77,F77)</f>
+        <v/>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -15102,10 +15152,9 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="7">
+        <f>SUM(C78,D78,E78,F78)</f>
+        <v/>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -15160,10 +15209,9 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="7">
+        <f>SUM(C79,D79,E79,F79)</f>
+        <v/>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -15242,9 +15290,10 @@
         <f>G43-G45</f>
         <v/>
       </c>
-      <c r="H80" s="9">
-        <f>H43-H45</f>
-        <v/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" s="9">
         <f>I43-I45</f>
@@ -15292,9 +15341,10 @@
         <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
-      <c r="H81" s="10">
-        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
-        <v/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" s="10">
         <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
@@ -15342,9 +15392,10 @@
         <f>SUM(G83,G84,G85,G86)</f>
         <v/>
       </c>
-      <c r="H82" s="7">
-        <f>SUM(H83,H84,H85,H86)</f>
-        <v/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" s="7">
         <f>SUM(I83,I84,I85,I86)</f>
@@ -15368,10 +15419,9 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="7">
+        <f>SUM(C83,D83,E83,F83)</f>
+        <v/>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -15426,10 +15476,9 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="7">
+        <f>SUM(C84,D84,E84,F84)</f>
+        <v/>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -15484,10 +15533,9 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="7">
+        <f>SUM(C85,D85,E85,F85)</f>
+        <v/>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -15542,10 +15590,9 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="7">
+        <f>SUM(C86,D86,E86,F86)</f>
+        <v/>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -15624,9 +15671,10 @@
         <f>SUM(G88)</f>
         <v/>
       </c>
-      <c r="H87" s="7">
-        <f>SUM(H88)</f>
-        <v/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="7">
         <f>SUM(I88)</f>
@@ -15650,10 +15698,9 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="7">
+        <f>SUM(C88,D88,E88,F88)</f>
+        <v/>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -15732,9 +15779,10 @@
         <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
-        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
-        <v/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="9">
         <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
@@ -15782,9 +15830,10 @@
         <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
-      <c r="H90" s="10">
-        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
-        <v/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I90" s="10">
         <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
@@ -15832,9 +15881,10 @@
         <f>SUM(G92,G93)</f>
         <v/>
       </c>
-      <c r="H91" s="7">
-        <f>SUM(H92,H93)</f>
-        <v/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I91" s="7">
         <f>SUM(I92,I93)</f>
@@ -15858,10 +15908,9 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="7">
+        <f>SUM(C92,D92,E92,F92)</f>
+        <v/>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -15916,10 +15965,9 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="7">
+        <f>SUM(C93,D93,E93,F93)</f>
+        <v/>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -15974,10 +16022,9 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="7">
+        <f>SUM(C94,D94,E94,F94)</f>
+        <v/>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -16056,9 +16103,10 @@
         <f>SUM(G96,G97)</f>
         <v/>
       </c>
-      <c r="H95" s="7">
-        <f>SUM(H96,H97)</f>
-        <v/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="7">
         <f>SUM(I96,I97)</f>
@@ -16082,8 +16130,9 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
-        <v>44000</v>
+      <c r="B96" s="7">
+        <f>SUM(C96,D96,E96,F96)</f>
+        <v/>
       </c>
       <c r="C96" s="7" t="n">
         <v>11000</v>
@@ -16130,8 +16179,9 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7" t="n">
-        <v>142778.72</v>
+      <c r="B97" s="7">
+        <f>SUM(C97,D97,E97,F97)</f>
+        <v/>
       </c>
       <c r="C97" s="7" t="n">
         <v>35694.68</v>
@@ -16202,9 +16252,10 @@
         <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
-      <c r="H98" s="9">
-        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
-        <v/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="9">
         <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
@@ -16252,9 +16303,10 @@
         <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
-      <c r="H99" s="10">
-        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
-        <v/>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="10">
         <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
@@ -16461,9 +16513,10 @@
         <f>SUM(G5,G6)</f>
         <v/>
       </c>
-      <c r="H4" s="7">
-        <f>SUM(H5,H6)</f>
-        <v/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="7">
         <f>SUM(I5,I6)</f>
@@ -16487,10 +16540,9 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="7">
+        <f>SUM(C5,D5,E5,F5)</f>
+        <v/>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -16569,9 +16621,10 @@
         <f>SUM(G7,G8,G9)</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>SUM(H7,H8,H9)</f>
-        <v/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I6" s="7">
         <f>SUM(I7,I8,I9)</f>
@@ -16595,8 +16648,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>6928360.96</v>
+      <c r="B7" s="7">
+        <f>SUM(C7,D7,E7,F7)</f>
+        <v/>
       </c>
       <c r="C7" s="7" t="n">
         <v>1732090.24</v>
@@ -16643,10 +16697,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="7">
+        <f>SUM(C8,D8,E8,F8)</f>
+        <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -16701,10 +16754,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="7">
+        <f>SUM(C9,D9,E9,F9)</f>
+        <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -16783,9 +16835,10 @@
         <f>SUM(G11,G12,G13,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30,G31,G32,G33,G34)</f>
         <v/>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(H11,H12,H13,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30,H31,H32,H33,H34)</f>
-        <v/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7">
         <f>SUM(I11,I12,I13,I21,I22,I23,I24,I25,I26,I27,I28,I29,I30,I31,I32,I33,I34)</f>
@@ -16809,10 +16862,9 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="7">
+        <f>SUM(C11,D11,E11,F11)</f>
+        <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -16867,10 +16919,9 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="7">
+        <f>SUM(C12,D12,E12,F12)</f>
+        <v/>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -16949,9 +17000,10 @@
         <f>SUM(G14,G15,G16,G17,G18,G19,G20)</f>
         <v/>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(H14,H15,H16,H17,H18,H19,H20)</f>
-        <v/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7">
         <f>SUM(I14,I15,I16,I17,I18,I19,I20)</f>
@@ -16975,10 +17027,9 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="7">
+        <f>SUM(C14,D14,E14,F14)</f>
+        <v/>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -17033,8 +17084,9 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
-        <v>356500</v>
+      <c r="B15" s="7">
+        <f>SUM(C15,D15,E15,F15)</f>
+        <v/>
       </c>
       <c r="C15" s="7" t="n">
         <v>80500</v>
@@ -17081,10 +17133,9 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="7">
+        <f>SUM(C16,D16,E16,F16)</f>
+        <v/>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -17139,8 +17190,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>20000</v>
+      <c r="B17" s="7">
+        <f>SUM(C17,D17,E17,F17)</f>
+        <v/>
       </c>
       <c r="C17" s="7" t="n">
         <v>5000</v>
@@ -17187,8 +17239,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>40019</v>
+      <c r="B18" s="7">
+        <f>SUM(C18,D18,E18,F18)</f>
+        <v/>
       </c>
       <c r="C18" s="7" t="n">
         <v>25019</v>
@@ -17235,10 +17288,9 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B19" s="7">
+        <f>SUM(C19,D19,E19,F19)</f>
+        <v/>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -17293,10 +17345,9 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="7">
+        <f>SUM(C20,D20,E20,F20)</f>
+        <v/>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -17351,8 +17402,9 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>1204000</v>
+      <c r="B21" s="7">
+        <f>SUM(C21,D21,E21,F21)</f>
+        <v/>
       </c>
       <c r="C21" s="7" t="n">
         <v>301000</v>
@@ -17399,8 +17451,9 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>1335994</v>
+      <c r="B22" s="7">
+        <f>SUM(C22,D22,E22,F22)</f>
+        <v/>
       </c>
       <c r="C22" s="7" t="n">
         <v>333994</v>
@@ -17447,8 +17500,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
-        <v>195244</v>
+      <c r="B23" s="7">
+        <f>SUM(C23,D23,E23,F23)</f>
+        <v/>
       </c>
       <c r="C23" s="7" t="n">
         <v>48811</v>
@@ -17495,8 +17549,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
-        <v>56000</v>
+      <c r="B24" s="7">
+        <f>SUM(C24,D24,E24,F24)</f>
+        <v/>
       </c>
       <c r="C24" s="7" t="n">
         <v>14000</v>
@@ -17543,8 +17598,9 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
-        <v>2000</v>
+      <c r="B25" s="7">
+        <f>SUM(C25,D25,E25,F25)</f>
+        <v/>
       </c>
       <c r="C25" s="7" t="n">
         <v>2000</v>
@@ -17597,10 +17653,9 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="7">
+        <f>SUM(C26,D26,E26,F26)</f>
+        <v/>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -17655,10 +17710,9 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="7">
+        <f>SUM(C27,D27,E27,F27)</f>
+        <v/>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -17713,10 +17767,9 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="7">
+        <f>SUM(C28,D28,E28,F28)</f>
+        <v/>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -17771,10 +17824,9 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="7">
+        <f>SUM(C29,D29,E29,F29)</f>
+        <v/>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -17829,10 +17881,9 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="7">
+        <f>SUM(C30,D30,E30,F30)</f>
+        <v/>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -17887,8 +17938,9 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n">
-        <v>3200</v>
+      <c r="B31" s="7">
+        <f>SUM(C31,D31,E31,F31)</f>
+        <v/>
       </c>
       <c r="C31" s="7" t="n">
         <v>3200</v>
@@ -17941,10 +17993,9 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="7">
+        <f>SUM(C32,D32,E32,F32)</f>
+        <v/>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -17999,10 +18050,9 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B33" s="7">
+        <f>SUM(C33,D33,E33,F33)</f>
+        <v/>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -18081,9 +18131,10 @@
         <f>SUM(G35,G36,G37,G38,G39,G40,G41,G42)</f>
         <v/>
       </c>
-      <c r="H34" s="7">
-        <f>SUM(H35,H36,H37,H38,H39,H40,H41,H42)</f>
-        <v/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" s="7">
         <f>SUM(I35,I36,I37,I38,I39,I40,I41,I42)</f>
@@ -18107,10 +18158,9 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="7">
+        <f>SUM(C35,D35,E35,F35)</f>
+        <v/>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -18165,10 +18215,9 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="7">
+        <f>SUM(C36,D36,E36,F36)</f>
+        <v/>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -18223,8 +18272,9 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
-        <v>2000</v>
+      <c r="B37" s="7">
+        <f>SUM(C37,D37,E37,F37)</f>
+        <v/>
       </c>
       <c r="C37" s="7" t="n">
         <v>2000</v>
@@ -18277,10 +18327,9 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="7">
+        <f>SUM(C38,D38,E38,F38)</f>
+        <v/>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -18335,8 +18384,9 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
-        <v>232500</v>
+      <c r="B39" s="7">
+        <f>SUM(C39,D39,E39,F39)</f>
+        <v/>
       </c>
       <c r="C39" s="7" t="n">
         <v>72900</v>
@@ -18383,10 +18433,9 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="7">
+        <f>SUM(C40,D40,E40,F40)</f>
+        <v/>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -18441,10 +18490,9 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="7">
+        <f>SUM(C41,D41,E41,F41)</f>
+        <v/>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
@@ -18499,10 +18547,9 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="7">
+        <f>SUM(C42,D42,E42,F42)</f>
+        <v/>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -18581,9 +18628,10 @@
         <f>G4-G10</f>
         <v/>
       </c>
-      <c r="H43" s="9">
-        <f>H4-H10</f>
-        <v/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="9">
         <f>I4-I10</f>
@@ -18631,9 +18679,10 @@
         <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
-        <v/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="10">
         <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
@@ -18681,9 +18730,10 @@
         <f>SUM(G46,G47,G48,G52,G56,G57,G58,G59,G60,G63,G64,G65,G66,G67,G68,G69,G70,G71,G72,G73,G74,G75,G76,G77,G78,G79)</f>
         <v/>
       </c>
-      <c r="H45" s="7">
-        <f>SUM(H46,H47,H48,H52,H56,H57,H58,H59,H60,H63,H64,H65,H66,H67,H68,H69,H70,H71,H72,H73,H74,H75,H76,H77,H78,H79)</f>
-        <v/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="7">
         <f>SUM(I46,I47,I48,I52,I56,I57,I58,I59,I60,I63,I64,I65,I66,I67,I68,I69,I70,I71,I72,I73,I74,I75,I76,I77,I78,I79)</f>
@@ -18707,8 +18757,9 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7" t="n">
-        <v>772399.64</v>
+      <c r="B46" s="7">
+        <f>SUM(C46,D46,E46,F46)</f>
+        <v/>
       </c>
       <c r="C46" s="7" t="n">
         <v>193099.91</v>
@@ -18755,10 +18806,9 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="7">
+        <f>SUM(C47,D47,E47,F47)</f>
+        <v/>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -18837,9 +18887,10 @@
         <f>SUM(G49,G50,G51)</f>
         <v/>
       </c>
-      <c r="H48" s="7">
-        <f>SUM(H49,H50,H51)</f>
-        <v/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="7">
         <f>SUM(I49,I50,I51)</f>
@@ -18863,10 +18914,9 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="7">
+        <f>SUM(C49,D49,E49,F49)</f>
+        <v/>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -18921,10 +18971,9 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="7">
+        <f>SUM(C50,D50,E50,F50)</f>
+        <v/>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -18979,10 +19028,9 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="7">
+        <f>SUM(C51,D51,E51,F51)</f>
+        <v/>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -19061,9 +19109,10 @@
         <f>SUM(G53,G54,G55)</f>
         <v/>
       </c>
-      <c r="H52" s="7">
-        <f>SUM(H53,H54,H55)</f>
-        <v/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="7">
         <f>SUM(I53,I54,I55)</f>
@@ -19087,8 +19136,9 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7" t="n">
-        <v>39295.42</v>
+      <c r="B53" s="7">
+        <f>SUM(C53,D53,E53,F53)</f>
+        <v/>
       </c>
       <c r="C53" s="7" t="n">
         <v>9886.42</v>
@@ -19135,10 +19185,9 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="7">
+        <f>SUM(C54,D54,E54,F54)</f>
+        <v/>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -19193,10 +19242,9 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B55" s="7">
+        <f>SUM(C55,D55,E55,F55)</f>
+        <v/>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -19251,8 +19299,9 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7" t="n">
-        <v>8000</v>
+      <c r="B56" s="7">
+        <f>SUM(C56,D56,E56,F56)</f>
+        <v/>
       </c>
       <c r="C56" s="7" t="n">
         <v>2000</v>
@@ -19299,10 +19348,9 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="7">
+        <f>SUM(C57,D57,E57,F57)</f>
+        <v/>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -19357,10 +19405,9 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="7">
+        <f>SUM(C58,D58,E58,F58)</f>
+        <v/>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -19415,10 +19462,9 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="7">
+        <f>SUM(C59,D59,E59,F59)</f>
+        <v/>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -19497,9 +19543,10 @@
         <f>SUM(G61,G62)</f>
         <v/>
       </c>
-      <c r="H60" s="7">
-        <f>SUM(H61,H62)</f>
-        <v/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="7">
         <f>SUM(I61,I62)</f>
@@ -19523,10 +19570,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="7">
+        <f>SUM(C61,D61,E61,F61)</f>
+        <v/>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -19581,10 +19627,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="7">
+        <f>SUM(C62,D62,E62,F62)</f>
+        <v/>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -19639,10 +19684,9 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="7">
+        <f>SUM(C63,D63,E63,F63)</f>
+        <v/>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -19697,10 +19741,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="7">
+        <f>SUM(C64,D64,E64,F64)</f>
+        <v/>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -19755,10 +19798,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="7">
+        <f>SUM(C65,D65,E65,F65)</f>
+        <v/>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -19813,10 +19855,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="7">
+        <f>SUM(C66,D66,E66,F66)</f>
+        <v/>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -19871,10 +19912,9 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="7">
+        <f>SUM(C67,D67,E67,F67)</f>
+        <v/>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -19929,10 +19969,9 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="7">
+        <f>SUM(C68,D68,E68,F68)</f>
+        <v/>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -19987,10 +20026,9 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="7">
+        <f>SUM(C69,D69,E69,F69)</f>
+        <v/>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -20045,10 +20083,9 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="7">
+        <f>SUM(C70,D70,E70,F70)</f>
+        <v/>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -20103,10 +20140,9 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="7">
+        <f>SUM(C71,D71,E71,F71)</f>
+        <v/>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -20161,10 +20197,9 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="7">
+        <f>SUM(C72,D72,E72,F72)</f>
+        <v/>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -20219,10 +20254,9 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="7">
+        <f>SUM(C73,D73,E73,F73)</f>
+        <v/>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -20277,10 +20311,9 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="7">
+        <f>SUM(C74,D74,E74,F74)</f>
+        <v/>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -20335,10 +20368,9 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="7">
+        <f>SUM(C75,D75,E75,F75)</f>
+        <v/>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -20393,10 +20425,9 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="7">
+        <f>SUM(C76,D76,E76,F76)</f>
+        <v/>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -20451,10 +20482,9 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="7">
+        <f>SUM(C77,D77,E77,F77)</f>
+        <v/>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -20509,10 +20539,9 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="7">
+        <f>SUM(C78,D78,E78,F78)</f>
+        <v/>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -20567,10 +20596,9 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="7">
+        <f>SUM(C79,D79,E79,F79)</f>
+        <v/>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -20649,9 +20677,10 @@
         <f>G43-G45</f>
         <v/>
       </c>
-      <c r="H80" s="9">
-        <f>H43-H45</f>
-        <v/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" s="9">
         <f>I43-I45</f>
@@ -20699,9 +20728,10 @@
         <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
-      <c r="H81" s="10">
-        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
-        <v/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" s="10">
         <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
@@ -20749,9 +20779,10 @@
         <f>SUM(G83,G84,G85,G86)</f>
         <v/>
       </c>
-      <c r="H82" s="7">
-        <f>SUM(H83,H84,H85,H86)</f>
-        <v/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" s="7">
         <f>SUM(I83,I84,I85,I86)</f>
@@ -20775,10 +20806,9 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="7">
+        <f>SUM(C83,D83,E83,F83)</f>
+        <v/>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -20833,10 +20863,9 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="7">
+        <f>SUM(C84,D84,E84,F84)</f>
+        <v/>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -20891,10 +20920,9 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="7">
+        <f>SUM(C85,D85,E85,F85)</f>
+        <v/>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -20949,10 +20977,9 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="7">
+        <f>SUM(C86,D86,E86,F86)</f>
+        <v/>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -21031,9 +21058,10 @@
         <f>SUM(G88)</f>
         <v/>
       </c>
-      <c r="H87" s="7">
-        <f>SUM(H88)</f>
-        <v/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="7">
         <f>SUM(I88)</f>
@@ -21057,10 +21085,9 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="7">
+        <f>SUM(C88,D88,E88,F88)</f>
+        <v/>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -21139,9 +21166,10 @@
         <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
-        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
-        <v/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="9">
         <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
@@ -21189,9 +21217,10 @@
         <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
-      <c r="H90" s="10">
-        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
-        <v/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I90" s="10">
         <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
@@ -21239,9 +21268,10 @@
         <f>SUM(G92,G93)</f>
         <v/>
       </c>
-      <c r="H91" s="7">
-        <f>SUM(H92,H93)</f>
-        <v/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I91" s="7">
         <f>SUM(I92,I93)</f>
@@ -21265,10 +21295,9 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="7">
+        <f>SUM(C92,D92,E92,F92)</f>
+        <v/>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -21323,10 +21352,9 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="7">
+        <f>SUM(C93,D93,E93,F93)</f>
+        <v/>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -21381,10 +21409,9 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="7">
+        <f>SUM(C94,D94,E94,F94)</f>
+        <v/>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -21463,9 +21490,10 @@
         <f>SUM(G96,G97)</f>
         <v/>
       </c>
-      <c r="H95" s="7">
-        <f>SUM(H96,H97)</f>
-        <v/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="7">
         <f>SUM(I96,I97)</f>
@@ -21489,8 +21517,9 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
-        <v>100000</v>
+      <c r="B96" s="7">
+        <f>SUM(C96,D96,E96,F96)</f>
+        <v/>
       </c>
       <c r="C96" s="7" t="n">
         <v>25000</v>
@@ -21537,8 +21566,9 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7" t="n">
-        <v>329930.56</v>
+      <c r="B97" s="7">
+        <f>SUM(C97,D97,E97,F97)</f>
+        <v/>
       </c>
       <c r="C97" s="7" t="n">
         <v>82482.64</v>
@@ -21609,9 +21639,10 @@
         <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
-      <c r="H98" s="9">
-        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
-        <v/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="9">
         <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
@@ -21659,9 +21690,10 @@
         <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
-      <c r="H99" s="10">
-        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
-        <v/>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="10">
         <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>
@@ -21868,9 +21900,10 @@
         <f>SUM(G5,G6)</f>
         <v/>
       </c>
-      <c r="H4" s="7">
-        <f>SUM(H5,H6)</f>
-        <v/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="7">
         <f>SUM(I5,I6)</f>
@@ -21894,10 +21927,9 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="7">
+        <f>SUM(C5,D5,E5,F5)</f>
+        <v/>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -21976,9 +22008,10 @@
         <f>SUM(G7,G8,G9)</f>
         <v/>
       </c>
-      <c r="H6" s="7">
-        <f>SUM(H7,H8,H9)</f>
-        <v/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I6" s="7">
         <f>SUM(I7,I8,I9)</f>
@@ -22002,8 +22035,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>872916.16</v>
+      <c r="B7" s="7">
+        <f>SUM(C7,D7,E7,F7)</f>
+        <v/>
       </c>
       <c r="C7" s="7" t="n">
         <v>218229.04</v>
@@ -22050,10 +22084,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="7">
+        <f>SUM(C8,D8,E8,F8)</f>
+        <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -22108,10 +22141,9 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="7">
+        <f>SUM(C9,D9,E9,F9)</f>
+        <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -22190,9 +22222,10 @@
         <f>SUM(G11,G12,G13,G21,G22,G23,G24,G25,G26,G27,G28,G29,G30,G31,G32,G33,G34)</f>
         <v/>
       </c>
-      <c r="H10" s="7">
-        <f>SUM(H11,H12,H13,H21,H22,H23,H24,H25,H26,H27,H28,H29,H30,H31,H32,H33,H34)</f>
-        <v/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7">
         <f>SUM(I11,I12,I13,I21,I22,I23,I24,I25,I26,I27,I28,I29,I30,I31,I32,I33,I34)</f>
@@ -22216,10 +22249,9 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="7">
+        <f>SUM(C11,D11,E11,F11)</f>
+        <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -22274,10 +22306,9 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="7">
+        <f>SUM(C12,D12,E12,F12)</f>
+        <v/>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -22356,9 +22387,10 @@
         <f>SUM(G14,G15,G16,G17,G18,G19,G20)</f>
         <v/>
       </c>
-      <c r="H13" s="7">
-        <f>SUM(H14,H15,H16,H17,H18,H19,H20)</f>
-        <v/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7">
         <f>SUM(I14,I15,I16,I17,I18,I19,I20)</f>
@@ -22382,10 +22414,9 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="7">
+        <f>SUM(C14,D14,E14,F14)</f>
+        <v/>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -22440,10 +22471,9 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="7">
+        <f>SUM(C15,D15,E15,F15)</f>
+        <v/>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -22498,10 +22528,9 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="7">
+        <f>SUM(C16,D16,E16,F16)</f>
+        <v/>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -22556,8 +22585,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>3219.98</v>
+      <c r="B17" s="7">
+        <f>SUM(C17,D17,E17,F17)</f>
+        <v/>
       </c>
       <c r="C17" s="7" t="n">
         <v>219.98</v>
@@ -22604,8 +22634,9 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>4000</v>
+      <c r="B18" s="7">
+        <f>SUM(C18,D18,E18,F18)</f>
+        <v/>
       </c>
       <c r="C18" s="7" t="n">
         <v>1000</v>
@@ -22652,10 +22683,9 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B19" s="7">
+        <f>SUM(C19,D19,E19,F19)</f>
+        <v/>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -22710,10 +22740,9 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="7">
+        <f>SUM(C20,D20,E20,F20)</f>
+        <v/>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -22768,8 +22797,9 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>340000</v>
+      <c r="B21" s="7">
+        <f>SUM(C21,D21,E21,F21)</f>
+        <v/>
       </c>
       <c r="C21" s="7" t="n">
         <v>85000</v>
@@ -22816,8 +22846,9 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>500000</v>
+      <c r="B22" s="7">
+        <f>SUM(C22,D22,E22,F22)</f>
+        <v/>
       </c>
       <c r="C22" s="7" t="n">
         <v>125000</v>
@@ -22864,10 +22895,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="7">
+        <f>SUM(C23,D23,E23,F23)</f>
+        <v/>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -22922,8 +22952,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
-        <v>48631.75</v>
+      <c r="B24" s="7">
+        <f>SUM(C24,D24,E24,F24)</f>
+        <v/>
       </c>
       <c r="C24" s="7" t="n">
         <v>6631.75</v>
@@ -22970,10 +23001,9 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="7">
+        <f>SUM(C25,D25,E25,F25)</f>
+        <v/>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -23028,10 +23058,9 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="7">
+        <f>SUM(C26,D26,E26,F26)</f>
+        <v/>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -23086,10 +23115,9 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="7">
+        <f>SUM(C27,D27,E27,F27)</f>
+        <v/>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -23144,10 +23172,9 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="7">
+        <f>SUM(C28,D28,E28,F28)</f>
+        <v/>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -23202,10 +23229,9 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="7">
+        <f>SUM(C29,D29,E29,F29)</f>
+        <v/>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -23260,8 +23286,9 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
-        <v>12000</v>
+      <c r="B30" s="7">
+        <f>SUM(C30,D30,E30,F30)</f>
+        <v/>
       </c>
       <c r="C30" s="7" t="n">
         <v>3000</v>
@@ -23308,10 +23335,9 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="7">
+        <f>SUM(C31,D31,E31,F31)</f>
+        <v/>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -23366,10 +23392,9 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="7">
+        <f>SUM(C32,D32,E32,F32)</f>
+        <v/>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -23424,10 +23449,9 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B33" s="7">
+        <f>SUM(C33,D33,E33,F33)</f>
+        <v/>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -23506,9 +23530,10 @@
         <f>SUM(G35,G36,G37,G38,G39,G40,G41,G42)</f>
         <v/>
       </c>
-      <c r="H34" s="7">
-        <f>SUM(H35,H36,H37,H38,H39,H40,H41,H42)</f>
-        <v/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I34" s="7">
         <f>SUM(I35,I36,I37,I38,I39,I40,I41,I42)</f>
@@ -23532,10 +23557,9 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="7">
+        <f>SUM(C35,D35,E35,F35)</f>
+        <v/>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -23590,8 +23614,9 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>80000</v>
+      <c r="B36" s="7">
+        <f>SUM(C36,D36,E36,F36)</f>
+        <v/>
       </c>
       <c r="C36" s="7" t="n">
         <v>20000</v>
@@ -23638,8 +23663,9 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
-        <v>4118.38</v>
+      <c r="B37" s="7">
+        <f>SUM(C37,D37,E37,F37)</f>
+        <v/>
       </c>
       <c r="C37" s="7" t="n">
         <v>1118.38</v>
@@ -23686,10 +23712,9 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="7">
+        <f>SUM(C38,D38,E38,F38)</f>
+        <v/>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -23744,8 +23769,9 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
-        <v>52000</v>
+      <c r="B39" s="7">
+        <f>SUM(C39,D39,E39,F39)</f>
+        <v/>
       </c>
       <c r="C39" s="7" t="n">
         <v>13000</v>
@@ -23792,10 +23818,9 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="7">
+        <f>SUM(C40,D40,E40,F40)</f>
+        <v/>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -23850,10 +23875,9 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="7">
+        <f>SUM(C41,D41,E41,F41)</f>
+        <v/>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
@@ -23908,10 +23932,9 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="7">
+        <f>SUM(C42,D42,E42,F42)</f>
+        <v/>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -23990,9 +24013,10 @@
         <f>G4-G10</f>
         <v/>
       </c>
-      <c r="H43" s="9">
-        <f>H4-H10</f>
-        <v/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I43" s="9">
         <f>I4-I10</f>
@@ -24040,9 +24064,10 @@
         <f>IFERROR(IF(G4=0,"-",G43/G4),"-")</f>
         <v/>
       </c>
-      <c r="H44" s="10">
-        <f>IFERROR(IF(H4=0,"-",H43/H4),"-")</f>
-        <v/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I44" s="10">
         <f>IFERROR(IF(I4=0,"-",I43/I4),"-")</f>
@@ -24090,9 +24115,10 @@
         <f>SUM(G46,G47,G48,G52,G56,G57,G58,G59,G60,G63,G64,G65,G66,G67,G68,G69,G70,G71,G72,G73,G74,G75,G76,G77,G78,G79)</f>
         <v/>
       </c>
-      <c r="H45" s="7">
-        <f>SUM(H46,H47,H48,H52,H56,H57,H58,H59,H60,H63,H64,H65,H66,H67,H68,H69,H70,H71,H72,H73,H74,H75,H76,H77,H78,H79)</f>
-        <v/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="7">
         <f>SUM(I46,I47,I48,I52,I56,I57,I58,I59,I60,I63,I64,I65,I66,I67,I68,I69,I70,I71,I72,I73,I74,I75,I76,I77,I78,I79)</f>
@@ -24116,8 +24142,9 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7" t="n">
-        <v>150809.56</v>
+      <c r="B46" s="7">
+        <f>SUM(C46,D46,E46,F46)</f>
+        <v/>
       </c>
       <c r="C46" s="7" t="n">
         <v>37702.39</v>
@@ -24164,10 +24191,9 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="7">
+        <f>SUM(C47,D47,E47,F47)</f>
+        <v/>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -24246,9 +24272,10 @@
         <f>SUM(G49,G50,G51)</f>
         <v/>
       </c>
-      <c r="H48" s="7">
-        <f>SUM(H49,H50,H51)</f>
-        <v/>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="7">
         <f>SUM(I49,I50,I51)</f>
@@ -24272,10 +24299,9 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="7">
+        <f>SUM(C49,D49,E49,F49)</f>
+        <v/>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -24330,10 +24356,9 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="7">
+        <f>SUM(C50,D50,E50,F50)</f>
+        <v/>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -24388,10 +24413,9 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="7">
+        <f>SUM(C51,D51,E51,F51)</f>
+        <v/>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -24470,9 +24494,10 @@
         <f>SUM(G53,G54,G55)</f>
         <v/>
       </c>
-      <c r="H52" s="7">
-        <f>SUM(H53,H54,H55)</f>
-        <v/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I52" s="7">
         <f>SUM(I53,I54,I55)</f>
@@ -24496,10 +24521,9 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="7">
+        <f>SUM(C53,D53,E53,F53)</f>
+        <v/>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -24554,10 +24578,9 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="7">
+        <f>SUM(C54,D54,E54,F54)</f>
+        <v/>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -24612,10 +24635,9 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B55" s="7">
+        <f>SUM(C55,D55,E55,F55)</f>
+        <v/>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -24670,10 +24692,9 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="7">
+        <f>SUM(C56,D56,E56,F56)</f>
+        <v/>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -24728,10 +24749,9 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="7">
+        <f>SUM(C57,D57,E57,F57)</f>
+        <v/>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -24786,10 +24806,9 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="7">
+        <f>SUM(C58,D58,E58,F58)</f>
+        <v/>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -24844,10 +24863,9 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="7">
+        <f>SUM(C59,D59,E59,F59)</f>
+        <v/>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -24926,9 +24944,10 @@
         <f>SUM(G61,G62)</f>
         <v/>
       </c>
-      <c r="H60" s="7">
-        <f>SUM(H61,H62)</f>
-        <v/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="7">
         <f>SUM(I61,I62)</f>
@@ -24952,10 +24971,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="7">
+        <f>SUM(C61,D61,E61,F61)</f>
+        <v/>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -25010,10 +25028,9 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="7">
+        <f>SUM(C62,D62,E62,F62)</f>
+        <v/>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -25068,10 +25085,9 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="7">
+        <f>SUM(C63,D63,E63,F63)</f>
+        <v/>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -25126,10 +25142,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="7">
+        <f>SUM(C64,D64,E64,F64)</f>
+        <v/>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -25184,10 +25199,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="7">
+        <f>SUM(C65,D65,E65,F65)</f>
+        <v/>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -25242,10 +25256,9 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="7">
+        <f>SUM(C66,D66,E66,F66)</f>
+        <v/>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -25300,10 +25313,9 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="7">
+        <f>SUM(C67,D67,E67,F67)</f>
+        <v/>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -25358,10 +25370,9 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="7">
+        <f>SUM(C68,D68,E68,F68)</f>
+        <v/>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -25416,10 +25427,9 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="7">
+        <f>SUM(C69,D69,E69,F69)</f>
+        <v/>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -25474,10 +25484,9 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="7">
+        <f>SUM(C70,D70,E70,F70)</f>
+        <v/>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -25532,10 +25541,9 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="7">
+        <f>SUM(C71,D71,E71,F71)</f>
+        <v/>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -25590,10 +25598,9 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="7">
+        <f>SUM(C72,D72,E72,F72)</f>
+        <v/>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -25648,10 +25655,9 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="7">
+        <f>SUM(C73,D73,E73,F73)</f>
+        <v/>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -25706,10 +25712,9 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="7">
+        <f>SUM(C74,D74,E74,F74)</f>
+        <v/>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -25764,10 +25769,9 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="7">
+        <f>SUM(C75,D75,E75,F75)</f>
+        <v/>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -25822,10 +25826,9 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="7">
+        <f>SUM(C76,D76,E76,F76)</f>
+        <v/>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -25880,10 +25883,9 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="7">
+        <f>SUM(C77,D77,E77,F77)</f>
+        <v/>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -25938,10 +25940,9 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="7">
+        <f>SUM(C78,D78,E78,F78)</f>
+        <v/>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -25996,10 +25997,9 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="7">
+        <f>SUM(C79,D79,E79,F79)</f>
+        <v/>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -26078,9 +26078,10 @@
         <f>G43-G45</f>
         <v/>
       </c>
-      <c r="H80" s="9">
-        <f>H43-H45</f>
-        <v/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I80" s="9">
         <f>I43-I45</f>
@@ -26128,9 +26129,10 @@
         <f>IFERROR(IF(G4=0,"-",G80/G4),"-")</f>
         <v/>
       </c>
-      <c r="H81" s="10">
-        <f>IFERROR(IF(H4=0,"-",H80/H4),"-")</f>
-        <v/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" s="10">
         <f>IFERROR(IF(I4=0,"-",I80/I4),"-")</f>
@@ -26178,9 +26180,10 @@
         <f>SUM(G83,G84,G85,G86)</f>
         <v/>
       </c>
-      <c r="H82" s="7">
-        <f>SUM(H83,H84,H85,H86)</f>
-        <v/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I82" s="7">
         <f>SUM(I83,I84,I85,I86)</f>
@@ -26204,10 +26207,9 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="7">
+        <f>SUM(C83,D83,E83,F83)</f>
+        <v/>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -26262,10 +26264,9 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="7">
+        <f>SUM(C84,D84,E84,F84)</f>
+        <v/>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -26320,10 +26321,9 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="7">
+        <f>SUM(C85,D85,E85,F85)</f>
+        <v/>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -26378,10 +26378,9 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="7">
+        <f>SUM(C86,D86,E86,F86)</f>
+        <v/>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -26460,9 +26459,10 @@
         <f>SUM(G88)</f>
         <v/>
       </c>
-      <c r="H87" s="7">
-        <f>SUM(H88)</f>
-        <v/>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I87" s="7">
         <f>SUM(I88)</f>
@@ -26486,10 +26486,9 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="7">
+        <f>SUM(C88,D88,E88,F88)</f>
+        <v/>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -26568,9 +26567,10 @@
         <f>G80+IFERROR(G82*1,0)-IFERROR(G87*1,0)</f>
         <v/>
       </c>
-      <c r="H89" s="9">
-        <f>H80+IFERROR(H82*1,0)-IFERROR(H87*1,0)</f>
-        <v/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I89" s="9">
         <f>I80+IFERROR(I82*1,0)-IFERROR(I87*1,0)</f>
@@ -26618,9 +26618,10 @@
         <f>IFERROR(IF(G4=0,"-",G89/G4),"-")</f>
         <v/>
       </c>
-      <c r="H90" s="10">
-        <f>IFERROR(IF(H4=0,"-",H89/H4),"-")</f>
-        <v/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I90" s="10">
         <f>IFERROR(IF(I4=0,"-",I89/I4),"-")</f>
@@ -26668,9 +26669,10 @@
         <f>SUM(G92,G93)</f>
         <v/>
       </c>
-      <c r="H91" s="7">
-        <f>SUM(H92,H93)</f>
-        <v/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I91" s="7">
         <f>SUM(I92,I93)</f>
@@ -26694,10 +26696,9 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="7">
+        <f>SUM(C92,D92,E92,F92)</f>
+        <v/>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -26752,10 +26753,9 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="7">
+        <f>SUM(C93,D93,E93,F93)</f>
+        <v/>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -26810,10 +26810,9 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="7">
+        <f>SUM(C94,D94,E94,F94)</f>
+        <v/>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -26892,9 +26891,10 @@
         <f>SUM(G96,G97)</f>
         <v/>
       </c>
-      <c r="H95" s="7">
-        <f>SUM(H96,H97)</f>
-        <v/>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="7">
         <f>SUM(I96,I97)</f>
@@ -26918,8 +26918,9 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
-        <v>13200</v>
+      <c r="B96" s="7">
+        <f>SUM(C96,D96,E96,F96)</f>
+        <v/>
       </c>
       <c r="C96" s="7" t="n">
         <v>3300</v>
@@ -26966,8 +26967,9 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7" t="n">
-        <v>41567.88</v>
+      <c r="B97" s="7">
+        <f>SUM(C97,D97,E97,F97)</f>
+        <v/>
       </c>
       <c r="C97" s="7" t="n">
         <v>10391.97</v>
@@ -27038,9 +27040,10 @@
         <f>IFERROR(G89*1,0)-IFERROR(G91*1,0)-IFERROR(G94*1,0)-IFERROR(G95*1,0)</f>
         <v/>
       </c>
-      <c r="H98" s="9">
-        <f>IFERROR(H89*1,0)-IFERROR(H91*1,0)-IFERROR(H94*1,0)-IFERROR(H95*1,0)</f>
-        <v/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="9">
         <f>IFERROR(I89*1,0)-IFERROR(I91*1,0)-IFERROR(I94*1,0)-IFERROR(I95*1,0)</f>
@@ -27088,9 +27091,10 @@
         <f>IFERROR(IF(G4=0,"-",G98/G4),"-")</f>
         <v/>
       </c>
-      <c r="H99" s="10">
-        <f>IFERROR(IF(H4=0,"-",H98/H4),"-")</f>
-        <v/>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="10">
         <f>IFERROR(IF(I4=0,"-",I98/I4),"-")</f>

--- a/budget/output/Сводный бюджет Екатеринбурга.xlsx
+++ b/budget/output/Сводный бюджет Екатеринбурга.xlsx
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>SUM(C5,D5,E5,F5)</f>
+        <f>SUM('Твоя Привелегия'!B5,'Исеть Парк'!B5,'Космонавтов 11'!B5,'Утес'!B5)</f>
         <v/>
       </c>
       <c r="C5" s="7">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B7" s="7">
-        <f>SUM(C7,D7,E7,F7)</f>
+        <f>SUM('Твоя Привелегия'!B7,'Исеть Парк'!B7,'Космонавтов 11'!B7,'Утес'!B7)</f>
         <v/>
       </c>
       <c r="C7" s="7">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>SUM(C8,D8,E8,F8)</f>
+        <f>SUM('Твоя Привелегия'!B8,'Исеть Парк'!B8,'Космонавтов 11'!B8,'Утес'!B8)</f>
         <v/>
       </c>
       <c r="C8" s="7">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>SUM(C9,D9,E9,F9)</f>
+        <f>SUM('Твоя Привелегия'!B9,'Исеть Парк'!B9,'Космонавтов 11'!B9,'Утес'!B9)</f>
         <v/>
       </c>
       <c r="C9" s="7">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>SUM(C11,D11,E11,F11)</f>
+        <f>SUM('Твоя Привелегия'!B11,'Исеть Парк'!B11,'Космонавтов 11'!B11,'Утес'!B11)</f>
         <v/>
       </c>
       <c r="C11" s="7">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>SUM(C12,D12,E12,F12)</f>
+        <f>SUM('Твоя Привелегия'!B12,'Исеть Парк'!B12,'Космонавтов 11'!B12,'Утес'!B12)</f>
         <v/>
       </c>
       <c r="C12" s="7">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>SUM(C14,D14,E14,F14)</f>
+        <f>SUM('Твоя Привелегия'!B14,'Исеть Парк'!B14,'Космонавтов 11'!B14,'Утес'!B14)</f>
         <v/>
       </c>
       <c r="C14" s="7">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B15" s="7">
-        <f>SUM(C15,D15,E15,F15)</f>
+        <f>SUM('Твоя Привелегия'!B15,'Исеть Парк'!B15,'Космонавтов 11'!B15,'Утес'!B15)</f>
         <v/>
       </c>
       <c r="C15" s="7">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="B16" s="7">
-        <f>SUM(C16,D16,E16,F16)</f>
+        <f>SUM('Твоя Привелегия'!B16,'Исеть Парк'!B16,'Космонавтов 11'!B16,'Утес'!B16)</f>
         <v/>
       </c>
       <c r="C16" s="7">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="B17" s="7">
-        <f>SUM(C17,D17,E17,F17)</f>
+        <f>SUM('Твоя Привелегия'!B17,'Исеть Парк'!B17,'Космонавтов 11'!B17,'Утес'!B17)</f>
         <v/>
       </c>
       <c r="C17" s="7">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>SUM(C18,D18,E18,F18)</f>
+        <f>SUM('Твоя Привелегия'!B18,'Исеть Парк'!B18,'Космонавтов 11'!B18,'Утес'!B18)</f>
         <v/>
       </c>
       <c r="C18" s="7">
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>SUM(C19,D19,E19,F19)</f>
+        <f>SUM('Твоя Привелегия'!B19,'Исеть Парк'!B19,'Космонавтов 11'!B19,'Утес'!B19)</f>
         <v/>
       </c>
       <c r="C19" s="7">
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>SUM(C20,D20,E20,F20)</f>
+        <f>SUM('Твоя Привелегия'!B20,'Исеть Парк'!B20,'Космонавтов 11'!B20,'Утес'!B20)</f>
         <v/>
       </c>
       <c r="C20" s="7">
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="B21" s="7">
-        <f>SUM(C21,D21,E21,F21)</f>
+        <f>SUM('Твоя Привелегия'!B21,'Исеть Парк'!B21,'Космонавтов 11'!B21,'Утес'!B21)</f>
         <v/>
       </c>
       <c r="C21" s="7">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B22" s="7">
-        <f>SUM(C22,D22,E22,F22)</f>
+        <f>SUM('Твоя Привелегия'!B22,'Исеть Парк'!B22,'Космонавтов 11'!B22,'Утес'!B22)</f>
         <v/>
       </c>
       <c r="C22" s="7">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="B23" s="7">
-        <f>SUM(C23,D23,E23,F23)</f>
+        <f>SUM('Твоя Привелегия'!B23,'Исеть Парк'!B23,'Космонавтов 11'!B23,'Утес'!B23)</f>
         <v/>
       </c>
       <c r="C23" s="7">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>SUM(C24,D24,E24,F24)</f>
+        <f>SUM('Твоя Привелегия'!B24,'Исеть Парк'!B24,'Космонавтов 11'!B24,'Утес'!B24)</f>
         <v/>
       </c>
       <c r="C24" s="7">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>SUM(C25,D25,E25,F25)</f>
+        <f>SUM('Твоя Привелегия'!B25,'Исеть Парк'!B25,'Космонавтов 11'!B25,'Утес'!B25)</f>
         <v/>
       </c>
       <c r="C25" s="7">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>SUM(C26,D26,E26,F26)</f>
+        <f>SUM('Твоя Привелегия'!B26,'Исеть Парк'!B26,'Космонавтов 11'!B26,'Утес'!B26)</f>
         <v/>
       </c>
       <c r="C26" s="7">
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>SUM(C27,D27,E27,F27)</f>
+        <f>SUM('Твоя Привелегия'!B27,'Исеть Парк'!B27,'Космонавтов 11'!B27,'Утес'!B27)</f>
         <v/>
       </c>
       <c r="C27" s="7">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="B28" s="7">
-        <f>SUM(C28,D28,E28,F28)</f>
+        <f>SUM('Твоя Привелегия'!B28,'Исеть Парк'!B28,'Космонавтов 11'!B28,'Утес'!B28)</f>
         <v/>
       </c>
       <c r="C28" s="7">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="B29" s="7">
-        <f>SUM(C29,D29,E29,F29)</f>
+        <f>SUM('Твоя Привелегия'!B29,'Исеть Парк'!B29,'Космонавтов 11'!B29,'Утес'!B29)</f>
         <v/>
       </c>
       <c r="C29" s="7">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="B30" s="7">
-        <f>SUM(C30,D30,E30,F30)</f>
+        <f>SUM('Твоя Привелегия'!B30,'Исеть Парк'!B30,'Космонавтов 11'!B30,'Утес'!B30)</f>
         <v/>
       </c>
       <c r="C30" s="7">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="B31" s="7">
-        <f>SUM(C31,D31,E31,F31)</f>
+        <f>SUM('Твоя Привелегия'!B31,'Исеть Парк'!B31,'Космонавтов 11'!B31,'Утес'!B31)</f>
         <v/>
       </c>
       <c r="C31" s="7">
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="B32" s="7">
-        <f>SUM(C32,D32,E32,F32)</f>
+        <f>SUM('Твоя Привелегия'!B32,'Исеть Парк'!B32,'Космонавтов 11'!B32,'Утес'!B32)</f>
         <v/>
       </c>
       <c r="C32" s="7">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="B33" s="7">
-        <f>SUM(C33,D33,E33,F33)</f>
+        <f>SUM('Твоя Привелегия'!B33,'Исеть Парк'!B33,'Космонавтов 11'!B33,'Утес'!B33)</f>
         <v/>
       </c>
       <c r="C33" s="7">
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>SUM(C35,D35,E35,F35)</f>
+        <f>SUM('Твоя Привелегия'!B35,'Исеть Парк'!B35,'Космонавтов 11'!B35,'Утес'!B35)</f>
         <v/>
       </c>
       <c r="C35" s="7">
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>SUM(C36,D36,E36,F36)</f>
+        <f>SUM('Твоя Привелегия'!B36,'Исеть Парк'!B36,'Космонавтов 11'!B36,'Утес'!B36)</f>
         <v/>
       </c>
       <c r="C36" s="7">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="B37" s="7">
-        <f>SUM(C37,D37,E37,F37)</f>
+        <f>SUM('Твоя Привелегия'!B37,'Исеть Парк'!B37,'Космонавтов 11'!B37,'Утес'!B37)</f>
         <v/>
       </c>
       <c r="C37" s="7">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>SUM(C38,D38,E38,F38)</f>
+        <f>SUM('Твоя Привелегия'!B38,'Исеть Парк'!B38,'Космонавтов 11'!B38,'Утес'!B38)</f>
         <v/>
       </c>
       <c r="C38" s="7">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="B39" s="7">
-        <f>SUM(C39,D39,E39,F39)</f>
+        <f>SUM('Твоя Привелегия'!B39,'Исеть Парк'!B39,'Космонавтов 11'!B39,'Утес'!B39)</f>
         <v/>
       </c>
       <c r="C39" s="7">
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="B40" s="7">
-        <f>SUM(C40,D40,E40,F40)</f>
+        <f>SUM('Твоя Привелегия'!B40,'Исеть Парк'!B40,'Космонавтов 11'!B40,'Утес'!B40)</f>
         <v/>
       </c>
       <c r="C40" s="7">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="B41" s="7">
-        <f>SUM(C41,D41,E41,F41)</f>
+        <f>SUM('Твоя Привелегия'!B41,'Исеть Парк'!B41,'Космонавтов 11'!B41,'Утес'!B41)</f>
         <v/>
       </c>
       <c r="C41" s="7">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="B42" s="7">
-        <f>SUM(C42,D42,E42,F42)</f>
+        <f>SUM('Твоя Привелегия'!B42,'Исеть Парк'!B42,'Космонавтов 11'!B42,'Утес'!B42)</f>
         <v/>
       </c>
       <c r="C42" s="7">
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="B46" s="7">
-        <f>SUM(C46,D46,E46,F46)</f>
+        <f>SUM('Твоя Привелегия'!B46,'Исеть Парк'!B46,'Космонавтов 11'!B46,'Утес'!B46)</f>
         <v/>
       </c>
       <c r="C46" s="7">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="B47" s="7">
-        <f>SUM(C47,D47,E47,F47)</f>
+        <f>SUM('Твоя Привелегия'!B47,'Исеть Парк'!B47,'Космонавтов 11'!B47,'Утес'!B47)</f>
         <v/>
       </c>
       <c r="C47" s="7">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="B49" s="7">
-        <f>SUM(C49,D49,E49,F49)</f>
+        <f>SUM('Твоя Привелегия'!B49,'Исеть Парк'!B49,'Космонавтов 11'!B49,'Утес'!B49)</f>
         <v/>
       </c>
       <c r="C49" s="7">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="B50" s="7">
-        <f>SUM(C50,D50,E50,F50)</f>
+        <f>SUM('Твоя Привелегия'!B50,'Исеть Парк'!B50,'Космонавтов 11'!B50,'Утес'!B50)</f>
         <v/>
       </c>
       <c r="C50" s="7">
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="B51" s="7">
-        <f>SUM(C51,D51,E51,F51)</f>
+        <f>SUM('Твоя Привелегия'!B51,'Исеть Парк'!B51,'Космонавтов 11'!B51,'Утес'!B51)</f>
         <v/>
       </c>
       <c r="C51" s="7">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="B53" s="7">
-        <f>SUM(C53,D53,E53,F53)</f>
+        <f>SUM('Твоя Привелегия'!B53,'Исеть Парк'!B53,'Космонавтов 11'!B53,'Утес'!B53)</f>
         <v/>
       </c>
       <c r="C53" s="7">
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="B54" s="7">
-        <f>SUM(C54,D54,E54,F54)</f>
+        <f>SUM('Твоя Привелегия'!B54,'Исеть Парк'!B54,'Космонавтов 11'!B54,'Утес'!B54)</f>
         <v/>
       </c>
       <c r="C54" s="7">
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="B55" s="7">
-        <f>SUM(C55,D55,E55,F55)</f>
+        <f>SUM('Твоя Привелегия'!B55,'Исеть Парк'!B55,'Космонавтов 11'!B55,'Утес'!B55)</f>
         <v/>
       </c>
       <c r="C55" s="7">
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="B56" s="7">
-        <f>SUM(C56,D56,E56,F56)</f>
+        <f>SUM('Твоя Привелегия'!B56,'Исеть Парк'!B56,'Космонавтов 11'!B56,'Утес'!B56)</f>
         <v/>
       </c>
       <c r="C56" s="7">
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="B57" s="7">
-        <f>SUM(C57,D57,E57,F57)</f>
+        <f>SUM('Твоя Привелегия'!B57,'Исеть Парк'!B57,'Космонавтов 11'!B57,'Утес'!B57)</f>
         <v/>
       </c>
       <c r="C57" s="7">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="B58" s="7">
-        <f>SUM(C58,D58,E58,F58)</f>
+        <f>SUM('Твоя Привелегия'!B58,'Исеть Парк'!B58,'Космонавтов 11'!B58,'Утес'!B58)</f>
         <v/>
       </c>
       <c r="C58" s="7">
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="B59" s="7">
-        <f>SUM(C59,D59,E59,F59)</f>
+        <f>SUM('Твоя Привелегия'!B59,'Исеть Парк'!B59,'Космонавтов 11'!B59,'Утес'!B59)</f>
         <v/>
       </c>
       <c r="C59" s="7">
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="B61" s="7">
-        <f>SUM(C61,D61,E61,F61)</f>
+        <f>SUM('Твоя Привелегия'!B61,'Исеть Парк'!B61,'Космонавтов 11'!B61,'Утес'!B61)</f>
         <v/>
       </c>
       <c r="C61" s="7">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="B62" s="7">
-        <f>SUM(C62,D62,E62,F62)</f>
+        <f>SUM('Твоя Привелегия'!B62,'Исеть Парк'!B62,'Космонавтов 11'!B62,'Утес'!B62)</f>
         <v/>
       </c>
       <c r="C62" s="7">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="B63" s="7">
-        <f>SUM(C63,D63,E63,F63)</f>
+        <f>SUM('Твоя Привелегия'!B63,'Исеть Парк'!B63,'Космонавтов 11'!B63,'Утес'!B63)</f>
         <v/>
       </c>
       <c r="C63" s="7">
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="B64" s="7">
-        <f>SUM(C64,D64,E64,F64)</f>
+        <f>SUM('Твоя Привелегия'!B64,'Исеть Парк'!B64,'Космонавтов 11'!B64,'Утес'!B64)</f>
         <v/>
       </c>
       <c r="C64" s="7">
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="B65" s="7">
-        <f>SUM(C65,D65,E65,F65)</f>
+        <f>SUM('Твоя Привелегия'!B65,'Исеть Парк'!B65,'Космонавтов 11'!B65,'Утес'!B65)</f>
         <v/>
       </c>
       <c r="C65" s="7">
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="B66" s="7">
-        <f>SUM(C66,D66,E66,F66)</f>
+        <f>SUM('Твоя Привелегия'!B66,'Исеть Парк'!B66,'Космонавтов 11'!B66,'Утес'!B66)</f>
         <v/>
       </c>
       <c r="C66" s="7">
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="B67" s="7">
-        <f>SUM(C67,D67,E67,F67)</f>
+        <f>SUM('Твоя Привелегия'!B67,'Исеть Парк'!B67,'Космонавтов 11'!B67,'Утес'!B67)</f>
         <v/>
       </c>
       <c r="C67" s="7">
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="B68" s="7">
-        <f>SUM(C68,D68,E68,F68)</f>
+        <f>SUM('Твоя Привелегия'!B68,'Исеть Парк'!B68,'Космонавтов 11'!B68,'Утес'!B68)</f>
         <v/>
       </c>
       <c r="C68" s="7">
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B69" s="7">
-        <f>SUM(C69,D69,E69,F69)</f>
+        <f>SUM('Твоя Привелегия'!B69,'Исеть Парк'!B69,'Космонавтов 11'!B69,'Утес'!B69)</f>
         <v/>
       </c>
       <c r="C69" s="7">
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="B70" s="7">
-        <f>SUM(C70,D70,E70,F70)</f>
+        <f>SUM('Твоя Привелегия'!B70,'Исеть Парк'!B70,'Космонавтов 11'!B70,'Утес'!B70)</f>
         <v/>
       </c>
       <c r="C70" s="7">
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="B71" s="7">
-        <f>SUM(C71,D71,E71,F71)</f>
+        <f>SUM('Твоя Привелегия'!B71,'Исеть Парк'!B71,'Космонавтов 11'!B71,'Утес'!B71)</f>
         <v/>
       </c>
       <c r="C71" s="7">
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="B72" s="7">
-        <f>SUM(C72,D72,E72,F72)</f>
+        <f>SUM('Твоя Привелегия'!B72,'Исеть Парк'!B72,'Космонавтов 11'!B72,'Утес'!B72)</f>
         <v/>
       </c>
       <c r="C72" s="7">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="B73" s="7">
-        <f>SUM(C73,D73,E73,F73)</f>
+        <f>SUM('Твоя Привелегия'!B73,'Исеть Парк'!B73,'Космонавтов 11'!B73,'Утес'!B73)</f>
         <v/>
       </c>
       <c r="C73" s="7">
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="B74" s="7">
-        <f>SUM(C74,D74,E74,F74)</f>
+        <f>SUM('Твоя Привелегия'!B74,'Исеть Парк'!B74,'Космонавтов 11'!B74,'Утес'!B74)</f>
         <v/>
       </c>
       <c r="C74" s="7">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="B75" s="7">
-        <f>SUM(C75,D75,E75,F75)</f>
+        <f>SUM('Твоя Привелегия'!B75,'Исеть Парк'!B75,'Космонавтов 11'!B75,'Утес'!B75)</f>
         <v/>
       </c>
       <c r="C75" s="7">
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="B76" s="7">
-        <f>SUM(C76,D76,E76,F76)</f>
+        <f>SUM('Твоя Привелегия'!B76,'Исеть Парк'!B76,'Космонавтов 11'!B76,'Утес'!B76)</f>
         <v/>
       </c>
       <c r="C76" s="7">
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="B77" s="7">
-        <f>SUM(C77,D77,E77,F77)</f>
+        <f>SUM('Твоя Привелегия'!B77,'Исеть Парк'!B77,'Космонавтов 11'!B77,'Утес'!B77)</f>
         <v/>
       </c>
       <c r="C77" s="7">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="B78" s="7">
-        <f>SUM(C78,D78,E78,F78)</f>
+        <f>SUM('Твоя Привелегия'!B78,'Исеть Парк'!B78,'Космонавтов 11'!B78,'Утес'!B78)</f>
         <v/>
       </c>
       <c r="C78" s="7">
@@ -4482,7 +4482,7 @@
         </is>
       </c>
       <c r="B79" s="7">
-        <f>SUM(C79,D79,E79,F79)</f>
+        <f>SUM('Твоя Привелегия'!B79,'Исеть Парк'!B79,'Космонавтов 11'!B79,'Утес'!B79)</f>
         <v/>
       </c>
       <c r="C79" s="7">
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="B83" s="7">
-        <f>SUM(C83,D83,E83,F83)</f>
+        <f>SUM('Твоя Привелегия'!B83,'Исеть Парк'!B83,'Космонавтов 11'!B83,'Утес'!B83)</f>
         <v/>
       </c>
       <c r="C83" s="7">
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="B84" s="7">
-        <f>SUM(C84,D84,E84,F84)</f>
+        <f>SUM('Твоя Привелегия'!B84,'Исеть Парк'!B84,'Космонавтов 11'!B84,'Утес'!B84)</f>
         <v/>
       </c>
       <c r="C84" s="7">
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="B85" s="7">
-        <f>SUM(C85,D85,E85,F85)</f>
+        <f>SUM('Твоя Привелегия'!B85,'Исеть Парк'!B85,'Космонавтов 11'!B85,'Утес'!B85)</f>
         <v/>
       </c>
       <c r="C85" s="7">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="B86" s="7">
-        <f>SUM(C86,D86,E86,F86)</f>
+        <f>SUM('Твоя Привелегия'!B86,'Исеть Парк'!B86,'Космонавтов 11'!B86,'Утес'!B86)</f>
         <v/>
       </c>
       <c r="C86" s="7">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="B88" s="7">
-        <f>SUM(C88,D88,E88,F88)</f>
+        <f>SUM('Твоя Привелегия'!B88,'Исеть Парк'!B88,'Космонавтов 11'!B88,'Утес'!B88)</f>
         <v/>
       </c>
       <c r="C88" s="7">
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="B92" s="7">
-        <f>SUM(C92,D92,E92,F92)</f>
+        <f>SUM('Твоя Привелегия'!B92,'Исеть Парк'!B92,'Космонавтов 11'!B92,'Утес'!B92)</f>
         <v/>
       </c>
       <c r="C92" s="7">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="B93" s="7">
-        <f>SUM(C93,D93,E93,F93)</f>
+        <f>SUM('Твоя Привелегия'!B93,'Исеть Парк'!B93,'Космонавтов 11'!B93,'Утес'!B93)</f>
         <v/>
       </c>
       <c r="C93" s="7">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="B94" s="7">
-        <f>SUM(C94,D94,E94,F94)</f>
+        <f>SUM('Твоя Привелегия'!B94,'Исеть Парк'!B94,'Космонавтов 11'!B94,'Утес'!B94)</f>
         <v/>
       </c>
       <c r="C94" s="7">
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="B96" s="7">
-        <f>SUM(C96,D96,E96,F96)</f>
+        <f>SUM('Твоя Привелегия'!B96,'Исеть Парк'!B96,'Космонавтов 11'!B96,'Утес'!B96)</f>
         <v/>
       </c>
       <c r="C96" s="7">
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="B97" s="7">
-        <f>SUM(C97,D97,E97,F97)</f>
+        <f>SUM('Твоя Привелегия'!B97,'Исеть Парк'!B97,'Космонавтов 11'!B97,'Утес'!B97)</f>
         <v/>
       </c>
       <c r="C97" s="7">
@@ -5711,9 +5711,8 @@
           <t>Выручка</t>
         </is>
       </c>
-      <c r="B4" s="7">
-        <f>SUM(B5,B6)</f>
-        <v/>
+      <c r="B4" s="7" t="n">
+        <v>3590716.24</v>
       </c>
       <c r="C4" s="7">
         <f>SUM(C5,C6)</f>
@@ -5762,9 +5761,10 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7">
-        <f>SUM(C5,D5,E5,F5)</f>
-        <v/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -5819,9 +5819,8 @@
           <t xml:space="preserve">    Выручка </t>
         </is>
       </c>
-      <c r="B6" s="7">
-        <f>SUM(B7,B8,B9)</f>
-        <v/>
+      <c r="B6" s="7" t="n">
+        <v>3590716.24</v>
       </c>
       <c r="C6" s="7">
         <f>SUM(C7,C8,C9)</f>
@@ -5870,9 +5869,8 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7">
-        <f>SUM(C7,D7,E7,F7)</f>
-        <v/>
+      <c r="B7" s="7" t="n">
+        <v>3590716.24</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>897679.0600000001</v>
@@ -5919,9 +5917,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7">
-        <f>SUM(C8,D8,E8,F8)</f>
-        <v/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -5976,9 +5975,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7">
-        <f>SUM(C9,D9,E9,F9)</f>
-        <v/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -6033,9 +6033,8 @@
           <t>Прямые расходы</t>
         </is>
       </c>
-      <c r="B10" s="7">
-        <f>SUM(B11,B12,B13,B21,B22,B23,B24,B25,B26,B27,B28,B29,B30,B31,B32,B33,B34)</f>
-        <v/>
+      <c r="B10" s="7" t="n">
+        <v>2622334</v>
       </c>
       <c r="C10" s="7">
         <f>SUM(C11,C12,C13,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34)</f>
@@ -6084,9 +6083,10 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7">
-        <f>SUM(C11,D11,E11,F11)</f>
-        <v/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -6141,9 +6141,8 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7">
-        <f>SUM(C12,D12,E12,F12)</f>
-        <v/>
+      <c r="B12" s="7" t="n">
+        <v>1080</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>1080</v>
@@ -6196,9 +6195,8 @@
           <t xml:space="preserve">    Переменные</t>
         </is>
       </c>
-      <c r="B13" s="7">
-        <f>SUM(B14,B15,B16,B17,B18,B19,B20)</f>
-        <v/>
+      <c r="B13" s="7" t="n">
+        <v>269530.5</v>
       </c>
       <c r="C13" s="7">
         <f>SUM(C14,C15,C16,C17,C18,C19,C20)</f>
@@ -6247,9 +6245,10 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7">
-        <f>SUM(C14,D14,E14,F14)</f>
-        <v/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -6304,9 +6303,8 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(C15,D15,E15,F15)</f>
-        <v/>
+      <c r="B15" s="7" t="n">
+        <v>184000</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>46000</v>
@@ -6353,9 +6351,8 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(C16,D16,E16,F16)</f>
-        <v/>
+      <c r="B16" s="7" t="n">
+        <v>18000</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>18000</v>
@@ -6408,9 +6405,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7">
-        <f>SUM(C17,D17,E17,F17)</f>
-        <v/>
+      <c r="B17" s="7" t="n">
+        <v>32095</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>2095</v>
@@ -6457,9 +6453,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>SUM(C18,D18,E18,F18)</f>
-        <v/>
+      <c r="B18" s="7" t="n">
+        <v>35435.5</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>5435.5</v>
@@ -6506,9 +6501,10 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>SUM(C19,D19,E19,F19)</f>
-        <v/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -6563,9 +6559,10 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>SUM(C20,D20,E20,F20)</f>
-        <v/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -6620,9 +6617,8 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>SUM(C21,D21,E21,F21)</f>
-        <v/>
+      <c r="B21" s="7" t="n">
+        <v>1040000</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>260000</v>
@@ -6669,9 +6665,8 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>SUM(C22,D22,E22,F22)</f>
-        <v/>
+      <c r="B22" s="7" t="n">
+        <v>777600</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>194400</v>
@@ -6718,9 +6713,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>SUM(C23,D23,E23,F23)</f>
-        <v/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -6775,9 +6771,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>SUM(C24,D24,E24,F24)</f>
-        <v/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -6832,9 +6829,8 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>SUM(C25,D25,E25,F25)</f>
-        <v/>
+      <c r="B25" s="7" t="n">
+        <v>10000</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>10000</v>
@@ -6887,9 +6883,10 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>SUM(C26,D26,E26,F26)</f>
-        <v/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -6944,9 +6941,10 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7">
-        <f>SUM(C27,D27,E27,F27)</f>
-        <v/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -7001,9 +6999,10 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7">
-        <f>SUM(C28,D28,E28,F28)</f>
-        <v/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -7058,9 +7057,10 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7">
-        <f>SUM(C29,D29,E29,F29)</f>
-        <v/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -7115,9 +7115,10 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7">
-        <f>SUM(C30,D30,E30,F30)</f>
-        <v/>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -7172,9 +7173,10 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7">
-        <f>SUM(C31,D31,E31,F31)</f>
-        <v/>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -7229,9 +7231,10 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>SUM(C32,D32,E32,F32)</f>
-        <v/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -7286,9 +7289,10 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>SUM(C33,D33,E33,F33)</f>
-        <v/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -7343,9 +7347,8 @@
           <t xml:space="preserve">    Общехозяйственные</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>SUM(B35,B36,B37,B38,B39,B40,B41,B42)</f>
-        <v/>
+      <c r="B34" s="7" t="n">
+        <v>524123.5</v>
       </c>
       <c r="C34" s="7">
         <f>SUM(C35,C36,C37,C38,C39,C40,C41,C42)</f>
@@ -7394,9 +7397,8 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>SUM(C35,D35,E35,F35)</f>
-        <v/>
+      <c r="B35" s="7" t="n">
+        <v>10000</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>2500</v>
@@ -7443,9 +7445,8 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7">
-        <f>SUM(C36,D36,E36,F36)</f>
-        <v/>
+      <c r="B36" s="7" t="n">
+        <v>260000</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>65000</v>
@@ -7492,9 +7493,8 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7">
-        <f>SUM(C37,D37,E37,F37)</f>
-        <v/>
+      <c r="B37" s="7" t="n">
+        <v>26123.5</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>5123.5</v>
@@ -7541,9 +7541,10 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7">
-        <f>SUM(C38,D38,E38,F38)</f>
-        <v/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -7598,9 +7599,8 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7">
-        <f>SUM(C39,D39,E39,F39)</f>
-        <v/>
+      <c r="B39" s="7" t="n">
+        <v>224000</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>56000</v>
@@ -7647,9 +7647,10 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>SUM(C40,D40,E40,F40)</f>
-        <v/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -7704,9 +7705,8 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>SUM(C41,D41,E41,F41)</f>
-        <v/>
+      <c r="B41" s="7" t="n">
+        <v>4000</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>1000</v>
@@ -7753,9 +7753,10 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>SUM(C42,D42,E42,F42)</f>
-        <v/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -7810,9 +7811,8 @@
           <t>Валовая прибыль</t>
         </is>
       </c>
-      <c r="B43" s="9">
-        <f>B4-B10</f>
-        <v/>
+      <c r="B43" s="9" t="n">
+        <v>968382.2400000002</v>
       </c>
       <c r="C43" s="9">
         <f>C4-C10</f>
@@ -7861,9 +7861,10 @@
           <t>Валовая рентабельность</t>
         </is>
       </c>
-      <c r="B44" s="10">
-        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
-        <v/>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>26.97%</t>
+        </is>
       </c>
       <c r="C44" s="10">
         <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
@@ -7912,9 +7913,8 @@
           <t>Косвенные расходы</t>
         </is>
       </c>
-      <c r="B45" s="7">
-        <f>SUM(B46,B47,B48,B52,B56,B57,B58,B59,B60,B63,B64,B65,B66,B67,B68,B69,B70,B71,B72,B73,B74,B75,B76,B77,B78,B79)</f>
-        <v/>
+      <c r="B45" s="7" t="n">
+        <v>269881.08</v>
       </c>
       <c r="C45" s="7">
         <f>SUM(C46,C47,C48,C52,C56,C57,C58,C59,C60,C63,C64,C65,C66,C67,C68,C69,C70,C71,C72,C73,C74,C75,C76,C77,C78,C79)</f>
@@ -7963,9 +7963,8 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7">
-        <f>SUM(C46,D46,E46,F46)</f>
-        <v/>
+      <c r="B46" s="7" t="n">
+        <v>269881.08</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>67470.27</v>
@@ -8012,9 +8011,10 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7">
-        <f>SUM(C47,D47,E47,F47)</f>
-        <v/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -8069,9 +8069,10 @@
           <t xml:space="preserve">    Автомобиль</t>
         </is>
       </c>
-      <c r="B48" s="7">
-        <f>SUM(B49,B50,B51)</f>
-        <v/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C48" s="7">
         <f>SUM(C49,C50,C51)</f>
@@ -8120,9 +8121,10 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7">
-        <f>SUM(C49,D49,E49,F49)</f>
-        <v/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -8177,9 +8179,10 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7">
-        <f>SUM(C50,D50,E50,F50)</f>
-        <v/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -8234,9 +8237,10 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7">
-        <f>SUM(C51,D51,E51,F51)</f>
-        <v/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -8291,9 +8295,10 @@
           <t xml:space="preserve">    Офисные расходы</t>
         </is>
       </c>
-      <c r="B52" s="7">
-        <f>SUM(B53,B54,B55)</f>
-        <v/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C52" s="7">
         <f>SUM(C53,C54,C55)</f>
@@ -8342,9 +8347,10 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7">
-        <f>SUM(C53,D53,E53,F53)</f>
-        <v/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -8399,9 +8405,10 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7">
-        <f>SUM(C54,D54,E54,F54)</f>
-        <v/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -8456,9 +8463,10 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7">
-        <f>SUM(C55,D55,E55,F55)</f>
-        <v/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -8513,9 +8521,10 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7">
-        <f>SUM(C56,D56,E56,F56)</f>
-        <v/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -8570,9 +8579,10 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7">
-        <f>SUM(C57,D57,E57,F57)</f>
-        <v/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -8627,9 +8637,10 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7">
-        <f>SUM(C58,D58,E58,F58)</f>
-        <v/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -8684,9 +8695,10 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7">
-        <f>SUM(C59,D59,E59,F59)</f>
-        <v/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -8741,9 +8753,10 @@
           <t xml:space="preserve">    Командировочные расходы</t>
         </is>
       </c>
-      <c r="B60" s="7">
-        <f>SUM(B61,B62)</f>
-        <v/>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C60" s="7">
         <f>SUM(C61,C62)</f>
@@ -8792,9 +8805,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7">
-        <f>SUM(C61,D61,E61,F61)</f>
-        <v/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -8849,9 +8863,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7">
-        <f>SUM(C62,D62,E62,F62)</f>
-        <v/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -8906,9 +8921,10 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7">
-        <f>SUM(C63,D63,E63,F63)</f>
-        <v/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -8963,9 +8979,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7">
-        <f>SUM(C64,D64,E64,F64)</f>
-        <v/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -9020,9 +9037,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7">
-        <f>SUM(C65,D65,E65,F65)</f>
-        <v/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -9077,9 +9095,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7">
-        <f>SUM(C66,D66,E66,F66)</f>
-        <v/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -9134,9 +9153,10 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7">
-        <f>SUM(C67,D67,E67,F67)</f>
-        <v/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -9191,9 +9211,10 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7">
-        <f>SUM(C68,D68,E68,F68)</f>
-        <v/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -9248,9 +9269,10 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7">
-        <f>SUM(C69,D69,E69,F69)</f>
-        <v/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -9305,9 +9327,10 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7">
-        <f>SUM(C70,D70,E70,F70)</f>
-        <v/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -9362,9 +9385,10 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7">
-        <f>SUM(C71,D71,E71,F71)</f>
-        <v/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -9419,9 +9443,10 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7">
-        <f>SUM(C72,D72,E72,F72)</f>
-        <v/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -9476,9 +9501,10 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7">
-        <f>SUM(C73,D73,E73,F73)</f>
-        <v/>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -9533,9 +9559,10 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7">
-        <f>SUM(C74,D74,E74,F74)</f>
-        <v/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -9590,9 +9617,10 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7">
-        <f>SUM(C75,D75,E75,F75)</f>
-        <v/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -9647,9 +9675,10 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7">
-        <f>SUM(C76,D76,E76,F76)</f>
-        <v/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -9704,9 +9733,10 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7">
-        <f>SUM(C77,D77,E77,F77)</f>
-        <v/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -9761,9 +9791,10 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7">
-        <f>SUM(C78,D78,E78,F78)</f>
-        <v/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -9818,9 +9849,10 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7">
-        <f>SUM(C79,D79,E79,F79)</f>
-        <v/>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -9875,9 +9907,8 @@
           <t>Операционная прибыль</t>
         </is>
       </c>
-      <c r="B80" s="9">
-        <f>B43-B45</f>
-        <v/>
+      <c r="B80" s="9" t="n">
+        <v>698501.1600000001</v>
       </c>
       <c r="C80" s="9">
         <f>C43-C45</f>
@@ -9926,9 +9957,10 @@
           <t>Операционная рентабельность</t>
         </is>
       </c>
-      <c r="B81" s="10">
-        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
-        <v/>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>19.45%</t>
+        </is>
       </c>
       <c r="C81" s="10">
         <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
@@ -9977,9 +10009,10 @@
           <t>Прочие доходы</t>
         </is>
       </c>
-      <c r="B82" s="7">
-        <f>SUM(B83,B84,B85,B86)</f>
-        <v/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C82" s="7">
         <f>SUM(C83,C84,C85,C86)</f>
@@ -10028,9 +10061,10 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7">
-        <f>SUM(C83,D83,E83,F83)</f>
-        <v/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -10085,9 +10119,10 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7">
-        <f>SUM(C84,D84,E84,F84)</f>
-        <v/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -10142,9 +10177,10 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7">
-        <f>SUM(C85,D85,E85,F85)</f>
-        <v/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -10199,9 +10235,10 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7">
-        <f>SUM(C86,D86,E86,F86)</f>
-        <v/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -10256,9 +10293,10 @@
           <t>Прочие расходы</t>
         </is>
       </c>
-      <c r="B87" s="7">
-        <f>SUM(B88)</f>
-        <v/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C87" s="7">
         <f>SUM(C88)</f>
@@ -10307,9 +10345,10 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7">
-        <f>SUM(C88,D88,E88,F88)</f>
-        <v/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -10364,9 +10403,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B89" s="9">
-        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
-        <v/>
+      <c r="B89" s="9" t="n">
+        <v>698501.1600000001</v>
       </c>
       <c r="C89" s="9">
         <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
@@ -10415,9 +10453,10 @@
           <t>Рентабельность по EBITDA</t>
         </is>
       </c>
-      <c r="B90" s="10">
-        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
-        <v/>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>19.45%</t>
+        </is>
       </c>
       <c r="C90" s="10">
         <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
@@ -10466,9 +10505,10 @@
           <t>Амортизация</t>
         </is>
       </c>
-      <c r="B91" s="7">
-        <f>SUM(B92,B93)</f>
-        <v/>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C91" s="7">
         <f>SUM(C92,C93)</f>
@@ -10517,9 +10557,10 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7">
-        <f>SUM(C92,D92,E92,F92)</f>
-        <v/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -10574,9 +10615,10 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7">
-        <f>SUM(C93,D93,E93,F93)</f>
-        <v/>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -10631,9 +10673,10 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7">
-        <f>SUM(C94,D94,E94,F94)</f>
-        <v/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -10688,9 +10731,8 @@
           <t>Налог на прибыль</t>
         </is>
       </c>
-      <c r="B95" s="7">
-        <f>SUM(B96,B97)</f>
-        <v/>
+      <c r="B95" s="7" t="n">
+        <v>271789.84</v>
       </c>
       <c r="C95" s="7">
         <f>SUM(C96,C97)</f>
@@ -10739,9 +10781,8 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7">
-        <f>SUM(C96,D96,E96,F96)</f>
-        <v/>
+      <c r="B96" s="7" t="n">
+        <v>54000</v>
       </c>
       <c r="C96" s="7" t="n">
         <v>13500</v>
@@ -10788,9 +10829,8 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7">
-        <f>SUM(C97,D97,E97,F97)</f>
-        <v/>
+      <c r="B97" s="7" t="n">
+        <v>217789.84</v>
       </c>
       <c r="C97" s="7" t="n">
         <v>54447.46</v>
@@ -10837,9 +10877,8 @@
           <t>Чистая прибыль (убыток)</t>
         </is>
       </c>
-      <c r="B98" s="9">
-        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
-        <v/>
+      <c r="B98" s="9" t="n">
+        <v>426711.3200000002</v>
       </c>
       <c r="C98" s="9">
         <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
@@ -10888,9 +10927,10 @@
           <t>Рентабельность чистой прибыли</t>
         </is>
       </c>
-      <c r="B99" s="10">
-        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
-        <v/>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>11.88%</t>
+        </is>
       </c>
       <c r="C99" s="10">
         <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
@@ -11098,9 +11138,8 @@
           <t>Выручка</t>
         </is>
       </c>
-      <c r="B4" s="7">
-        <f>SUM(B5,B6)</f>
-        <v/>
+      <c r="B4" s="7" t="n">
+        <v>2998544</v>
       </c>
       <c r="C4" s="7">
         <f>SUM(C5,C6)</f>
@@ -11149,9 +11188,10 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7">
-        <f>SUM(C5,D5,E5,F5)</f>
-        <v/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -11206,9 +11246,8 @@
           <t xml:space="preserve">    Выручка </t>
         </is>
       </c>
-      <c r="B6" s="7">
-        <f>SUM(B7,B8,B9)</f>
-        <v/>
+      <c r="B6" s="7" t="n">
+        <v>2998544</v>
       </c>
       <c r="C6" s="7">
         <f>SUM(C7,C8,C9)</f>
@@ -11257,9 +11296,8 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7">
-        <f>SUM(C7,D7,E7,F7)</f>
-        <v/>
+      <c r="B7" s="7" t="n">
+        <v>2998544</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>749636</v>
@@ -11306,9 +11344,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7">
-        <f>SUM(C8,D8,E8,F8)</f>
-        <v/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -11363,9 +11402,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7">
-        <f>SUM(C9,D9,E9,F9)</f>
-        <v/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -11420,9 +11460,8 @@
           <t>Прямые расходы</t>
         </is>
       </c>
-      <c r="B10" s="7">
-        <f>SUM(B11,B12,B13,B21,B22,B23,B24,B25,B26,B27,B28,B29,B30,B31,B32,B33,B34)</f>
-        <v/>
+      <c r="B10" s="7" t="n">
+        <v>1816868.9</v>
       </c>
       <c r="C10" s="7">
         <f>SUM(C11,C12,C13,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34)</f>
@@ -11471,9 +11510,10 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7">
-        <f>SUM(C11,D11,E11,F11)</f>
-        <v/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -11528,9 +11568,10 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7">
-        <f>SUM(C12,D12,E12,F12)</f>
-        <v/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -11585,9 +11626,8 @@
           <t xml:space="preserve">    Переменные</t>
         </is>
       </c>
-      <c r="B13" s="7">
-        <f>SUM(B14,B15,B16,B17,B18,B19,B20)</f>
-        <v/>
+      <c r="B13" s="7" t="n">
+        <v>38868.9</v>
       </c>
       <c r="C13" s="7">
         <f>SUM(C14,C15,C16,C17,C18,C19,C20)</f>
@@ -11636,9 +11676,10 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7">
-        <f>SUM(C14,D14,E14,F14)</f>
-        <v/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -11693,9 +11734,10 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(C15,D15,E15,F15)</f>
-        <v/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -11750,9 +11792,10 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(C16,D16,E16,F16)</f>
-        <v/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -11807,9 +11850,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7">
-        <f>SUM(C17,D17,E17,F17)</f>
-        <v/>
+      <c r="B17" s="7" t="n">
+        <v>19356.4</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>4356.4</v>
@@ -11856,9 +11898,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>SUM(C18,D18,E18,F18)</f>
-        <v/>
+      <c r="B18" s="7" t="n">
+        <v>19512.5</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>4512.5</v>
@@ -11905,9 +11946,10 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>SUM(C19,D19,E19,F19)</f>
-        <v/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -11962,9 +12004,10 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>SUM(C20,D20,E20,F20)</f>
-        <v/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -12019,9 +12062,8 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>SUM(C21,D21,E21,F21)</f>
-        <v/>
+      <c r="B21" s="7" t="n">
+        <v>512000</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>128000</v>
@@ -12068,9 +12110,8 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>SUM(C22,D22,E22,F22)</f>
-        <v/>
+      <c r="B22" s="7" t="n">
+        <v>840000</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>210000</v>
@@ -12117,9 +12158,8 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>SUM(C23,D23,E23,F23)</f>
-        <v/>
+      <c r="B23" s="7" t="n">
+        <v>56000</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>14000</v>
@@ -12166,9 +12206,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>SUM(C24,D24,E24,F24)</f>
-        <v/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -12223,9 +12264,10 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>SUM(C25,D25,E25,F25)</f>
-        <v/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -12280,9 +12322,10 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>SUM(C26,D26,E26,F26)</f>
-        <v/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -12337,9 +12380,8 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7">
-        <f>SUM(C27,D27,E27,F27)</f>
-        <v/>
+      <c r="B27" s="7" t="n">
+        <v>10000</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>10000</v>
@@ -12392,9 +12434,10 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7">
-        <f>SUM(C28,D28,E28,F28)</f>
-        <v/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -12449,9 +12492,10 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7">
-        <f>SUM(C29,D29,E29,F29)</f>
-        <v/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -12506,9 +12550,8 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7">
-        <f>SUM(C30,D30,E30,F30)</f>
-        <v/>
+      <c r="B30" s="7" t="n">
+        <v>8000</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>2000</v>
@@ -12555,9 +12598,10 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7">
-        <f>SUM(C31,D31,E31,F31)</f>
-        <v/>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -12612,9 +12656,10 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>SUM(C32,D32,E32,F32)</f>
-        <v/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -12669,9 +12714,10 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>SUM(C33,D33,E33,F33)</f>
-        <v/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -12726,9 +12772,8 @@
           <t xml:space="preserve">    Общехозяйственные</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>SUM(B35,B36,B37,B38,B39,B40,B41,B42)</f>
-        <v/>
+      <c r="B34" s="7" t="n">
+        <v>352000</v>
       </c>
       <c r="C34" s="7">
         <f>SUM(C35,C36,C37,C38,C39,C40,C41,C42)</f>
@@ -12777,9 +12822,10 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>SUM(C35,D35,E35,F35)</f>
-        <v/>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -12834,9 +12880,8 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7">
-        <f>SUM(C36,D36,E36,F36)</f>
-        <v/>
+      <c r="B36" s="7" t="n">
+        <v>240000</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>60000</v>
@@ -12883,9 +12928,8 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7">
-        <f>SUM(C37,D37,E37,F37)</f>
-        <v/>
+      <c r="B37" s="7" t="n">
+        <v>4000</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>1000</v>
@@ -12932,9 +12976,10 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7">
-        <f>SUM(C38,D38,E38,F38)</f>
-        <v/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -12989,9 +13034,8 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7">
-        <f>SUM(C39,D39,E39,F39)</f>
-        <v/>
+      <c r="B39" s="7" t="n">
+        <v>104000</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>26000</v>
@@ -13038,9 +13082,10 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>SUM(C40,D40,E40,F40)</f>
-        <v/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -13095,9 +13140,8 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>SUM(C41,D41,E41,F41)</f>
-        <v/>
+      <c r="B41" s="7" t="n">
+        <v>4000</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>1000</v>
@@ -13144,9 +13188,10 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>SUM(C42,D42,E42,F42)</f>
-        <v/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -13201,9 +13246,8 @@
           <t>Валовая прибыль</t>
         </is>
       </c>
-      <c r="B43" s="9">
-        <f>B4-B10</f>
-        <v/>
+      <c r="B43" s="9" t="n">
+        <v>1181675.1</v>
       </c>
       <c r="C43" s="9">
         <f>C4-C10</f>
@@ -13252,9 +13296,10 @@
           <t>Валовая рентабельность</t>
         </is>
       </c>
-      <c r="B44" s="10">
-        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
-        <v/>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>39.41%</t>
+        </is>
       </c>
       <c r="C44" s="10">
         <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
@@ -13303,9 +13348,8 @@
           <t>Косвенные расходы</t>
         </is>
       </c>
-      <c r="B45" s="7">
-        <f>SUM(B46,B47,B48,B52,B56,B57,B58,B59,B60,B63,B64,B65,B66,B67,B68,B69,B70,B71,B72,B73,B74,B75,B76,B77,B78,B79)</f>
-        <v/>
+      <c r="B45" s="7" t="n">
+        <v>334040.8</v>
       </c>
       <c r="C45" s="7">
         <f>SUM(C46,C47,C48,C52,C56,C57,C58,C59,C60,C63,C64,C65,C66,C67,C68,C69,C70,C71,C72,C73,C74,C75,C76,C77,C78,C79)</f>
@@ -13354,9 +13398,8 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7">
-        <f>SUM(C46,D46,E46,F46)</f>
-        <v/>
+      <c r="B46" s="7" t="n">
+        <v>334040.8</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>83510.2</v>
@@ -13403,9 +13446,10 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7">
-        <f>SUM(C47,D47,E47,F47)</f>
-        <v/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -13460,9 +13504,10 @@
           <t xml:space="preserve">    Автомобиль</t>
         </is>
       </c>
-      <c r="B48" s="7">
-        <f>SUM(B49,B50,B51)</f>
-        <v/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C48" s="7">
         <f>SUM(C49,C50,C51)</f>
@@ -13511,9 +13556,10 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7">
-        <f>SUM(C49,D49,E49,F49)</f>
-        <v/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -13568,9 +13614,10 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7">
-        <f>SUM(C50,D50,E50,F50)</f>
-        <v/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -13625,9 +13672,10 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7">
-        <f>SUM(C51,D51,E51,F51)</f>
-        <v/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -13682,9 +13730,10 @@
           <t xml:space="preserve">    Офисные расходы</t>
         </is>
       </c>
-      <c r="B52" s="7">
-        <f>SUM(B53,B54,B55)</f>
-        <v/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C52" s="7">
         <f>SUM(C53,C54,C55)</f>
@@ -13733,9 +13782,10 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7">
-        <f>SUM(C53,D53,E53,F53)</f>
-        <v/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -13790,9 +13840,10 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7">
-        <f>SUM(C54,D54,E54,F54)</f>
-        <v/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -13847,9 +13898,10 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7">
-        <f>SUM(C55,D55,E55,F55)</f>
-        <v/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -13904,9 +13956,10 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7">
-        <f>SUM(C56,D56,E56,F56)</f>
-        <v/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -13961,9 +14014,10 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7">
-        <f>SUM(C57,D57,E57,F57)</f>
-        <v/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -14018,9 +14072,10 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7">
-        <f>SUM(C58,D58,E58,F58)</f>
-        <v/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -14075,9 +14130,10 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7">
-        <f>SUM(C59,D59,E59,F59)</f>
-        <v/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -14132,9 +14188,10 @@
           <t xml:space="preserve">    Командировочные расходы</t>
         </is>
       </c>
-      <c r="B60" s="7">
-        <f>SUM(B61,B62)</f>
-        <v/>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C60" s="7">
         <f>SUM(C61,C62)</f>
@@ -14183,9 +14240,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7">
-        <f>SUM(C61,D61,E61,F61)</f>
-        <v/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -14240,9 +14298,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7">
-        <f>SUM(C62,D62,E62,F62)</f>
-        <v/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -14297,9 +14356,10 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7">
-        <f>SUM(C63,D63,E63,F63)</f>
-        <v/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -14354,9 +14414,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7">
-        <f>SUM(C64,D64,E64,F64)</f>
-        <v/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -14411,9 +14472,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7">
-        <f>SUM(C65,D65,E65,F65)</f>
-        <v/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -14468,9 +14530,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7">
-        <f>SUM(C66,D66,E66,F66)</f>
-        <v/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -14525,9 +14588,10 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7">
-        <f>SUM(C67,D67,E67,F67)</f>
-        <v/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -14582,9 +14646,10 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7">
-        <f>SUM(C68,D68,E68,F68)</f>
-        <v/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -14639,9 +14704,10 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7">
-        <f>SUM(C69,D69,E69,F69)</f>
-        <v/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -14696,9 +14762,10 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7">
-        <f>SUM(C70,D70,E70,F70)</f>
-        <v/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -14753,9 +14820,10 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7">
-        <f>SUM(C71,D71,E71,F71)</f>
-        <v/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -14810,9 +14878,10 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7">
-        <f>SUM(C72,D72,E72,F72)</f>
-        <v/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -14867,9 +14936,10 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7">
-        <f>SUM(C73,D73,E73,F73)</f>
-        <v/>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -14924,9 +14994,10 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7">
-        <f>SUM(C74,D74,E74,F74)</f>
-        <v/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -14981,9 +15052,10 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7">
-        <f>SUM(C75,D75,E75,F75)</f>
-        <v/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -15038,9 +15110,10 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7">
-        <f>SUM(C76,D76,E76,F76)</f>
-        <v/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -15095,9 +15168,10 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7">
-        <f>SUM(C77,D77,E77,F77)</f>
-        <v/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -15152,9 +15226,10 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7">
-        <f>SUM(C78,D78,E78,F78)</f>
-        <v/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -15209,9 +15284,10 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7">
-        <f>SUM(C79,D79,E79,F79)</f>
-        <v/>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -15266,9 +15342,8 @@
           <t>Операционная прибыль</t>
         </is>
       </c>
-      <c r="B80" s="9">
-        <f>B43-B45</f>
-        <v/>
+      <c r="B80" s="9" t="n">
+        <v>847634.3</v>
       </c>
       <c r="C80" s="9">
         <f>C43-C45</f>
@@ -15317,9 +15392,10 @@
           <t>Операционная рентабельность</t>
         </is>
       </c>
-      <c r="B81" s="10">
-        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
-        <v/>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>28.27%</t>
+        </is>
       </c>
       <c r="C81" s="10">
         <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
@@ -15368,9 +15444,10 @@
           <t>Прочие доходы</t>
         </is>
       </c>
-      <c r="B82" s="7">
-        <f>SUM(B83,B84,B85,B86)</f>
-        <v/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C82" s="7">
         <f>SUM(C83,C84,C85,C86)</f>
@@ -15419,9 +15496,10 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7">
-        <f>SUM(C83,D83,E83,F83)</f>
-        <v/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -15476,9 +15554,10 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7">
-        <f>SUM(C84,D84,E84,F84)</f>
-        <v/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -15533,9 +15612,10 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7">
-        <f>SUM(C85,D85,E85,F85)</f>
-        <v/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -15590,9 +15670,10 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7">
-        <f>SUM(C86,D86,E86,F86)</f>
-        <v/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -15647,9 +15728,10 @@
           <t>Прочие расходы</t>
         </is>
       </c>
-      <c r="B87" s="7">
-        <f>SUM(B88)</f>
-        <v/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C87" s="7">
         <f>SUM(C88)</f>
@@ -15698,9 +15780,10 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7">
-        <f>SUM(C88,D88,E88,F88)</f>
-        <v/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -15755,9 +15838,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B89" s="9">
-        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
-        <v/>
+      <c r="B89" s="9" t="n">
+        <v>847634.3</v>
       </c>
       <c r="C89" s="9">
         <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
@@ -15806,9 +15888,10 @@
           <t>Рентабельность по EBITDA</t>
         </is>
       </c>
-      <c r="B90" s="10">
-        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
-        <v/>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>28.27%</t>
+        </is>
       </c>
       <c r="C90" s="10">
         <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
@@ -15857,9 +15940,10 @@
           <t>Амортизация</t>
         </is>
       </c>
-      <c r="B91" s="7">
-        <f>SUM(B92,B93)</f>
-        <v/>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C91" s="7">
         <f>SUM(C92,C93)</f>
@@ -15908,9 +15992,10 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7">
-        <f>SUM(C92,D92,E92,F92)</f>
-        <v/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -15965,9 +16050,10 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7">
-        <f>SUM(C93,D93,E93,F93)</f>
-        <v/>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -16022,9 +16108,10 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7">
-        <f>SUM(C94,D94,E94,F94)</f>
-        <v/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -16079,9 +16166,8 @@
           <t>Налог на прибыль</t>
         </is>
       </c>
-      <c r="B95" s="7">
-        <f>SUM(B96,B97)</f>
-        <v/>
+      <c r="B95" s="7" t="n">
+        <v>186778.72</v>
       </c>
       <c r="C95" s="7">
         <f>SUM(C96,C97)</f>
@@ -16130,9 +16216,8 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7">
-        <f>SUM(C96,D96,E96,F96)</f>
-        <v/>
+      <c r="B96" s="7" t="n">
+        <v>44000</v>
       </c>
       <c r="C96" s="7" t="n">
         <v>11000</v>
@@ -16179,9 +16264,8 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7">
-        <f>SUM(C97,D97,E97,F97)</f>
-        <v/>
+      <c r="B97" s="7" t="n">
+        <v>142778.72</v>
       </c>
       <c r="C97" s="7" t="n">
         <v>35694.68</v>
@@ -16228,9 +16312,8 @@
           <t>Чистая прибыль (убыток)</t>
         </is>
       </c>
-      <c r="B98" s="9">
-        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
-        <v/>
+      <c r="B98" s="9" t="n">
+        <v>660855.5800000001</v>
       </c>
       <c r="C98" s="9">
         <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
@@ -16279,9 +16362,10 @@
           <t>Рентабельность чистой прибыли</t>
         </is>
       </c>
-      <c r="B99" s="10">
-        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
-        <v/>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>22.04%</t>
+        </is>
       </c>
       <c r="C99" s="10">
         <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
@@ -16489,9 +16573,8 @@
           <t>Выручка</t>
         </is>
       </c>
-      <c r="B4" s="7">
-        <f>SUM(B5,B6)</f>
-        <v/>
+      <c r="B4" s="7" t="n">
+        <v>6928360.96</v>
       </c>
       <c r="C4" s="7">
         <f>SUM(C5,C6)</f>
@@ -16540,9 +16623,10 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7">
-        <f>SUM(C5,D5,E5,F5)</f>
-        <v/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -16597,9 +16681,8 @@
           <t xml:space="preserve">    Выручка </t>
         </is>
       </c>
-      <c r="B6" s="7">
-        <f>SUM(B7,B8,B9)</f>
-        <v/>
+      <c r="B6" s="7" t="n">
+        <v>6928360.96</v>
       </c>
       <c r="C6" s="7">
         <f>SUM(C7,C8,C9)</f>
@@ -16648,9 +16731,8 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7">
-        <f>SUM(C7,D7,E7,F7)</f>
-        <v/>
+      <c r="B7" s="7" t="n">
+        <v>6928360.96</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>1732090.24</v>
@@ -16697,9 +16779,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7">
-        <f>SUM(C8,D8,E8,F8)</f>
-        <v/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -16754,9 +16837,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7">
-        <f>SUM(C9,D9,E9,F9)</f>
-        <v/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -16811,9 +16895,8 @@
           <t>Прямые расходы</t>
         </is>
       </c>
-      <c r="B10" s="7">
-        <f>SUM(B11,B12,B13,B21,B22,B23,B24,B25,B26,B27,B28,B29,B30,B31,B32,B33,B34)</f>
-        <v/>
+      <c r="B10" s="7" t="n">
+        <v>3447457</v>
       </c>
       <c r="C10" s="7">
         <f>SUM(C11,C12,C13,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34)</f>
@@ -16862,9 +16945,10 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7">
-        <f>SUM(C11,D11,E11,F11)</f>
-        <v/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -16919,9 +17003,10 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7">
-        <f>SUM(C12,D12,E12,F12)</f>
-        <v/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -16976,9 +17061,8 @@
           <t xml:space="preserve">    Переменные</t>
         </is>
       </c>
-      <c r="B13" s="7">
-        <f>SUM(B14,B15,B16,B17,B18,B19,B20)</f>
-        <v/>
+      <c r="B13" s="7" t="n">
+        <v>416519</v>
       </c>
       <c r="C13" s="7">
         <f>SUM(C14,C15,C16,C17,C18,C19,C20)</f>
@@ -17027,9 +17111,10 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7">
-        <f>SUM(C14,D14,E14,F14)</f>
-        <v/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -17084,9 +17169,8 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(C15,D15,E15,F15)</f>
-        <v/>
+      <c r="B15" s="7" t="n">
+        <v>356500</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>80500</v>
@@ -17133,9 +17217,10 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(C16,D16,E16,F16)</f>
-        <v/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -17190,9 +17275,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7">
-        <f>SUM(C17,D17,E17,F17)</f>
-        <v/>
+      <c r="B17" s="7" t="n">
+        <v>20000</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>5000</v>
@@ -17239,9 +17323,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>SUM(C18,D18,E18,F18)</f>
-        <v/>
+      <c r="B18" s="7" t="n">
+        <v>40019</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>25019</v>
@@ -17288,9 +17371,10 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>SUM(C19,D19,E19,F19)</f>
-        <v/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -17345,9 +17429,10 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>SUM(C20,D20,E20,F20)</f>
-        <v/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -17402,9 +17487,8 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>SUM(C21,D21,E21,F21)</f>
-        <v/>
+      <c r="B21" s="7" t="n">
+        <v>1204000</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>301000</v>
@@ -17451,9 +17535,8 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>SUM(C22,D22,E22,F22)</f>
-        <v/>
+      <c r="B22" s="7" t="n">
+        <v>1335994</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>333994</v>
@@ -17500,9 +17583,8 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>SUM(C23,D23,E23,F23)</f>
-        <v/>
+      <c r="B23" s="7" t="n">
+        <v>195244</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>48811</v>
@@ -17549,9 +17631,8 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>SUM(C24,D24,E24,F24)</f>
-        <v/>
+      <c r="B24" s="7" t="n">
+        <v>56000</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>14000</v>
@@ -17598,9 +17679,8 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>SUM(C25,D25,E25,F25)</f>
-        <v/>
+      <c r="B25" s="7" t="n">
+        <v>2000</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>2000</v>
@@ -17653,9 +17733,10 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>SUM(C26,D26,E26,F26)</f>
-        <v/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -17710,9 +17791,10 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7">
-        <f>SUM(C27,D27,E27,F27)</f>
-        <v/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -17767,9 +17849,10 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7">
-        <f>SUM(C28,D28,E28,F28)</f>
-        <v/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -17824,9 +17907,10 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7">
-        <f>SUM(C29,D29,E29,F29)</f>
-        <v/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -17881,9 +17965,10 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7">
-        <f>SUM(C30,D30,E30,F30)</f>
-        <v/>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -17938,9 +18023,8 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7">
-        <f>SUM(C31,D31,E31,F31)</f>
-        <v/>
+      <c r="B31" s="7" t="n">
+        <v>3200</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>3200</v>
@@ -17993,9 +18077,10 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>SUM(C32,D32,E32,F32)</f>
-        <v/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -18050,9 +18135,10 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>SUM(C33,D33,E33,F33)</f>
-        <v/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -18107,9 +18193,8 @@
           <t xml:space="preserve">    Общехозяйственные</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>SUM(B35,B36,B37,B38,B39,B40,B41,B42)</f>
-        <v/>
+      <c r="B34" s="7" t="n">
+        <v>234500</v>
       </c>
       <c r="C34" s="7">
         <f>SUM(C35,C36,C37,C38,C39,C40,C41,C42)</f>
@@ -18158,9 +18243,10 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>SUM(C35,D35,E35,F35)</f>
-        <v/>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -18215,9 +18301,10 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7">
-        <f>SUM(C36,D36,E36,F36)</f>
-        <v/>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -18272,9 +18359,8 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7">
-        <f>SUM(C37,D37,E37,F37)</f>
-        <v/>
+      <c r="B37" s="7" t="n">
+        <v>2000</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>2000</v>
@@ -18327,9 +18413,10 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7">
-        <f>SUM(C38,D38,E38,F38)</f>
-        <v/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -18384,9 +18471,8 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7">
-        <f>SUM(C39,D39,E39,F39)</f>
-        <v/>
+      <c r="B39" s="7" t="n">
+        <v>232500</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>72900</v>
@@ -18433,9 +18519,10 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>SUM(C40,D40,E40,F40)</f>
-        <v/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -18490,9 +18577,10 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>SUM(C41,D41,E41,F41)</f>
-        <v/>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
@@ -18547,9 +18635,10 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>SUM(C42,D42,E42,F42)</f>
-        <v/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -18604,9 +18693,8 @@
           <t>Валовая прибыль</t>
         </is>
       </c>
-      <c r="B43" s="9">
-        <f>B4-B10</f>
-        <v/>
+      <c r="B43" s="9" t="n">
+        <v>3480903.96</v>
       </c>
       <c r="C43" s="9">
         <f>C4-C10</f>
@@ -18655,9 +18743,10 @@
           <t>Валовая рентабельность</t>
         </is>
       </c>
-      <c r="B44" s="10">
-        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
-        <v/>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>50.24%</t>
+        </is>
       </c>
       <c r="C44" s="10">
         <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
@@ -18706,9 +18795,8 @@
           <t>Косвенные расходы</t>
         </is>
       </c>
-      <c r="B45" s="7">
-        <f>SUM(B46,B47,B48,B52,B56,B57,B58,B59,B60,B63,B64,B65,B66,B67,B68,B69,B70,B71,B72,B73,B74,B75,B76,B77,B78,B79)</f>
-        <v/>
+      <c r="B45" s="7" t="n">
+        <v>819695.0600000001</v>
       </c>
       <c r="C45" s="7">
         <f>SUM(C46,C47,C48,C52,C56,C57,C58,C59,C60,C63,C64,C65,C66,C67,C68,C69,C70,C71,C72,C73,C74,C75,C76,C77,C78,C79)</f>
@@ -18757,9 +18845,8 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7">
-        <f>SUM(C46,D46,E46,F46)</f>
-        <v/>
+      <c r="B46" s="7" t="n">
+        <v>772399.64</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>193099.91</v>
@@ -18806,9 +18893,10 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7">
-        <f>SUM(C47,D47,E47,F47)</f>
-        <v/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -18863,9 +18951,10 @@
           <t xml:space="preserve">    Автомобиль</t>
         </is>
       </c>
-      <c r="B48" s="7">
-        <f>SUM(B49,B50,B51)</f>
-        <v/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C48" s="7">
         <f>SUM(C49,C50,C51)</f>
@@ -18914,9 +19003,10 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7">
-        <f>SUM(C49,D49,E49,F49)</f>
-        <v/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -18971,9 +19061,10 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7">
-        <f>SUM(C50,D50,E50,F50)</f>
-        <v/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -19028,9 +19119,10 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7">
-        <f>SUM(C51,D51,E51,F51)</f>
-        <v/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -19085,9 +19177,8 @@
           <t xml:space="preserve">    Офисные расходы</t>
         </is>
       </c>
-      <c r="B52" s="7">
-        <f>SUM(B53,B54,B55)</f>
-        <v/>
+      <c r="B52" s="7" t="n">
+        <v>39295.42</v>
       </c>
       <c r="C52" s="7">
         <f>SUM(C53,C54,C55)</f>
@@ -19136,9 +19227,8 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7">
-        <f>SUM(C53,D53,E53,F53)</f>
-        <v/>
+      <c r="B53" s="7" t="n">
+        <v>39295.42</v>
       </c>
       <c r="C53" s="7" t="n">
         <v>9886.42</v>
@@ -19185,9 +19275,10 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7">
-        <f>SUM(C54,D54,E54,F54)</f>
-        <v/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -19242,9 +19333,10 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7">
-        <f>SUM(C55,D55,E55,F55)</f>
-        <v/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -19299,9 +19391,8 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7">
-        <f>SUM(C56,D56,E56,F56)</f>
-        <v/>
+      <c r="B56" s="7" t="n">
+        <v>8000</v>
       </c>
       <c r="C56" s="7" t="n">
         <v>2000</v>
@@ -19348,9 +19439,10 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7">
-        <f>SUM(C57,D57,E57,F57)</f>
-        <v/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -19405,9 +19497,10 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7">
-        <f>SUM(C58,D58,E58,F58)</f>
-        <v/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -19462,9 +19555,10 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7">
-        <f>SUM(C59,D59,E59,F59)</f>
-        <v/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -19519,9 +19613,10 @@
           <t xml:space="preserve">    Командировочные расходы</t>
         </is>
       </c>
-      <c r="B60" s="7">
-        <f>SUM(B61,B62)</f>
-        <v/>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C60" s="7">
         <f>SUM(C61,C62)</f>
@@ -19570,9 +19665,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7">
-        <f>SUM(C61,D61,E61,F61)</f>
-        <v/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -19627,9 +19723,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7">
-        <f>SUM(C62,D62,E62,F62)</f>
-        <v/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -19684,9 +19781,10 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7">
-        <f>SUM(C63,D63,E63,F63)</f>
-        <v/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -19741,9 +19839,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7">
-        <f>SUM(C64,D64,E64,F64)</f>
-        <v/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -19798,9 +19897,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7">
-        <f>SUM(C65,D65,E65,F65)</f>
-        <v/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -19855,9 +19955,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7">
-        <f>SUM(C66,D66,E66,F66)</f>
-        <v/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -19912,9 +20013,10 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7">
-        <f>SUM(C67,D67,E67,F67)</f>
-        <v/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -19969,9 +20071,10 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7">
-        <f>SUM(C68,D68,E68,F68)</f>
-        <v/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -20026,9 +20129,10 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7">
-        <f>SUM(C69,D69,E69,F69)</f>
-        <v/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -20083,9 +20187,10 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7">
-        <f>SUM(C70,D70,E70,F70)</f>
-        <v/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -20140,9 +20245,10 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7">
-        <f>SUM(C71,D71,E71,F71)</f>
-        <v/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -20197,9 +20303,10 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7">
-        <f>SUM(C72,D72,E72,F72)</f>
-        <v/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -20254,9 +20361,10 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7">
-        <f>SUM(C73,D73,E73,F73)</f>
-        <v/>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -20311,9 +20419,10 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7">
-        <f>SUM(C74,D74,E74,F74)</f>
-        <v/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -20368,9 +20477,10 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7">
-        <f>SUM(C75,D75,E75,F75)</f>
-        <v/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -20425,9 +20535,10 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7">
-        <f>SUM(C76,D76,E76,F76)</f>
-        <v/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -20482,9 +20593,10 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7">
-        <f>SUM(C77,D77,E77,F77)</f>
-        <v/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -20539,9 +20651,10 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7">
-        <f>SUM(C78,D78,E78,F78)</f>
-        <v/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -20596,9 +20709,10 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7">
-        <f>SUM(C79,D79,E79,F79)</f>
-        <v/>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -20653,9 +20767,8 @@
           <t>Операционная прибыль</t>
         </is>
       </c>
-      <c r="B80" s="9">
-        <f>B43-B45</f>
-        <v/>
+      <c r="B80" s="9" t="n">
+        <v>2661208.9</v>
       </c>
       <c r="C80" s="9">
         <f>C43-C45</f>
@@ -20704,9 +20817,10 @@
           <t>Операционная рентабельность</t>
         </is>
       </c>
-      <c r="B81" s="10">
-        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
-        <v/>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>38.41%</t>
+        </is>
       </c>
       <c r="C81" s="10">
         <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
@@ -20755,9 +20869,10 @@
           <t>Прочие доходы</t>
         </is>
       </c>
-      <c r="B82" s="7">
-        <f>SUM(B83,B84,B85,B86)</f>
-        <v/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C82" s="7">
         <f>SUM(C83,C84,C85,C86)</f>
@@ -20806,9 +20921,10 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7">
-        <f>SUM(C83,D83,E83,F83)</f>
-        <v/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -20863,9 +20979,10 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7">
-        <f>SUM(C84,D84,E84,F84)</f>
-        <v/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -20920,9 +21037,10 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7">
-        <f>SUM(C85,D85,E85,F85)</f>
-        <v/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -20977,9 +21095,10 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7">
-        <f>SUM(C86,D86,E86,F86)</f>
-        <v/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -21034,9 +21153,10 @@
           <t>Прочие расходы</t>
         </is>
       </c>
-      <c r="B87" s="7">
-        <f>SUM(B88)</f>
-        <v/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C87" s="7">
         <f>SUM(C88)</f>
@@ -21085,9 +21205,10 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7">
-        <f>SUM(C88,D88,E88,F88)</f>
-        <v/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -21142,9 +21263,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B89" s="9">
-        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
-        <v/>
+      <c r="B89" s="9" t="n">
+        <v>2661208.9</v>
       </c>
       <c r="C89" s="9">
         <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
@@ -21193,9 +21313,10 @@
           <t>Рентабельность по EBITDA</t>
         </is>
       </c>
-      <c r="B90" s="10">
-        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
-        <v/>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>38.41%</t>
+        </is>
       </c>
       <c r="C90" s="10">
         <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
@@ -21244,9 +21365,10 @@
           <t>Амортизация</t>
         </is>
       </c>
-      <c r="B91" s="7">
-        <f>SUM(B92,B93)</f>
-        <v/>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C91" s="7">
         <f>SUM(C92,C93)</f>
@@ -21295,9 +21417,10 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7">
-        <f>SUM(C92,D92,E92,F92)</f>
-        <v/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -21352,9 +21475,10 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7">
-        <f>SUM(C93,D93,E93,F93)</f>
-        <v/>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -21409,9 +21533,10 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7">
-        <f>SUM(C94,D94,E94,F94)</f>
-        <v/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -21466,9 +21591,8 @@
           <t>Налог на прибыль</t>
         </is>
       </c>
-      <c r="B95" s="7">
-        <f>SUM(B96,B97)</f>
-        <v/>
+      <c r="B95" s="7" t="n">
+        <v>429930.56</v>
       </c>
       <c r="C95" s="7">
         <f>SUM(C96,C97)</f>
@@ -21517,9 +21641,8 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7">
-        <f>SUM(C96,D96,E96,F96)</f>
-        <v/>
+      <c r="B96" s="7" t="n">
+        <v>100000</v>
       </c>
       <c r="C96" s="7" t="n">
         <v>25000</v>
@@ -21566,9 +21689,8 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7">
-        <f>SUM(C97,D97,E97,F97)</f>
-        <v/>
+      <c r="B97" s="7" t="n">
+        <v>329930.56</v>
       </c>
       <c r="C97" s="7" t="n">
         <v>82482.64</v>
@@ -21615,9 +21737,8 @@
           <t>Чистая прибыль (убыток)</t>
         </is>
       </c>
-      <c r="B98" s="9">
-        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
-        <v/>
+      <c r="B98" s="9" t="n">
+        <v>2231278.34</v>
       </c>
       <c r="C98" s="9">
         <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
@@ -21666,9 +21787,10 @@
           <t>Рентабельность чистой прибыли</t>
         </is>
       </c>
-      <c r="B99" s="10">
-        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
-        <v/>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>32.20%</t>
+        </is>
       </c>
       <c r="C99" s="10">
         <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
@@ -21876,9 +21998,8 @@
           <t>Выручка</t>
         </is>
       </c>
-      <c r="B4" s="7">
-        <f>SUM(B5,B6)</f>
-        <v/>
+      <c r="B4" s="7" t="n">
+        <v>872916.16</v>
       </c>
       <c r="C4" s="7">
         <f>SUM(C5,C6)</f>
@@ -21927,9 +22048,10 @@
           <t xml:space="preserve">    Нераспределенный доход</t>
         </is>
       </c>
-      <c r="B5" s="7">
-        <f>SUM(C5,D5,E5,F5)</f>
-        <v/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -21984,9 +22106,8 @@
           <t xml:space="preserve">    Выручка </t>
         </is>
       </c>
-      <c r="B6" s="7">
-        <f>SUM(B7,B8,B9)</f>
-        <v/>
+      <c r="B6" s="7" t="n">
+        <v>872916.16</v>
       </c>
       <c r="C6" s="7">
         <f>SUM(C7,C8,C9)</f>
@@ -22035,9 +22156,8 @@
           <t xml:space="preserve">        Реализация услуг Клининг (ОД)</t>
         </is>
       </c>
-      <c r="B7" s="7">
-        <f>SUM(C7,D7,E7,F7)</f>
-        <v/>
+      <c r="B7" s="7" t="n">
+        <v>872916.16</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>218229.04</v>
@@ -22084,9 +22204,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (Доп.услуги)</t>
         </is>
       </c>
-      <c r="B8" s="7">
-        <f>SUM(C8,D8,E8,F8)</f>
-        <v/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -22141,9 +22262,10 @@
           <t xml:space="preserve">        Реализация услуг Клининг (снег)</t>
         </is>
       </c>
-      <c r="B9" s="7">
-        <f>SUM(C9,D9,E9,F9)</f>
-        <v/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -22198,9 +22320,8 @@
           <t>Прямые расходы</t>
         </is>
       </c>
-      <c r="B10" s="7">
-        <f>SUM(B11,B12,B13,B21,B22,B23,B24,B25,B26,B27,B28,B29,B30,B31,B32,B33,B34)</f>
-        <v/>
+      <c r="B10" s="7" t="n">
+        <v>1043970.11</v>
       </c>
       <c r="C10" s="7">
         <f>SUM(C11,C12,C13,C21,C22,C23,C24,C25,C26,C27,C28,C29,C30,C31,C32,C33,C34)</f>
@@ -22249,9 +22370,10 @@
           <t xml:space="preserve">    Нераспределенный расход</t>
         </is>
       </c>
-      <c r="B11" s="7">
-        <f>SUM(C11,D11,E11,F11)</f>
-        <v/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -22306,9 +22428,10 @@
           <t xml:space="preserve">    Транспортные расходы</t>
         </is>
       </c>
-      <c r="B12" s="7">
-        <f>SUM(C12,D12,E12,F12)</f>
-        <v/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -22363,9 +22486,8 @@
           <t xml:space="preserve">    Переменные</t>
         </is>
       </c>
-      <c r="B13" s="7">
-        <f>SUM(B14,B15,B16,B17,B18,B19,B20)</f>
-        <v/>
+      <c r="B13" s="7" t="n">
+        <v>7219.98</v>
       </c>
       <c r="C13" s="7">
         <f>SUM(C14,C15,C16,C17,C18,C19,C20)</f>
@@ -22414,9 +22536,10 @@
           <t xml:space="preserve">        Услуги техниги для уборки снега (ПТ)</t>
         </is>
       </c>
-      <c r="B14" s="7">
-        <f>SUM(C14,D14,E14,F14)</f>
-        <v/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -22471,9 +22594,10 @@
           <t xml:space="preserve">        Услуги садовника (ПТ)</t>
         </is>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(C15,D15,E15,F15)</f>
-        <v/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -22528,9 +22652,10 @@
           <t xml:space="preserve">        Сыпучие материалы (ПТ)</t>
         </is>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(C16,D16,E16,F16)</f>
-        <v/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -22585,9 +22710,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы (МОП)</t>
         </is>
       </c>
-      <c r="B17" s="7">
-        <f>SUM(C17,D17,E17,F17)</f>
-        <v/>
+      <c r="B17" s="7" t="n">
+        <v>3219.98</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>219.98</v>
@@ -22634,9 +22758,8 @@
           <t xml:space="preserve">        Расходные материалы и инстументы  (ПТ)</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>SUM(C18,D18,E18,F18)</f>
-        <v/>
+      <c r="B18" s="7" t="n">
+        <v>4000</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>1000</v>
@@ -22683,9 +22806,10 @@
           <t xml:space="preserve">        Арена оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>SUM(C19,D19,E19,F19)</f>
-        <v/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -22740,9 +22864,10 @@
           <t xml:space="preserve">        Арена оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>SUM(C20,D20,E20,F20)</f>
-        <v/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -22797,9 +22922,8 @@
           <t xml:space="preserve">    Заработная плата  (МОП)</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>SUM(C21,D21,E21,F21)</f>
-        <v/>
+      <c r="B21" s="7" t="n">
+        <v>340000</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>85000</v>
@@ -22846,9 +22970,8 @@
           <t xml:space="preserve">    Заработная плата (ПТ)</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>SUM(C22,D22,E22,F22)</f>
-        <v/>
+      <c r="B22" s="7" t="n">
+        <v>500000</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>125000</v>
@@ -22895,9 +23018,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (МОП)</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>SUM(C23,D23,E23,F23)</f>
-        <v/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -22952,9 +23076,8 @@
           <t xml:space="preserve">    Налоги с ФОТ (ПТ)</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>SUM(C24,D24,E24,F24)</f>
-        <v/>
+      <c r="B24" s="7" t="n">
+        <v>48631.75</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>6631.75</v>
@@ -23001,9 +23124,10 @@
           <t xml:space="preserve">    Премми  (МОП)</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>SUM(C25,D25,E25,F25)</f>
-        <v/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -23058,9 +23182,10 @@
           <t xml:space="preserve">    Премми (ПТ)</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>SUM(C26,D26,E26,F26)</f>
-        <v/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -23115,9 +23240,10 @@
           <t xml:space="preserve">    Униформа (МОП)</t>
         </is>
       </c>
-      <c r="B27" s="7">
-        <f>SUM(C27,D27,E27,F27)</f>
-        <v/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -23172,9 +23298,10 @@
           <t xml:space="preserve">    Униформа (ПТ)</t>
         </is>
       </c>
-      <c r="B28" s="7">
-        <f>SUM(C28,D28,E28,F28)</f>
-        <v/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -23229,9 +23356,10 @@
           <t xml:space="preserve">    Ремонт оборудования (МОП)</t>
         </is>
       </c>
-      <c r="B29" s="7">
-        <f>SUM(C29,D29,E29,F29)</f>
-        <v/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -23286,9 +23414,8 @@
           <t xml:space="preserve">    Ремонт оборудования (ПТ)</t>
         </is>
       </c>
-      <c r="B30" s="7">
-        <f>SUM(C30,D30,E30,F30)</f>
-        <v/>
+      <c r="B30" s="7" t="n">
+        <v>12000</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>3000</v>
@@ -23335,9 +23462,10 @@
           <t xml:space="preserve">    Вывоз мусора</t>
         </is>
       </c>
-      <c r="B31" s="7">
-        <f>SUM(C31,D31,E31,F31)</f>
-        <v/>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -23392,9 +23520,10 @@
           <t xml:space="preserve">    Штрафы, пени, неустойки</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>SUM(C32,D32,E32,F32)</f>
-        <v/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -23449,9 +23578,10 @@
           <t xml:space="preserve">    Расходы к удержанию</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>SUM(C33,D33,E33,F33)</f>
-        <v/>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -23506,9 +23636,8 @@
           <t xml:space="preserve">    Общехозяйственные</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>SUM(B35,B36,B37,B38,B39,B40,B41,B42)</f>
-        <v/>
+      <c r="B34" s="7" t="n">
+        <v>136118.38</v>
       </c>
       <c r="C34" s="7">
         <f>SUM(C35,C36,C37,C38,C39,C40,C41,C42)</f>
@@ -23557,9 +23686,10 @@
           <t xml:space="preserve">        Аутсорс (направления)</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>SUM(C35,D35,E35,F35)</f>
-        <v/>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -23614,9 +23744,8 @@
           <t xml:space="preserve">        Заработная плата МО АУП</t>
         </is>
       </c>
-      <c r="B36" s="7">
-        <f>SUM(C36,D36,E36,F36)</f>
-        <v/>
+      <c r="B36" s="7" t="n">
+        <v>80000</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>20000</v>
@@ -23663,9 +23792,8 @@
           <t xml:space="preserve">        Инструменты: ГСМ</t>
         </is>
       </c>
-      <c r="B37" s="7">
-        <f>SUM(C37,D37,E37,F37)</f>
-        <v/>
+      <c r="B37" s="7" t="n">
+        <v>4118.38</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>1118.38</v>
@@ -23712,9 +23840,10 @@
           <t xml:space="preserve">        Медосмотры</t>
         </is>
       </c>
-      <c r="B38" s="7">
-        <f>SUM(C38,D38,E38,F38)</f>
-        <v/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -23769,9 +23898,8 @@
           <t xml:space="preserve">        Налоги с ФОТ (ИП)</t>
         </is>
       </c>
-      <c r="B39" s="7">
-        <f>SUM(C39,D39,E39,F39)</f>
-        <v/>
+      <c r="B39" s="7" t="n">
+        <v>52000</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>13000</v>
@@ -23818,9 +23946,10 @@
           <t xml:space="preserve">        Приобритение мебели, бытовой техники</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>SUM(C40,D40,E40,F40)</f>
-        <v/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -23875,9 +24004,10 @@
           <t xml:space="preserve">        Комиссия за перевод ЗП</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>SUM(C41,D41,E41,F41)</f>
-        <v/>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
@@ -23932,9 +24062,10 @@
           <t xml:space="preserve">        Аренда квартиры (включая коммуналку)</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>SUM(C42,D42,E42,F42)</f>
-        <v/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -23989,9 +24120,8 @@
           <t>Валовая прибыль</t>
         </is>
       </c>
-      <c r="B43" s="9">
-        <f>B4-B10</f>
-        <v/>
+      <c r="B43" s="9" t="n">
+        <v>-171053.95</v>
       </c>
       <c r="C43" s="9">
         <f>C4-C10</f>
@@ -24040,9 +24170,10 @@
           <t>Валовая рентабельность</t>
         </is>
       </c>
-      <c r="B44" s="10">
-        <f>IFERROR(IF(B4=0,"-",B43/B4),"-")</f>
-        <v/>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>-19.60%</t>
+        </is>
       </c>
       <c r="C44" s="10">
         <f>IFERROR(IF(C4=0,"-",C43/C4),"-")</f>
@@ -24091,9 +24222,8 @@
           <t>Косвенные расходы</t>
         </is>
       </c>
-      <c r="B45" s="7">
-        <f>SUM(B46,B47,B48,B52,B56,B57,B58,B59,B60,B63,B64,B65,B66,B67,B68,B69,B70,B71,B72,B73,B74,B75,B76,B77,B78,B79)</f>
-        <v/>
+      <c r="B45" s="7" t="n">
+        <v>150809.56</v>
       </c>
       <c r="C45" s="7">
         <f>SUM(C46,C47,C48,C52,C56,C57,C58,C59,C60,C63,C64,C65,C66,C67,C68,C69,C70,C71,C72,C73,C74,C75,C76,C77,C78,C79)</f>
@@ -24142,9 +24272,8 @@
           <t xml:space="preserve">    Расход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B46" s="7">
-        <f>SUM(C46,D46,E46,F46)</f>
-        <v/>
+      <c r="B46" s="7" t="n">
+        <v>150809.56</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>37702.39</v>
@@ -24191,9 +24320,10 @@
           <t xml:space="preserve">    Расходы на бэк-офис</t>
         </is>
       </c>
-      <c r="B47" s="7">
-        <f>SUM(C47,D47,E47,F47)</f>
-        <v/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
@@ -24248,9 +24378,10 @@
           <t xml:space="preserve">    Автомобиль</t>
         </is>
       </c>
-      <c r="B48" s="7">
-        <f>SUM(B49,B50,B51)</f>
-        <v/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C48" s="7">
         <f>SUM(C49,C50,C51)</f>
@@ -24299,9 +24430,10 @@
           <t xml:space="preserve">        Автомобиль: ГСМ</t>
         </is>
       </c>
-      <c r="B49" s="7">
-        <f>SUM(C49,D49,E49,F49)</f>
-        <v/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
@@ -24356,9 +24488,10 @@
           <t xml:space="preserve">        Автомобиль: страхование</t>
         </is>
       </c>
-      <c r="B50" s="7">
-        <f>SUM(C50,D50,E50,F50)</f>
-        <v/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
@@ -24413,9 +24546,10 @@
           <t xml:space="preserve">        Автомобиль: ТО</t>
         </is>
       </c>
-      <c r="B51" s="7">
-        <f>SUM(C51,D51,E51,F51)</f>
-        <v/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
@@ -24470,9 +24604,10 @@
           <t xml:space="preserve">    Офисные расходы</t>
         </is>
       </c>
-      <c r="B52" s="7">
-        <f>SUM(B53,B54,B55)</f>
-        <v/>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C52" s="7">
         <f>SUM(C53,C54,C55)</f>
@@ -24521,9 +24656,10 @@
           <t xml:space="preserve">        Аренда офиса</t>
         </is>
       </c>
-      <c r="B53" s="7">
-        <f>SUM(C53,D53,E53,F53)</f>
-        <v/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
@@ -24578,9 +24714,10 @@
           <t xml:space="preserve">        Канцелярия и обслуживание</t>
         </is>
       </c>
-      <c r="B54" s="7">
-        <f>SUM(C54,D54,E54,F54)</f>
-        <v/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
@@ -24635,9 +24772,10 @@
           <t xml:space="preserve">        Интернет и связь</t>
         </is>
       </c>
-      <c r="B55" s="7">
-        <f>SUM(C55,D55,E55,F55)</f>
-        <v/>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
@@ -24692,9 +24830,10 @@
           <t xml:space="preserve">    Банковские услуги</t>
         </is>
       </c>
-      <c r="B56" s="7">
-        <f>SUM(C56,D56,E56,F56)</f>
-        <v/>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
@@ -24749,9 +24888,10 @@
           <t xml:space="preserve">    Заработная плата АУП (БО)</t>
         </is>
       </c>
-      <c r="B57" s="7">
-        <f>SUM(C57,D57,E57,F57)</f>
-        <v/>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
@@ -24806,9 +24946,10 @@
           <t xml:space="preserve">    Заработная плата бухгалтерии (БО)</t>
         </is>
       </c>
-      <c r="B58" s="7">
-        <f>SUM(C58,D58,E58,F58)</f>
-        <v/>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
@@ -24863,9 +25004,10 @@
           <t xml:space="preserve">    Заработная плата СБ (БО)</t>
         </is>
       </c>
-      <c r="B59" s="7">
-        <f>SUM(C59,D59,E59,F59)</f>
-        <v/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
@@ -24920,9 +25062,10 @@
           <t xml:space="preserve">    Командировочные расходы</t>
         </is>
       </c>
-      <c r="B60" s="7">
-        <f>SUM(B61,B62)</f>
-        <v/>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C60" s="7">
         <f>SUM(C61,C62)</f>
@@ -24971,9 +25114,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: билеты (БО)</t>
         </is>
       </c>
-      <c r="B61" s="7">
-        <f>SUM(C61,D61,E61,F61)</f>
-        <v/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -25028,9 +25172,10 @@
           <t xml:space="preserve">        Командировнчеы расходы: проживание (БО)</t>
         </is>
       </c>
-      <c r="B62" s="7">
-        <f>SUM(C62,D62,E62,F62)</f>
-        <v/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -25085,9 +25230,10 @@
           <t xml:space="preserve">    Комиссия УК ДОМ</t>
         </is>
       </c>
-      <c r="B63" s="7">
-        <f>SUM(C63,D63,E63,F63)</f>
-        <v/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
@@ -25142,9 +25288,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (ИП)_БО</t>
         </is>
       </c>
-      <c r="B64" s="7">
-        <f>SUM(C64,D64,E64,F64)</f>
-        <v/>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
@@ -25199,9 +25346,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (НДФЛ) БО</t>
         </is>
       </c>
-      <c r="B65" s="7">
-        <f>SUM(C65,D65,E65,F65)</f>
-        <v/>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
@@ -25256,9 +25404,10 @@
           <t xml:space="preserve">    Налоги с ФОТ (страховые взносы) БО</t>
         </is>
       </c>
-      <c r="B66" s="7">
-        <f>SUM(C66,D66,E66,F66)</f>
-        <v/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
@@ -25313,9 +25462,10 @@
           <t xml:space="preserve">    Нотариальные услуги</t>
         </is>
       </c>
-      <c r="B67" s="7">
-        <f>SUM(C67,D67,E67,F67)</f>
-        <v/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -25370,9 +25520,10 @@
           <t xml:space="preserve">    Обслуживание техники (БО)</t>
         </is>
       </c>
-      <c r="B68" s="7">
-        <f>SUM(C68,D68,E68,F68)</f>
-        <v/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -25427,9 +25578,10 @@
           <t xml:space="preserve">    Программное обеспечение (БО)</t>
         </is>
       </c>
-      <c r="B69" s="7">
-        <f>SUM(C69,D69,E69,F69)</f>
-        <v/>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -25484,9 +25636,10 @@
           <t xml:space="preserve">        ПланФакт</t>
         </is>
       </c>
-      <c r="B70" s="7">
-        <f>SUM(C70,D70,E70,F70)</f>
-        <v/>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -25541,9 +25694,10 @@
           <t xml:space="preserve">        ТБ</t>
         </is>
       </c>
-      <c r="B71" s="7">
-        <f>SUM(C71,D71,E71,F71)</f>
-        <v/>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
@@ -25598,9 +25752,10 @@
           <t xml:space="preserve">        Контур</t>
         </is>
       </c>
-      <c r="B72" s="7">
-        <f>SUM(C72,D72,E72,F72)</f>
-        <v/>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
@@ -25655,9 +25810,10 @@
           <t xml:space="preserve">        Platrum</t>
         </is>
       </c>
-      <c r="B73" s="7">
-        <f>SUM(C73,D73,E73,F73)</f>
-        <v/>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -25712,9 +25868,10 @@
           <t xml:space="preserve">        Расходы на сайт (БО)</t>
         </is>
       </c>
-      <c r="B74" s="7">
-        <f>SUM(C74,D74,E74,F74)</f>
-        <v/>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -25769,9 +25926,10 @@
           <t xml:space="preserve">    Расходы на технику до 40т (БО)</t>
         </is>
       </c>
-      <c r="B75" s="7">
-        <f>SUM(C75,D75,E75,F75)</f>
-        <v/>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
@@ -25826,9 +25984,10 @@
           <t xml:space="preserve">    Такси</t>
         </is>
       </c>
-      <c r="B76" s="7">
-        <f>SUM(C76,D76,E76,F76)</f>
-        <v/>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
@@ -25883,9 +26042,10 @@
           <t xml:space="preserve">    ФД Аутосрс (управление)</t>
         </is>
       </c>
-      <c r="B77" s="7">
-        <f>SUM(C77,D77,E77,F77)</f>
-        <v/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
@@ -25940,9 +26100,10 @@
           <t xml:space="preserve">    Копортативные мероприятия</t>
         </is>
       </c>
-      <c r="B78" s="7">
-        <f>SUM(C78,D78,E78,F78)</f>
-        <v/>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
@@ -25997,9 +26158,10 @@
           <t xml:space="preserve">    HR (аутсорс)</t>
         </is>
       </c>
-      <c r="B79" s="7">
-        <f>SUM(C79,D79,E79,F79)</f>
-        <v/>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
@@ -26054,9 +26216,8 @@
           <t>Операционная прибыль</t>
         </is>
       </c>
-      <c r="B80" s="9">
-        <f>B43-B45</f>
-        <v/>
+      <c r="B80" s="9" t="n">
+        <v>-321863.51</v>
       </c>
       <c r="C80" s="9">
         <f>C43-C45</f>
@@ -26105,9 +26266,10 @@
           <t>Операционная рентабельность</t>
         </is>
       </c>
-      <c r="B81" s="10">
-        <f>IFERROR(IF(B4=0,"-",B80/B4),"-")</f>
-        <v/>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>-36.87%</t>
+        </is>
       </c>
       <c r="C81" s="10">
         <f>IFERROR(IF(C4=0,"-",C80/C4),"-")</f>
@@ -26156,9 +26318,10 @@
           <t>Прочие доходы</t>
         </is>
       </c>
-      <c r="B82" s="7">
-        <f>SUM(B83,B84,B85,B86)</f>
-        <v/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C82" s="7">
         <f>SUM(C83,C84,C85,C86)</f>
@@ -26207,9 +26370,10 @@
           <t xml:space="preserve">    Доход БЭК-ОФИС</t>
         </is>
       </c>
-      <c r="B83" s="7">
-        <f>SUM(C83,D83,E83,F83)</f>
-        <v/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
@@ -26264,9 +26428,10 @@
           <t xml:space="preserve">    Пополненин бэк-офис</t>
         </is>
       </c>
-      <c r="B84" s="7">
-        <f>SUM(C84,D84,E84,F84)</f>
-        <v/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
@@ -26321,9 +26486,10 @@
           <t xml:space="preserve">    Проценты по вкладам</t>
         </is>
       </c>
-      <c r="B85" s="7">
-        <f>SUM(C85,D85,E85,F85)</f>
-        <v/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
@@ -26378,9 +26544,10 @@
           <t xml:space="preserve">    Курсовая разница (+)</t>
         </is>
       </c>
-      <c r="B86" s="7">
-        <f>SUM(C86,D86,E86,F86)</f>
-        <v/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
@@ -26435,9 +26602,10 @@
           <t>Прочие расходы</t>
         </is>
       </c>
-      <c r="B87" s="7">
-        <f>SUM(B88)</f>
-        <v/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C87" s="7">
         <f>SUM(C88)</f>
@@ -26486,9 +26654,10 @@
           <t xml:space="preserve">    Курсовая разница (-)</t>
         </is>
       </c>
-      <c r="B88" s="7">
-        <f>SUM(C88,D88,E88,F88)</f>
-        <v/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
@@ -26543,9 +26712,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B89" s="9">
-        <f>B80+IFERROR(B82*1,0)-IFERROR(B87*1,0)</f>
-        <v/>
+      <c r="B89" s="9" t="n">
+        <v>-321863.51</v>
       </c>
       <c r="C89" s="9">
         <f>C80+IFERROR(C82*1,0)-IFERROR(C87*1,0)</f>
@@ -26594,9 +26762,10 @@
           <t>Рентабельность по EBITDA</t>
         </is>
       </c>
-      <c r="B90" s="10">
-        <f>IFERROR(IF(B4=0,"-",B89/B4),"-")</f>
-        <v/>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>-36.87%</t>
+        </is>
       </c>
       <c r="C90" s="10">
         <f>IFERROR(IF(C4=0,"-",C89/C4),"-")</f>
@@ -26645,9 +26814,10 @@
           <t>Амортизация</t>
         </is>
       </c>
-      <c r="B91" s="7">
-        <f>SUM(B92,B93)</f>
-        <v/>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C91" s="7">
         <f>SUM(C92,C93)</f>
@@ -26696,9 +26866,10 @@
           <t xml:space="preserve">    Амортизация ОС (ПТ)</t>
         </is>
       </c>
-      <c r="B92" s="7">
-        <f>SUM(C92,D92,E92,F92)</f>
-        <v/>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
@@ -26753,9 +26924,10 @@
           <t xml:space="preserve">    Амортизация ОС (МОП)</t>
         </is>
       </c>
-      <c r="B93" s="7">
-        <f>SUM(C93,D93,E93,F93)</f>
-        <v/>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
@@ -26810,9 +26982,10 @@
           <t>Проценты по кредитам и займам</t>
         </is>
       </c>
-      <c r="B94" s="7">
-        <f>SUM(C94,D94,E94,F94)</f>
-        <v/>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
@@ -26867,9 +27040,8 @@
           <t>Налог на прибыль</t>
         </is>
       </c>
-      <c r="B95" s="7">
-        <f>SUM(B96,B97)</f>
-        <v/>
+      <c r="B95" s="7" t="n">
+        <v>54767.88</v>
       </c>
       <c r="C95" s="7">
         <f>SUM(C96,C97)</f>
@@ -26918,9 +27090,8 @@
           <t xml:space="preserve">    Налоги УСН</t>
         </is>
       </c>
-      <c r="B96" s="7">
-        <f>SUM(C96,D96,E96,F96)</f>
-        <v/>
+      <c r="B96" s="7" t="n">
+        <v>13200</v>
       </c>
       <c r="C96" s="7" t="n">
         <v>3300</v>
@@ -26967,9 +27138,8 @@
           <t xml:space="preserve">    Налоги НДС 5%</t>
         </is>
       </c>
-      <c r="B97" s="7">
-        <f>SUM(C97,D97,E97,F97)</f>
-        <v/>
+      <c r="B97" s="7" t="n">
+        <v>41567.88</v>
       </c>
       <c r="C97" s="7" t="n">
         <v>10391.97</v>
@@ -27016,9 +27186,8 @@
           <t>Чистая прибыль (убыток)</t>
         </is>
       </c>
-      <c r="B98" s="9">
-        <f>IFERROR(B89*1,0)-IFERROR(B91*1,0)-IFERROR(B94*1,0)-IFERROR(B95*1,0)</f>
-        <v/>
+      <c r="B98" s="9" t="n">
+        <v>-376631.39</v>
       </c>
       <c r="C98" s="9">
         <f>IFERROR(C89*1,0)-IFERROR(C91*1,0)-IFERROR(C94*1,0)-IFERROR(C95*1,0)</f>
@@ -27067,9 +27236,10 @@
           <t>Рентабельность чистой прибыли</t>
         </is>
       </c>
-      <c r="B99" s="10">
-        <f>IFERROR(IF(B4=0,"-",B98/B4),"-")</f>
-        <v/>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>-43.15%</t>
+        </is>
       </c>
       <c r="C99" s="10">
         <f>IFERROR(IF(C4=0,"-",C98/C4),"-")</f>
